--- a/data/mock_product_data.xlsx
+++ b/data/mock_product_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,3290 +486,3518 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>OverrideType</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>AI Price</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Competitor Price</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence Score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Forecast Demand</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7463517</t>
+          <t>0f867433</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.27</v>
+        <v>78.53</v>
       </c>
       <c r="D2" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E2" t="n">
-        <v>90.06</v>
+        <v>61.82</v>
       </c>
       <c r="F2" t="n">
-        <v>76653</v>
+        <v>58680</v>
       </c>
       <c r="G2" t="n">
-        <v>62737</v>
+        <v>49892</v>
       </c>
       <c r="H2" t="n">
-        <v>70364</v>
+        <v>32217</v>
       </c>
       <c r="I2" t="n">
-        <v>45714</v>
+        <v>64332</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>62737</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>94.06</v>
-      </c>
+        <v>32217</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P2" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05633ba4</t>
+          <t>c4b79787</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43.64</v>
+        <v>53.85</v>
       </c>
       <c r="D3" t="n">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="E3" t="n">
-        <v>37.25</v>
+        <v>12.35</v>
       </c>
       <c r="F3" t="n">
-        <v>47082</v>
+        <v>48691</v>
       </c>
       <c r="G3" t="n">
-        <v>46346</v>
+        <v>32793</v>
       </c>
       <c r="H3" t="n">
-        <v>59513</v>
+        <v>74231</v>
       </c>
       <c r="I3" t="n">
-        <v>30066</v>
+        <v>63893</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="b">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>46346</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.82</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>40.25</v>
-      </c>
+        <v>32793</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5c2271e9</t>
+          <t>30cd5455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.38</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>481</v>
+        <v>214</v>
       </c>
       <c r="E4" t="n">
-        <v>59.46</v>
+        <v>58.43</v>
       </c>
       <c r="F4" t="n">
-        <v>75644</v>
+        <v>59355</v>
       </c>
       <c r="G4" t="n">
-        <v>35535</v>
+        <v>31841</v>
       </c>
       <c r="H4" t="n">
-        <v>75351</v>
+        <v>79523</v>
       </c>
       <c r="I4" t="n">
-        <v>25899</v>
+        <v>27807</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>35535</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>72.46000000000001</v>
-      </c>
+        <v>31841</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P4" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>98c23f14</t>
+          <t>ebafd7d0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46.35</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>271</v>
+        <v>121</v>
       </c>
       <c r="E5" t="n">
-        <v>51.76</v>
+        <v>17.32</v>
       </c>
       <c r="F5" t="n">
-        <v>51346</v>
+        <v>50792</v>
       </c>
       <c r="G5" t="n">
-        <v>74539</v>
+        <v>65587</v>
       </c>
       <c r="H5" t="n">
-        <v>71408</v>
+        <v>54637</v>
       </c>
       <c r="I5" t="n">
-        <v>29499</v>
+        <v>33812</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="b">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>51346</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>53.76</v>
-      </c>
+        <v>50792</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>85bd35e6</t>
+          <t>8416be31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsung S23</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.69</v>
+        <v>73.75</v>
       </c>
       <c r="D6" t="n">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E6" t="n">
-        <v>58.64</v>
+        <v>56.58</v>
       </c>
       <c r="F6" t="n">
-        <v>55603</v>
+        <v>57318</v>
       </c>
       <c r="G6" t="n">
-        <v>42804</v>
+        <v>55539</v>
       </c>
       <c r="H6" t="n">
-        <v>40551</v>
+        <v>77568</v>
       </c>
       <c r="I6" t="n">
-        <v>43558</v>
+        <v>18490</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="b">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>40551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.96</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>67.64</v>
-      </c>
+        <v>55539</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P6" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>52c7b4ad</t>
+          <t>53bfaa32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.87</v>
+        <v>87.11</v>
       </c>
       <c r="D7" t="n">
-        <v>348</v>
+        <v>140</v>
       </c>
       <c r="E7" t="n">
-        <v>94.7</v>
+        <v>82.89</v>
       </c>
       <c r="F7" t="n">
-        <v>35282</v>
+        <v>37795</v>
       </c>
       <c r="G7" t="n">
-        <v>34742</v>
+        <v>64875</v>
       </c>
       <c r="H7" t="n">
-        <v>36579</v>
+        <v>48994</v>
       </c>
       <c r="I7" t="n">
-        <v>10163</v>
+        <v>8443</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="b">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>34742</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>105.7</v>
-      </c>
+        <v>37795</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P7" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c87f4eaf</t>
+          <t>79b0243f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.82</v>
+        <v>98.58</v>
       </c>
       <c r="D8" t="n">
-        <v>232</v>
+        <v>394</v>
       </c>
       <c r="E8" t="n">
-        <v>51.62</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>57424</v>
+        <v>39185</v>
       </c>
       <c r="G8" t="n">
-        <v>59873</v>
+        <v>44889</v>
       </c>
       <c r="H8" t="n">
-        <v>69848</v>
+        <v>61293</v>
       </c>
       <c r="I8" t="n">
-        <v>12011</v>
+        <v>62688</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="b">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>57424</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.68</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>61.62</v>
-      </c>
+        <v>39185</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5eb0cb08</t>
+          <t>a3c9e17a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49.97</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>231</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>24.51</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65570</v>
+        <v>37844</v>
       </c>
       <c r="G9" t="n">
-        <v>52886</v>
+        <v>45868</v>
       </c>
       <c r="H9" t="n">
-        <v>69019</v>
+        <v>61346</v>
       </c>
       <c r="I9" t="n">
-        <v>24570</v>
+        <v>36131</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="b">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>52886</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>31.51</v>
-      </c>
+        <v>37844</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P9" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>003a7ec9</t>
+          <t>0d148b9c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34.28</v>
+        <v>47.14</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="E10" t="n">
-        <v>97.66</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>51949</v>
+        <v>54125</v>
       </c>
       <c r="G10" t="n">
-        <v>62089</v>
+        <v>46014</v>
       </c>
       <c r="H10" t="n">
-        <v>30451</v>
+        <v>38799</v>
       </c>
       <c r="I10" t="n">
-        <v>36016</v>
+        <v>46852</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="b">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>30451</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.96</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>105.66</v>
-      </c>
+        <v>38799</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P10" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8a527897</t>
+          <t>92427247</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>88.68000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="E11" t="n">
-        <v>49.99</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>46832</v>
+        <v>60231</v>
       </c>
       <c r="G11" t="n">
-        <v>46776</v>
+        <v>42677</v>
       </c>
       <c r="H11" t="n">
-        <v>59292</v>
+        <v>65003</v>
       </c>
       <c r="I11" t="n">
-        <v>55669</v>
+        <v>72126</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="b">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>46776</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>61.99</v>
-      </c>
+        <v>42677</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P11" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>60c00cf5</t>
+          <t>47244eea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82.16</v>
+        <v>96.78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="E12" t="n">
-        <v>26.09</v>
+        <v>24.33</v>
       </c>
       <c r="F12" t="n">
-        <v>33398</v>
+        <v>60563</v>
       </c>
       <c r="G12" t="n">
-        <v>50025</v>
+        <v>70675</v>
       </c>
       <c r="H12" t="n">
-        <v>72732</v>
+        <v>72075</v>
       </c>
       <c r="I12" t="n">
-        <v>39560</v>
+        <v>64513</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="b">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>33398</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.88</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>31.09</v>
-      </c>
+        <v>60563</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ea63d095</t>
+          <t>4920180a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>70.8</v>
+        <v>61.18</v>
       </c>
       <c r="D13" t="n">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>78.91</v>
+        <v>98.53</v>
       </c>
       <c r="F13" t="n">
-        <v>55831</v>
+        <v>56015</v>
       </c>
       <c r="G13" t="n">
-        <v>77371</v>
+        <v>38972</v>
       </c>
       <c r="H13" t="n">
-        <v>62427</v>
+        <v>74735</v>
       </c>
       <c r="I13" t="n">
-        <v>25448</v>
+        <v>13974</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="b">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>55831</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>86.91</v>
-      </c>
+        <v>38972</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>112.53</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b948bff8</t>
+          <t>9630b49d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>92.75</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>307</v>
+        <v>186</v>
       </c>
       <c r="E14" t="n">
-        <v>32.89</v>
+        <v>50.87</v>
       </c>
       <c r="F14" t="n">
-        <v>33177</v>
+        <v>61663</v>
       </c>
       <c r="G14" t="n">
-        <v>69925</v>
+        <v>59993</v>
       </c>
       <c r="H14" t="n">
-        <v>60105</v>
+        <v>65644</v>
       </c>
       <c r="I14" t="n">
-        <v>72481</v>
+        <v>16502</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="b">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>33177</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.74</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>37.89</v>
-      </c>
+        <v>59993</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P14" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d7f68627</t>
+          <t>608eaf6b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>77.97</v>
+        <v>36.72</v>
       </c>
       <c r="D15" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="E15" t="n">
-        <v>86.48</v>
+        <v>74.88</v>
       </c>
       <c r="F15" t="n">
-        <v>40872</v>
+        <v>32778</v>
       </c>
       <c r="G15" t="n">
-        <v>77614</v>
+        <v>43973</v>
       </c>
       <c r="H15" t="n">
-        <v>35165</v>
+        <v>54296</v>
       </c>
       <c r="I15" t="n">
-        <v>34387</v>
+        <v>36856</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="b">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>35165</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.78</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>93.48</v>
-      </c>
+        <v>32778</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P15" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cfcd4923</t>
+          <t>6a144c58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49.92</v>
+        <v>92.31</v>
       </c>
       <c r="D16" t="n">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c r="E16" t="n">
-        <v>30.91</v>
+        <v>73.56</v>
       </c>
       <c r="F16" t="n">
-        <v>52626</v>
+        <v>34252</v>
       </c>
       <c r="G16" t="n">
-        <v>32055</v>
+        <v>40976</v>
       </c>
       <c r="H16" t="n">
-        <v>48088</v>
+        <v>42283</v>
       </c>
       <c r="I16" t="n">
-        <v>15813</v>
+        <v>56682</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="b">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>32055</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.83</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>36.91</v>
-      </c>
+        <v>34252</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P16" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6fe3017e</t>
+          <t>2089e966</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75.40000000000001</v>
+        <v>32.29</v>
       </c>
       <c r="D17" t="n">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="E17" t="n">
-        <v>41.73</v>
+        <v>40.94</v>
       </c>
       <c r="F17" t="n">
-        <v>47944</v>
+        <v>74740</v>
       </c>
       <c r="G17" t="n">
-        <v>64862</v>
+        <v>43651</v>
       </c>
       <c r="H17" t="n">
-        <v>63731</v>
+        <v>65068</v>
       </c>
       <c r="I17" t="n">
-        <v>14724</v>
+        <v>51739</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="b">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>47944</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>47.73</v>
-      </c>
+        <v>43651</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P17" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>73a8486a</t>
+          <t>122889b4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>42.27</v>
+        <v>65.77</v>
       </c>
       <c r="D18" t="n">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="E18" t="n">
-        <v>79.67</v>
+        <v>64.11</v>
       </c>
       <c r="F18" t="n">
-        <v>51422</v>
+        <v>65948</v>
       </c>
       <c r="G18" t="n">
-        <v>77024</v>
+        <v>77965</v>
       </c>
       <c r="H18" t="n">
-        <v>45403</v>
+        <v>71390</v>
       </c>
       <c r="I18" t="n">
-        <v>11292</v>
+        <v>76080</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="b">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>45403</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.77</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>82.67</v>
-      </c>
+        <v>65948</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P18" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>92a35cdb</t>
+          <t>ee43da8b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37.97</v>
+        <v>99.19</v>
       </c>
       <c r="D19" t="n">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="E19" t="n">
-        <v>31.59</v>
+        <v>47.08</v>
       </c>
       <c r="F19" t="n">
-        <v>57560</v>
+        <v>73197</v>
       </c>
       <c r="G19" t="n">
-        <v>72830</v>
+        <v>61108</v>
       </c>
       <c r="H19" t="n">
-        <v>65695</v>
+        <v>37646</v>
       </c>
       <c r="I19" t="n">
-        <v>60432</v>
+        <v>56038</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="b">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>57560</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>40.59</v>
-      </c>
+        <v>37646</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P19" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e5b53f3c</t>
+          <t>83bc6045</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86.7</v>
+        <v>36.14</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="E20" t="n">
-        <v>95.2</v>
+        <v>84.45</v>
       </c>
       <c r="F20" t="n">
-        <v>65176</v>
+        <v>54567</v>
       </c>
       <c r="G20" t="n">
-        <v>47720</v>
+        <v>47186</v>
       </c>
       <c r="H20" t="n">
-        <v>38556</v>
+        <v>41027</v>
       </c>
       <c r="I20" t="n">
-        <v>54692</v>
+        <v>54114</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="b">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>38556</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>107.2</v>
-      </c>
+        <v>41027</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P20" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1c8a30d1</t>
+          <t>580f5766</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84.52</v>
+        <v>63.57</v>
       </c>
       <c r="D21" t="n">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="E21" t="n">
-        <v>29.13</v>
+        <v>18.35</v>
       </c>
       <c r="F21" t="n">
-        <v>52907</v>
+        <v>34044</v>
       </c>
       <c r="G21" t="n">
-        <v>42011</v>
+        <v>53848</v>
       </c>
       <c r="H21" t="n">
-        <v>70601</v>
+        <v>47712</v>
       </c>
       <c r="I21" t="n">
-        <v>64525</v>
+        <v>15539</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="b">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>42011</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>36.13</v>
-      </c>
+        <v>34044</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b87f1f99</t>
+          <t>05cef934</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32.48</v>
+        <v>71.23</v>
       </c>
       <c r="D22" t="n">
-        <v>161</v>
+        <v>343</v>
       </c>
       <c r="E22" t="n">
-        <v>52.33</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>63372</v>
+        <v>49194</v>
       </c>
       <c r="G22" t="n">
-        <v>76459</v>
+        <v>48537</v>
       </c>
       <c r="H22" t="n">
-        <v>47154</v>
+        <v>62127</v>
       </c>
       <c r="I22" t="n">
-        <v>49388</v>
+        <v>38032</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="b">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>47154</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.68</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>62.33</v>
-      </c>
+        <v>48537</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P22" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>da94476a</t>
+          <t>272df581</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samsung Edge 40</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>78.97</v>
+        <v>37.49</v>
       </c>
       <c r="D23" t="n">
-        <v>379</v>
+        <v>214</v>
       </c>
       <c r="E23" t="n">
-        <v>64.56</v>
+        <v>72.47</v>
       </c>
       <c r="F23" t="n">
-        <v>55830</v>
+        <v>42149</v>
       </c>
       <c r="G23" t="n">
-        <v>55220</v>
+        <v>55201</v>
       </c>
       <c r="H23" t="n">
-        <v>74173</v>
+        <v>70770</v>
       </c>
       <c r="I23" t="n">
-        <v>49406</v>
+        <v>39717</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="b">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>55220</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>77.56</v>
-      </c>
+        <v>42149</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a23e4600</t>
+          <t>67f406d2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35.07</v>
+        <v>80.17</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>471</v>
       </c>
       <c r="E24" t="n">
-        <v>57.82</v>
+        <v>97.53</v>
       </c>
       <c r="F24" t="n">
-        <v>65405</v>
+        <v>52023</v>
       </c>
       <c r="G24" t="n">
-        <v>43055</v>
+        <v>64691</v>
       </c>
       <c r="H24" t="n">
-        <v>57600</v>
+        <v>32945</v>
       </c>
       <c r="I24" t="n">
-        <v>25276</v>
+        <v>68231</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="b">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>43055</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.83</v>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>66.81999999999999</v>
-      </c>
+        <v>32945</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P24" t="n">
+        <v>109.53</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>95fc5f77</t>
+          <t>a7891030</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50.58</v>
+        <v>43.43</v>
       </c>
       <c r="D25" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E25" t="n">
-        <v>28.11</v>
+        <v>17.03</v>
       </c>
       <c r="F25" t="n">
-        <v>51226</v>
+        <v>58298</v>
       </c>
       <c r="G25" t="n">
-        <v>40962</v>
+        <v>36492</v>
       </c>
       <c r="H25" t="n">
-        <v>46229</v>
+        <v>33183</v>
       </c>
       <c r="I25" t="n">
-        <v>52233</v>
+        <v>55738</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="b">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>40962</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>34.11</v>
-      </c>
+        <v>33183</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>e61a873e</t>
+          <t>43416341</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34.74</v>
+        <v>84.83</v>
       </c>
       <c r="D26" t="n">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="E26" t="n">
-        <v>31.36</v>
+        <v>34.65</v>
       </c>
       <c r="F26" t="n">
-        <v>70674</v>
+        <v>55892</v>
       </c>
       <c r="G26" t="n">
-        <v>74598</v>
+        <v>65153</v>
       </c>
       <c r="H26" t="n">
-        <v>32937</v>
+        <v>44958</v>
       </c>
       <c r="I26" t="n">
-        <v>60457</v>
+        <v>47378</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="b">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>32937</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>33.36</v>
-      </c>
+        <v>44958</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8429dec0</t>
+          <t>b11e5393</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51.68</v>
+        <v>95.28</v>
       </c>
       <c r="D27" t="n">
-        <v>489</v>
+        <v>158</v>
       </c>
       <c r="E27" t="n">
-        <v>32.63</v>
+        <v>80.09</v>
       </c>
       <c r="F27" t="n">
-        <v>58912</v>
+        <v>66588</v>
       </c>
       <c r="G27" t="n">
-        <v>78688</v>
+        <v>42585</v>
       </c>
       <c r="H27" t="n">
-        <v>31446</v>
+        <v>43429</v>
       </c>
       <c r="I27" t="n">
-        <v>50600</v>
+        <v>62721</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="b">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>31446</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>42585</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.74</v>
       </c>
-      <c r="N27" t="n">
-        <v>44.63</v>
-      </c>
+      <c r="P27" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7bc8dbb4</t>
+          <t>4d658b63</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>50.6</v>
+        <v>76.56</v>
       </c>
       <c r="D28" t="n">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="E28" t="n">
-        <v>42.31</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>33852</v>
+        <v>46940</v>
       </c>
       <c r="G28" t="n">
-        <v>38325</v>
+        <v>77110</v>
       </c>
       <c r="H28" t="n">
-        <v>54047</v>
+        <v>67071</v>
       </c>
       <c r="I28" t="n">
-        <v>27269</v>
+        <v>43943</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="b">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>33852</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>51.31</v>
-      </c>
+        <v>46940</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P28" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>39061ed6</t>
+          <t>42167913</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.84</v>
+        <v>53.27</v>
       </c>
       <c r="D29" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E29" t="n">
-        <v>29.72</v>
+        <v>46.77</v>
       </c>
       <c r="F29" t="n">
-        <v>62810</v>
+        <v>62030</v>
       </c>
       <c r="G29" t="n">
-        <v>49741</v>
+        <v>34574</v>
       </c>
       <c r="H29" t="n">
-        <v>47850</v>
+        <v>77251</v>
       </c>
       <c r="I29" t="n">
-        <v>28763</v>
+        <v>48053</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="b">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>47850</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>38.72</v>
-      </c>
+        <v>34574</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P29" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f1d0da49</t>
+          <t>dc46b7ee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49.36</v>
+        <v>40.15</v>
       </c>
       <c r="D30" t="n">
-        <v>208</v>
+        <v>306</v>
       </c>
       <c r="E30" t="n">
-        <v>56.82</v>
+        <v>21.57</v>
       </c>
       <c r="F30" t="n">
-        <v>76899</v>
+        <v>42749</v>
       </c>
       <c r="G30" t="n">
-        <v>35770</v>
+        <v>75266</v>
       </c>
       <c r="H30" t="n">
-        <v>76279</v>
+        <v>36158</v>
       </c>
       <c r="I30" t="n">
-        <v>29872</v>
+        <v>69855</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="b">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>35770</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.76</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>64.81999999999999</v>
-      </c>
+        <v>36158</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P30" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a9b7c955</t>
+          <t>e0d55c93</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>76.02</v>
+        <v>35.02</v>
       </c>
       <c r="D31" t="n">
-        <v>457</v>
+        <v>275</v>
       </c>
       <c r="E31" t="n">
-        <v>79.43000000000001</v>
+        <v>32.44</v>
       </c>
       <c r="F31" t="n">
-        <v>64336</v>
+        <v>45026</v>
       </c>
       <c r="G31" t="n">
-        <v>33990</v>
+        <v>42474</v>
       </c>
       <c r="H31" t="n">
-        <v>57143</v>
+        <v>30791</v>
       </c>
       <c r="I31" t="n">
-        <v>45330</v>
+        <v>79220</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="b">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>33990</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>93.43000000000001</v>
-      </c>
+        <v>30791</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3c7c1c80</t>
+          <t>21fd59c6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60.39</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>480</v>
+        <v>235</v>
       </c>
       <c r="E32" t="n">
-        <v>55.65</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>58084</v>
+        <v>53361</v>
       </c>
       <c r="G32" t="n">
-        <v>41789</v>
+        <v>71784</v>
       </c>
       <c r="H32" t="n">
-        <v>36976</v>
+        <v>39023</v>
       </c>
       <c r="I32" t="n">
-        <v>41378</v>
+        <v>65651</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="b">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>36976</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>63.65</v>
-      </c>
+        <v>39023</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>91469f17</t>
+          <t>6790bf84</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realme S23</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49.82</v>
+        <v>35.93</v>
       </c>
       <c r="D33" t="n">
-        <v>430</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>86.02</v>
+        <v>57.15</v>
       </c>
       <c r="F33" t="n">
-        <v>41722</v>
+        <v>77698</v>
       </c>
       <c r="G33" t="n">
-        <v>32317</v>
+        <v>76376</v>
       </c>
       <c r="H33" t="n">
-        <v>35479</v>
+        <v>75369</v>
       </c>
       <c r="I33" t="n">
-        <v>10779</v>
+        <v>12579</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="b">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>32317</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>95.02</v>
-      </c>
+        <v>75369</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P33" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>e8c1df53</t>
+          <t>bf27371d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80.84999999999999</v>
+        <v>43.77</v>
       </c>
       <c r="D34" t="n">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="E34" t="n">
-        <v>19.93</v>
+        <v>20.06</v>
       </c>
       <c r="F34" t="n">
-        <v>65530</v>
+        <v>31267</v>
       </c>
       <c r="G34" t="n">
-        <v>65901</v>
+        <v>35488</v>
       </c>
       <c r="H34" t="n">
-        <v>79557</v>
+        <v>55296</v>
       </c>
       <c r="I34" t="n">
-        <v>68735</v>
+        <v>79977</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="b">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>65530</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>31.93</v>
-      </c>
+        <v>31267</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P34" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>71cc274f</t>
+          <t>8ce8cdbb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>79.13</v>
+        <v>64.2</v>
       </c>
       <c r="D35" t="n">
-        <v>497</v>
+        <v>154</v>
       </c>
       <c r="E35" t="n">
-        <v>47.32</v>
+        <v>63.48</v>
       </c>
       <c r="F35" t="n">
-        <v>33040</v>
+        <v>77266</v>
       </c>
       <c r="G35" t="n">
-        <v>37233</v>
+        <v>37438</v>
       </c>
       <c r="H35" t="n">
-        <v>67615</v>
+        <v>65638</v>
       </c>
       <c r="I35" t="n">
-        <v>22983</v>
+        <v>68841</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="b">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>33040</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>49.32</v>
-      </c>
+        <v>37438</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P35" t="n">
+        <v>71.47999999999999</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>e044d4e9</t>
+          <t>956465a8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>70.09999999999999</v>
+        <v>63.67</v>
       </c>
       <c r="D36" t="n">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E36" t="n">
-        <v>77.94</v>
+        <v>90.14</v>
       </c>
       <c r="F36" t="n">
-        <v>56127</v>
+        <v>47935</v>
       </c>
       <c r="G36" t="n">
-        <v>41188</v>
+        <v>70543</v>
       </c>
       <c r="H36" t="n">
-        <v>65278</v>
+        <v>79998</v>
       </c>
       <c r="I36" t="n">
-        <v>45403</v>
+        <v>39349</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="b">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>41188</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>91.94</v>
-      </c>
+        <v>47935</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>90dc2f50</t>
+          <t>4768154e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.95</v>
+        <v>99.03</v>
       </c>
       <c r="D37" t="n">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="E37" t="n">
-        <v>25.97</v>
+        <v>15.58</v>
       </c>
       <c r="F37" t="n">
-        <v>50687</v>
+        <v>51203</v>
       </c>
       <c r="G37" t="n">
-        <v>42110</v>
+        <v>32836</v>
       </c>
       <c r="H37" t="n">
-        <v>69905</v>
+        <v>62545</v>
       </c>
       <c r="I37" t="n">
-        <v>33880</v>
+        <v>49317</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="b">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>42110</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>29.97</v>
-      </c>
+        <v>32836</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="P37" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34c2464f</t>
+          <t>d30b4d29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>66.23</v>
+        <v>61.1</v>
       </c>
       <c r="D38" t="n">
-        <v>383</v>
+        <v>219</v>
       </c>
       <c r="E38" t="n">
-        <v>39.85</v>
+        <v>33.2</v>
       </c>
       <c r="F38" t="n">
-        <v>30480</v>
+        <v>68276</v>
       </c>
       <c r="G38" t="n">
-        <v>54040</v>
+        <v>62631</v>
       </c>
       <c r="H38" t="n">
-        <v>76682</v>
+        <v>72394</v>
       </c>
       <c r="I38" t="n">
-        <v>13803</v>
+        <v>17333</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="b">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>30480</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.87</v>
-      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>47.85</v>
-      </c>
+        <v>62631</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3599d6c2</t>
+          <t>7c9f8d33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>63.17</v>
+        <v>41.11</v>
       </c>
       <c r="D39" t="n">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="E39" t="n">
-        <v>54.35</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>35017</v>
+        <v>43787</v>
       </c>
       <c r="G39" t="n">
-        <v>30487</v>
+        <v>63306</v>
       </c>
       <c r="H39" t="n">
-        <v>39901</v>
+        <v>65606</v>
       </c>
       <c r="I39" t="n">
-        <v>37210</v>
+        <v>53923</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="b">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>30487</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>59.35</v>
-      </c>
+        <v>43787</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P39" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>acadf05c</t>
+          <t>fc8a2f19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>63.23</v>
+        <v>81.95</v>
       </c>
       <c r="D40" t="n">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="E40" t="n">
-        <v>94.72</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>50782</v>
+        <v>45649</v>
       </c>
       <c r="G40" t="n">
-        <v>50200</v>
+        <v>38270</v>
       </c>
       <c r="H40" t="n">
-        <v>64473</v>
+        <v>74780</v>
       </c>
       <c r="I40" t="n">
-        <v>26156</v>
+        <v>23606</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="b">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>50200</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>108.72</v>
-      </c>
+        <v>38270</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P40" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>020e988c</t>
+          <t>9e6455ac</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>64.05</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>492</v>
+        <v>155</v>
       </c>
       <c r="E41" t="n">
-        <v>86.27</v>
+        <v>17.36</v>
       </c>
       <c r="F41" t="n">
-        <v>75766</v>
+        <v>40166</v>
       </c>
       <c r="G41" t="n">
-        <v>55877</v>
+        <v>39441</v>
       </c>
       <c r="H41" t="n">
-        <v>31100</v>
+        <v>60810</v>
       </c>
       <c r="I41" t="n">
-        <v>67693</v>
+        <v>77666</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="b">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>31100</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.68</v>
-      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>94.27</v>
-      </c>
+        <v>39441</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P41" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09684dae</t>
+          <t>05ca374a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>36.5</v>
+        <v>63.97</v>
       </c>
       <c r="D42" t="n">
-        <v>86</v>
+        <v>250</v>
       </c>
       <c r="E42" t="n">
-        <v>78.52</v>
+        <v>53.14</v>
       </c>
       <c r="F42" t="n">
-        <v>31419</v>
+        <v>60278</v>
       </c>
       <c r="G42" t="n">
-        <v>65935</v>
+        <v>78932</v>
       </c>
       <c r="H42" t="n">
-        <v>78883</v>
+        <v>39138</v>
       </c>
       <c r="I42" t="n">
-        <v>54661</v>
+        <v>61792</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="b">
         <v>0</v>
       </c>
-      <c r="L42" t="n">
-        <v>31419</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>88.52</v>
-      </c>
+        <v>39138</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P42" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>b57058ae</t>
+          <t>8277805e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>82.18000000000001</v>
+        <v>86.17</v>
       </c>
       <c r="D43" t="n">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="E43" t="n">
-        <v>50.16</v>
+        <v>65.11</v>
       </c>
       <c r="F43" t="n">
-        <v>43725</v>
+        <v>67711</v>
       </c>
       <c r="G43" t="n">
-        <v>49942</v>
+        <v>74078</v>
       </c>
       <c r="H43" t="n">
-        <v>59705</v>
+        <v>55999</v>
       </c>
       <c r="I43" t="n">
-        <v>73756</v>
+        <v>11531</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="b">
         <v>0</v>
       </c>
-      <c r="L43" t="n">
-        <v>43725</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>61.16</v>
-      </c>
+        <v>55999</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P43" t="n">
+        <v>78.11</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5823c0ff</t>
+          <t>3f3489dd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>81.06999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="D44" t="n">
-        <v>316</v>
+        <v>457</v>
       </c>
       <c r="E44" t="n">
-        <v>97.27</v>
+        <v>15.14</v>
       </c>
       <c r="F44" t="n">
-        <v>79365</v>
+        <v>39989</v>
       </c>
       <c r="G44" t="n">
-        <v>58789</v>
+        <v>68624</v>
       </c>
       <c r="H44" t="n">
-        <v>64166</v>
+        <v>79077</v>
       </c>
       <c r="I44" t="n">
-        <v>42413</v>
+        <v>51766</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="b">
         <v>0</v>
       </c>
-      <c r="L44" t="n">
-        <v>58789</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.88</v>
-      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>101.27</v>
-      </c>
+        <v>39989</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="P44" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>87987d84</t>
+          <t>07af0141</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>91.5</v>
+        <v>74.97</v>
       </c>
       <c r="D45" t="n">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="E45" t="n">
-        <v>96.86</v>
+        <v>97.45</v>
       </c>
       <c r="F45" t="n">
-        <v>40131</v>
+        <v>31229</v>
       </c>
       <c r="G45" t="n">
-        <v>33363</v>
+        <v>62541</v>
       </c>
       <c r="H45" t="n">
-        <v>63389</v>
+        <v>66113</v>
       </c>
       <c r="I45" t="n">
-        <v>22175</v>
+        <v>59723</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="b">
         <v>0</v>
       </c>
-      <c r="L45" t="n">
-        <v>33363</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.86</v>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>106.86</v>
-      </c>
+        <v>31229</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P45" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0711e804</t>
+          <t>ace46e79</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50.21</v>
+        <v>80.53</v>
       </c>
       <c r="D46" t="n">
-        <v>92</v>
+        <v>329</v>
       </c>
       <c r="E46" t="n">
-        <v>63.62</v>
+        <v>69.97</v>
       </c>
       <c r="F46" t="n">
-        <v>77429</v>
+        <v>79631</v>
       </c>
       <c r="G46" t="n">
-        <v>69682</v>
+        <v>72686</v>
       </c>
       <c r="H46" t="n">
-        <v>76887</v>
+        <v>58125</v>
       </c>
       <c r="I46" t="n">
-        <v>18502</v>
+        <v>24953</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="b">
         <v>0</v>
       </c>
-      <c r="L46" t="n">
-        <v>69682</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>66.62</v>
-      </c>
+        <v>58125</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P46" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>de439a54</t>
+          <t>fb0bfee4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64.41</v>
+        <v>42.43</v>
       </c>
       <c r="D47" t="n">
-        <v>413</v>
+        <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>51.41</v>
+        <v>60.13</v>
       </c>
       <c r="F47" t="n">
-        <v>36450</v>
+        <v>71124</v>
       </c>
       <c r="G47" t="n">
-        <v>51425</v>
+        <v>47982</v>
       </c>
       <c r="H47" t="n">
-        <v>38062</v>
+        <v>48327</v>
       </c>
       <c r="I47" t="n">
-        <v>9623</v>
+        <v>14635</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="b">
         <v>0</v>
       </c>
-      <c r="L47" t="n">
-        <v>36450</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>65.41</v>
-      </c>
+        <v>47982</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P47" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>be3e646b</t>
+          <t>468cef30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>49.01</v>
+        <v>54.14</v>
       </c>
       <c r="D48" t="n">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="E48" t="n">
-        <v>19</v>
+        <v>31.55</v>
       </c>
       <c r="F48" t="n">
-        <v>60572</v>
+        <v>51774</v>
       </c>
       <c r="G48" t="n">
-        <v>44072</v>
+        <v>54241</v>
       </c>
       <c r="H48" t="n">
-        <v>75444</v>
+        <v>51769</v>
       </c>
       <c r="I48" t="n">
-        <v>14456</v>
+        <v>21892</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="b">
         <v>0</v>
       </c>
-      <c r="L48" t="n">
-        <v>44072</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>27</v>
-      </c>
+        <v>51769</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P48" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b56e8baa</t>
+          <t>5da75c29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>38.28</v>
+        <v>63.5</v>
       </c>
       <c r="D49" t="n">
-        <v>150</v>
+        <v>451</v>
       </c>
       <c r="E49" t="n">
-        <v>35.58</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>43780</v>
+        <v>75844</v>
       </c>
       <c r="G49" t="n">
-        <v>43359</v>
+        <v>58178</v>
       </c>
       <c r="H49" t="n">
-        <v>43489</v>
+        <v>30523</v>
       </c>
       <c r="I49" t="n">
-        <v>31090</v>
+        <v>27589</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="b">
         <v>0</v>
       </c>
-      <c r="L49" t="n">
-        <v>43359</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.83</v>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>49.58</v>
-      </c>
+        <v>30523</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P49" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>91b5c305</t>
+          <t>a33cf3b9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>46.78</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>230</v>
+        <v>456</v>
       </c>
       <c r="E50" t="n">
-        <v>43.8</v>
+        <v>24.83</v>
       </c>
       <c r="F50" t="n">
-        <v>55763</v>
+        <v>30088</v>
       </c>
       <c r="G50" t="n">
-        <v>40708</v>
+        <v>56688</v>
       </c>
       <c r="H50" t="n">
-        <v>44694</v>
+        <v>40805</v>
       </c>
       <c r="I50" t="n">
-        <v>55454</v>
+        <v>47546</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="b">
         <v>0</v>
       </c>
-      <c r="L50" t="n">
-        <v>40708</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.87</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>47.8</v>
-      </c>
+        <v>30088</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P50" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b79f78d1</t>
+          <t>5c4fb45c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>36.79</v>
+        <v>53.85</v>
       </c>
       <c r="D51" t="n">
-        <v>351</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>19.05</v>
+        <v>16.39</v>
       </c>
       <c r="F51" t="n">
-        <v>34185</v>
+        <v>63164</v>
       </c>
       <c r="G51" t="n">
-        <v>38310</v>
+        <v>37819</v>
       </c>
       <c r="H51" t="n">
-        <v>32953</v>
+        <v>75647</v>
       </c>
       <c r="I51" t="n">
-        <v>43695</v>
+        <v>58166</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="b">
         <v>0</v>
       </c>
-      <c r="L51" t="n">
-        <v>32953</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>28.05</v>
-      </c>
+        <v>37819</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P51" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>d6c31210</t>
+          <t>84ea0013</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>78.38</v>
+        <v>53.87</v>
       </c>
       <c r="D52" t="n">
-        <v>446</v>
+        <v>98</v>
       </c>
       <c r="E52" t="n">
-        <v>81.78</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>38427</v>
+        <v>53564</v>
       </c>
       <c r="G52" t="n">
-        <v>35702</v>
+        <v>76563</v>
       </c>
       <c r="H52" t="n">
-        <v>79219</v>
+        <v>49437</v>
       </c>
       <c r="I52" t="n">
-        <v>58914</v>
+        <v>23019</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="b">
         <v>0</v>
       </c>
-      <c r="L52" t="n">
-        <v>35702</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.78</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>83.78</v>
-      </c>
+        <v>49437</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P52" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07f3b089</t>
+          <t>2310e16b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>35.3</v>
+        <v>68.88</v>
       </c>
       <c r="D53" t="n">
-        <v>433</v>
+        <v>87</v>
       </c>
       <c r="E53" t="n">
-        <v>42.94</v>
+        <v>86.53</v>
       </c>
       <c r="F53" t="n">
-        <v>45705</v>
+        <v>31257</v>
       </c>
       <c r="G53" t="n">
-        <v>77821</v>
+        <v>48302</v>
       </c>
       <c r="H53" t="n">
-        <v>70552</v>
+        <v>74472</v>
       </c>
       <c r="I53" t="n">
-        <v>68286</v>
+        <v>28839</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="b">
         <v>0</v>
       </c>
-      <c r="L53" t="n">
-        <v>45705</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>44.94</v>
-      </c>
+        <v>31257</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P53" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b5743873</t>
+          <t>53f893e9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>76.93000000000001</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>65.84</v>
+        <v>21.9</v>
       </c>
       <c r="F54" t="n">
-        <v>60024</v>
+        <v>72512</v>
       </c>
       <c r="G54" t="n">
-        <v>75678</v>
+        <v>48763</v>
       </c>
       <c r="H54" t="n">
-        <v>35655</v>
+        <v>31431</v>
       </c>
       <c r="I54" t="n">
-        <v>34428</v>
+        <v>33065</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="b">
         <v>0</v>
       </c>
-      <c r="L54" t="n">
-        <v>35655</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>68.84</v>
-      </c>
+        <v>31431</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P54" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0af96038</t>
+          <t>a9a053f9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53.18</v>
+        <v>72.83</v>
       </c>
       <c r="D55" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E55" t="n">
-        <v>36.42</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>60302</v>
+        <v>66440</v>
       </c>
       <c r="G55" t="n">
-        <v>33216</v>
+        <v>32471</v>
       </c>
       <c r="H55" t="n">
-        <v>32805</v>
+        <v>45991</v>
       </c>
       <c r="I55" t="n">
-        <v>40951</v>
+        <v>54544</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="b">
         <v>0</v>
       </c>
-      <c r="L55" t="n">
-        <v>32805</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.74</v>
-      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>50.42</v>
-      </c>
+        <v>32471</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P55" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7ea6ee43</t>
+          <t>f37819e2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>70.63</v>
+        <v>44.39</v>
       </c>
       <c r="D56" t="n">
-        <v>471</v>
+        <v>111</v>
       </c>
       <c r="E56" t="n">
-        <v>89.26000000000001</v>
+        <v>30.7</v>
       </c>
       <c r="F56" t="n">
-        <v>37592</v>
+        <v>47525</v>
       </c>
       <c r="G56" t="n">
-        <v>32341</v>
+        <v>57025</v>
       </c>
       <c r="H56" t="n">
-        <v>36472</v>
+        <v>59225</v>
       </c>
       <c r="I56" t="n">
-        <v>41291</v>
+        <v>47759</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="b">
         <v>0</v>
       </c>
-      <c r="L56" t="n">
-        <v>32341</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>92.26000000000001</v>
-      </c>
+        <v>47525</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P56" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>b904a679</t>
+          <t>e41c4a4d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.08</v>
+        <v>44.24</v>
       </c>
       <c r="D57" t="n">
-        <v>441</v>
+        <v>209</v>
       </c>
       <c r="E57" t="n">
-        <v>12.87</v>
+        <v>26.6</v>
       </c>
       <c r="F57" t="n">
-        <v>30647</v>
+        <v>44319</v>
       </c>
       <c r="G57" t="n">
-        <v>50341</v>
+        <v>39193</v>
       </c>
       <c r="H57" t="n">
-        <v>41383</v>
+        <v>55414</v>
       </c>
       <c r="I57" t="n">
-        <v>60004</v>
+        <v>69404</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="b">
         <v>0</v>
       </c>
-      <c r="L57" t="n">
-        <v>30647</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.96</v>
-      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>15.87</v>
-      </c>
+        <v>39193</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P57" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>53385d0b</t>
+          <t>1b47e196</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>92.18000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="D58" t="n">
-        <v>210</v>
+        <v>432</v>
       </c>
       <c r="E58" t="n">
-        <v>46.73</v>
+        <v>62.75</v>
       </c>
       <c r="F58" t="n">
-        <v>39733</v>
+        <v>50330</v>
       </c>
       <c r="G58" t="n">
-        <v>36418</v>
+        <v>76448</v>
       </c>
       <c r="H58" t="n">
-        <v>33240</v>
+        <v>67409</v>
       </c>
       <c r="I58" t="n">
-        <v>19544</v>
+        <v>8011</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="b">
         <v>0</v>
       </c>
-      <c r="L58" t="n">
-        <v>33240</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>50.73</v>
-      </c>
+        <v>50330</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P58" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1d8579ae</t>
+          <t>764b3bb8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>70.16</v>
+        <v>48.08</v>
       </c>
       <c r="D59" t="n">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="E59" t="n">
-        <v>41.04</v>
+        <v>23.31</v>
       </c>
       <c r="F59" t="n">
-        <v>42591</v>
+        <v>46035</v>
       </c>
       <c r="G59" t="n">
-        <v>48686</v>
+        <v>54756</v>
       </c>
       <c r="H59" t="n">
-        <v>43343</v>
+        <v>59854</v>
       </c>
       <c r="I59" t="n">
-        <v>51211</v>
+        <v>44516</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="b">
         <v>0</v>
       </c>
-      <c r="L59" t="n">
-        <v>42591</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.86</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>43.04</v>
-      </c>
+        <v>46035</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P59" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>89d1f3e2</t>
+          <t>635b2bf0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>52.76</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>69.09999999999999</v>
+        <v>91.09</v>
       </c>
       <c r="F60" t="n">
-        <v>50748</v>
+        <v>37640</v>
       </c>
       <c r="G60" t="n">
-        <v>79158</v>
+        <v>30455</v>
       </c>
       <c r="H60" t="n">
-        <v>55607</v>
+        <v>41499</v>
       </c>
       <c r="I60" t="n">
-        <v>9953</v>
+        <v>41257</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="b">
         <v>0</v>
       </c>
-      <c r="L60" t="n">
-        <v>50748</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>30455</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P60" t="n">
+        <v>105.09</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>b7de388f</t>
+          <t>c8cecafd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>41.69</v>
+        <v>67.97</v>
       </c>
       <c r="D61" t="n">
-        <v>169</v>
+        <v>354</v>
       </c>
       <c r="E61" t="n">
-        <v>62.34</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>61663</v>
+        <v>33766</v>
       </c>
       <c r="G61" t="n">
-        <v>42347</v>
+        <v>70950</v>
       </c>
       <c r="H61" t="n">
-        <v>42578</v>
+        <v>52972</v>
       </c>
       <c r="I61" t="n">
-        <v>73048</v>
+        <v>30516</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="b">
         <v>0</v>
       </c>
-      <c r="L61" t="n">
-        <v>42347</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>74.34</v>
-      </c>
+        <v>33766</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P61" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>53f7f8de</t>
+          <t>180bd4f9</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>86.3</v>
+        <v>46.87</v>
       </c>
       <c r="D62" t="n">
-        <v>12</v>
+        <v>419</v>
       </c>
       <c r="E62" t="n">
-        <v>57.78</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>34298</v>
+        <v>56069</v>
       </c>
       <c r="G62" t="n">
-        <v>30514</v>
+        <v>61976</v>
       </c>
       <c r="H62" t="n">
-        <v>78917</v>
+        <v>36616</v>
       </c>
       <c r="I62" t="n">
-        <v>44885</v>
+        <v>27048</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="b">
         <v>0</v>
       </c>
-      <c r="L62" t="n">
-        <v>30514</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>59.78</v>
-      </c>
+        <v>36616</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P62" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27fa9faf</t>
+          <t>1c5db80c</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>46.63</v>
+        <v>44.63</v>
       </c>
       <c r="D63" t="n">
-        <v>383</v>
+        <v>257</v>
       </c>
       <c r="E63" t="n">
-        <v>73.18000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="F63" t="n">
-        <v>56238</v>
+        <v>45447</v>
       </c>
       <c r="G63" t="n">
-        <v>61030</v>
+        <v>38893</v>
       </c>
       <c r="H63" t="n">
-        <v>69125</v>
+        <v>50192</v>
       </c>
       <c r="I63" t="n">
-        <v>47262</v>
+        <v>67393</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="b">
         <v>0</v>
       </c>
-      <c r="L63" t="n">
-        <v>56238</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.86</v>
-      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>80.18000000000001</v>
-      </c>
+        <v>38893</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P63" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>efc4251e</t>
+          <t>95ec47a5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>95.18000000000001</v>
+        <v>40.97</v>
       </c>
       <c r="D64" t="n">
-        <v>358</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
-        <v>41.94</v>
+        <v>10.83</v>
       </c>
       <c r="F64" t="n">
-        <v>62766</v>
+        <v>38428</v>
       </c>
       <c r="G64" t="n">
-        <v>58336</v>
+        <v>75216</v>
       </c>
       <c r="H64" t="n">
-        <v>30449</v>
+        <v>66509</v>
       </c>
       <c r="I64" t="n">
-        <v>18857</v>
+        <v>32672</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="b">
         <v>0</v>
       </c>
-      <c r="L64" t="n">
-        <v>30449</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>46.94</v>
-      </c>
+        <v>38428</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P64" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>b9c142b3</t>
+          <t>8f7c1dd4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>35.22</v>
+        <v>59.99</v>
       </c>
       <c r="D65" t="n">
-        <v>321</v>
+        <v>184</v>
       </c>
       <c r="E65" t="n">
-        <v>57.62</v>
+        <v>41.06</v>
       </c>
       <c r="F65" t="n">
-        <v>31031</v>
+        <v>77811</v>
       </c>
       <c r="G65" t="n">
-        <v>64023</v>
+        <v>46560</v>
       </c>
       <c r="H65" t="n">
-        <v>52534</v>
+        <v>42843</v>
       </c>
       <c r="I65" t="n">
-        <v>39990</v>
+        <v>40247</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="b">
         <v>0</v>
       </c>
-      <c r="L65" t="n">
-        <v>31031</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>62.62</v>
-      </c>
+        <v>42843</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P65" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>e98135e8</t>
+          <t>fafd77d8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>72.52</v>
+        <v>42.23</v>
       </c>
       <c r="D66" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="E66" t="n">
-        <v>76.39</v>
+        <v>22.05</v>
       </c>
       <c r="F66" t="n">
-        <v>45315</v>
+        <v>59678</v>
       </c>
       <c r="G66" t="n">
-        <v>43637</v>
+        <v>65937</v>
       </c>
       <c r="H66" t="n">
-        <v>74413</v>
+        <v>72555</v>
       </c>
       <c r="I66" t="n">
-        <v>35126</v>
+        <v>66099</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="b">
         <v>0</v>
       </c>
-      <c r="L66" t="n">
-        <v>43637</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>90.39</v>
-      </c>
+        <v>59678</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P66" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0f6700de</t>
+          <t>95abdde1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>86.59</v>
+        <v>66.95</v>
       </c>
       <c r="D67" t="n">
-        <v>475</v>
+        <v>146</v>
       </c>
       <c r="E67" t="n">
-        <v>43.22</v>
+        <v>29.29</v>
       </c>
       <c r="F67" t="n">
-        <v>42305</v>
+        <v>53316</v>
       </c>
       <c r="G67" t="n">
-        <v>71705</v>
+        <v>37422</v>
       </c>
       <c r="H67" t="n">
-        <v>37208</v>
+        <v>53463</v>
       </c>
       <c r="I67" t="n">
-        <v>53247</v>
+        <v>75373</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="b">
         <v>0</v>
       </c>
-      <c r="L67" t="n">
-        <v>37208</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>50.22</v>
-      </c>
+        <v>37422</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P67" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>92dea027</t>
+          <t>a9e2ec67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>30.74</v>
+        <v>72.36</v>
       </c>
       <c r="D68" t="n">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="E68" t="n">
-        <v>11.97</v>
+        <v>38.32</v>
       </c>
       <c r="F68" t="n">
-        <v>35781</v>
+        <v>45070</v>
       </c>
       <c r="G68" t="n">
-        <v>33766</v>
+        <v>64175</v>
       </c>
       <c r="H68" t="n">
-        <v>30854</v>
+        <v>79624</v>
       </c>
       <c r="I68" t="n">
-        <v>63422</v>
+        <v>37778</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="b">
         <v>0</v>
       </c>
-      <c r="L68" t="n">
-        <v>30854</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0.68</v>
-      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>23.97</v>
-      </c>
+        <v>45070</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P68" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9ac92177</t>
+          <t>2feb16eb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>32.39</v>
+        <v>48.97</v>
       </c>
       <c r="D69" t="n">
-        <v>394</v>
+        <v>153</v>
       </c>
       <c r="E69" t="n">
-        <v>72.06</v>
+        <v>53.84</v>
       </c>
       <c r="F69" t="n">
-        <v>65352</v>
+        <v>42485</v>
       </c>
       <c r="G69" t="n">
-        <v>67321</v>
+        <v>52941</v>
       </c>
       <c r="H69" t="n">
-        <v>58219</v>
+        <v>41084</v>
       </c>
       <c r="I69" t="n">
-        <v>44681</v>
+        <v>71466</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="b">
         <v>0</v>
       </c>
-      <c r="L69" t="n">
-        <v>58219</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>76.06</v>
-      </c>
+        <v>41084</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P69" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>de750f88</t>
+          <t>69166c25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>98.42</v>
+        <v>88.33</v>
       </c>
       <c r="D70" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E70" t="n">
-        <v>19.38</v>
+        <v>48.03</v>
       </c>
       <c r="F70" t="n">
-        <v>38713</v>
+        <v>44763</v>
       </c>
       <c r="G70" t="n">
-        <v>40105</v>
+        <v>49731</v>
       </c>
       <c r="H70" t="n">
-        <v>54143</v>
+        <v>54356</v>
       </c>
       <c r="I70" t="n">
-        <v>45212</v>
+        <v>61821</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="b">
         <v>0</v>
       </c>
-      <c r="L70" t="n">
-        <v>38713</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0.83</v>
-      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>33.38</v>
-      </c>
+        <v>44763</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P70" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>319f4460</t>
+          <t>2d06aba3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>47.12</v>
+        <v>96.98</v>
       </c>
       <c r="D71" t="n">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="E71" t="n">
-        <v>31.95</v>
+        <v>79.38</v>
       </c>
       <c r="F71" t="n">
-        <v>59358</v>
+        <v>67455</v>
       </c>
       <c r="G71" t="n">
-        <v>44980</v>
+        <v>70254</v>
       </c>
       <c r="H71" t="n">
-        <v>43173</v>
+        <v>54926</v>
       </c>
       <c r="I71" t="n">
-        <v>9022</v>
+        <v>28896</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="b">
         <v>0</v>
       </c>
-      <c r="L71" t="n">
-        <v>43173</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>43.95</v>
-      </c>
+        <v>54926</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P71" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>64444ab5</t>
+          <t>684aa23a</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>68.91</v>
+        <v>89.53</v>
       </c>
       <c r="D72" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E72" t="n">
-        <v>74.94</v>
+        <v>56.99</v>
       </c>
       <c r="F72" t="n">
-        <v>58779</v>
+        <v>55795</v>
       </c>
       <c r="G72" t="n">
-        <v>79789</v>
+        <v>65802</v>
       </c>
       <c r="H72" t="n">
-        <v>66738</v>
+        <v>49807</v>
       </c>
       <c r="I72" t="n">
-        <v>73496</v>
+        <v>74911</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="b">
         <v>0</v>
       </c>
-      <c r="L72" t="n">
-        <v>58779</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0.86</v>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>77.94</v>
-      </c>
+        <v>49807</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P72" t="n">
+        <v>64.99000000000001</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ed459409</t>
+          <t>eedf440d</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3778,596 +4006,635 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>98.08</v>
+        <v>36</v>
       </c>
       <c r="D73" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>77.48999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>72622</v>
+        <v>36290</v>
       </c>
       <c r="G73" t="n">
-        <v>66580</v>
+        <v>47652</v>
       </c>
       <c r="H73" t="n">
-        <v>58479</v>
+        <v>45998</v>
       </c>
       <c r="I73" t="n">
-        <v>32966</v>
+        <v>32741</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="b">
         <v>0</v>
       </c>
-      <c r="L73" t="n">
-        <v>58479</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>82.48999999999999</v>
-      </c>
+        <v>36290</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P73" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>619cf690</t>
+          <t>79a50940</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>45.39</v>
+        <v>45.77</v>
       </c>
       <c r="D74" t="n">
-        <v>415</v>
+        <v>59</v>
       </c>
       <c r="E74" t="n">
-        <v>57.65</v>
+        <v>96.53</v>
       </c>
       <c r="F74" t="n">
-        <v>69022</v>
+        <v>78204</v>
       </c>
       <c r="G74" t="n">
-        <v>66292</v>
+        <v>66334</v>
       </c>
       <c r="H74" t="n">
-        <v>66150</v>
+        <v>66959</v>
       </c>
       <c r="I74" t="n">
-        <v>66778</v>
+        <v>78881</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="b">
         <v>0</v>
       </c>
-      <c r="L74" t="n">
-        <v>66150</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
-        <v>70.65000000000001</v>
-      </c>
+        <v>66334</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P74" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ae17cec1</t>
+          <t>f8e4536e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>68.98999999999999</v>
+        <v>36.58</v>
       </c>
       <c r="D75" t="n">
-        <v>214</v>
+        <v>446</v>
       </c>
       <c r="E75" t="n">
-        <v>21.17</v>
+        <v>69.98</v>
       </c>
       <c r="F75" t="n">
-        <v>39046</v>
+        <v>40672</v>
       </c>
       <c r="G75" t="n">
-        <v>52195</v>
+        <v>44125</v>
       </c>
       <c r="H75" t="n">
-        <v>68347</v>
+        <v>77945</v>
       </c>
       <c r="I75" t="n">
-        <v>23133</v>
+        <v>63540</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="b">
         <v>0</v>
       </c>
-      <c r="L75" t="n">
-        <v>39046</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>32.17</v>
-      </c>
+        <v>40672</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P75" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>084cd858</t>
+          <t>461853d0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>45.52</v>
+        <v>36.5</v>
       </c>
       <c r="D76" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E76" t="n">
-        <v>20.19</v>
+        <v>48.11</v>
       </c>
       <c r="F76" t="n">
-        <v>68255</v>
+        <v>79159</v>
       </c>
       <c r="G76" t="n">
-        <v>47085</v>
+        <v>73205</v>
       </c>
       <c r="H76" t="n">
-        <v>42815</v>
+        <v>48258</v>
       </c>
       <c r="I76" t="n">
-        <v>61971</v>
+        <v>18288</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="b">
         <v>0</v>
       </c>
-      <c r="L76" t="n">
-        <v>42815</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>25.19</v>
-      </c>
+        <v>48258</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P76" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>182c4c29</t>
+          <t>c5dc8d0d</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>71.5</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>347</v>
+        <v>396</v>
       </c>
       <c r="E77" t="n">
-        <v>98.06</v>
+        <v>37.03</v>
       </c>
       <c r="F77" t="n">
-        <v>68154</v>
+        <v>61769</v>
       </c>
       <c r="G77" t="n">
-        <v>79335</v>
+        <v>52283</v>
       </c>
       <c r="H77" t="n">
-        <v>71541</v>
+        <v>57558</v>
       </c>
       <c r="I77" t="n">
-        <v>27026</v>
+        <v>68863</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="b">
         <v>0</v>
       </c>
-      <c r="L77" t="n">
-        <v>68154</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.74</v>
-      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>105.06</v>
-      </c>
+        <v>52283</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P77" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>e88306f1</t>
+          <t>3d7fe79a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apple Pixel 8</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>31.43</v>
+        <v>84.64</v>
       </c>
       <c r="D78" t="n">
-        <v>136</v>
+        <v>398</v>
       </c>
       <c r="E78" t="n">
-        <v>47.8</v>
+        <v>11.55</v>
       </c>
       <c r="F78" t="n">
-        <v>33186</v>
+        <v>64224</v>
       </c>
       <c r="G78" t="n">
-        <v>75345</v>
+        <v>77578</v>
       </c>
       <c r="H78" t="n">
-        <v>43620</v>
+        <v>77481</v>
       </c>
       <c r="I78" t="n">
-        <v>27965</v>
+        <v>63975</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="b">
         <v>0</v>
       </c>
-      <c r="L78" t="n">
-        <v>33186</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.76</v>
-      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>58.8</v>
-      </c>
+        <v>64224</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P78" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7246567f</t>
+          <t>21769834</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>76.14</v>
+        <v>33.97</v>
       </c>
       <c r="D79" t="n">
-        <v>396</v>
+        <v>117</v>
       </c>
       <c r="E79" t="n">
-        <v>63.63</v>
+        <v>48.38</v>
       </c>
       <c r="F79" t="n">
-        <v>53834</v>
+        <v>36956</v>
       </c>
       <c r="G79" t="n">
-        <v>38795</v>
+        <v>79395</v>
       </c>
       <c r="H79" t="n">
-        <v>53880</v>
+        <v>48959</v>
       </c>
       <c r="I79" t="n">
-        <v>56997</v>
+        <v>62419</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="b">
         <v>0</v>
       </c>
-      <c r="L79" t="n">
-        <v>38795</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>70.63</v>
-      </c>
+        <v>36956</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="P79" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>c1e62ae4</t>
+          <t>c645f96f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>97.95999999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>92</v>
+        <v>399</v>
       </c>
       <c r="E80" t="n">
-        <v>79.27</v>
+        <v>89.34</v>
       </c>
       <c r="F80" t="n">
-        <v>77341</v>
+        <v>43538</v>
       </c>
       <c r="G80" t="n">
-        <v>47265</v>
+        <v>30030</v>
       </c>
       <c r="H80" t="n">
-        <v>57173</v>
+        <v>53102</v>
       </c>
       <c r="I80" t="n">
-        <v>62315</v>
+        <v>37028</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="b">
         <v>0</v>
       </c>
-      <c r="L80" t="n">
-        <v>47265</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>86.27</v>
-      </c>
+        <v>30030</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P80" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>f88dda57</t>
+          <t>5bfcda9b</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>75.08</v>
+        <v>48.47</v>
       </c>
       <c r="D81" t="n">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="E81" t="n">
-        <v>26.21</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>59970</v>
+        <v>45007</v>
       </c>
       <c r="G81" t="n">
-        <v>38011</v>
+        <v>75036</v>
       </c>
       <c r="H81" t="n">
-        <v>64096</v>
+        <v>60751</v>
       </c>
       <c r="I81" t="n">
-        <v>74122</v>
+        <v>19313</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="b">
         <v>0</v>
       </c>
-      <c r="L81" t="n">
-        <v>38011</v>
-      </c>
-      <c r="M81" t="n">
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>45007</v>
+      </c>
+      <c r="O81" t="n">
         <v>0.7</v>
       </c>
-      <c r="N81" t="n">
-        <v>36.21</v>
-      </c>
+      <c r="P81" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a1244e89</t>
+          <t>a38eb9c0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>31.57</v>
+        <v>88.23</v>
       </c>
       <c r="D82" t="n">
-        <v>432</v>
+        <v>159</v>
       </c>
       <c r="E82" t="n">
-        <v>13.98</v>
+        <v>56.17</v>
       </c>
       <c r="F82" t="n">
-        <v>42751</v>
+        <v>59488</v>
       </c>
       <c r="G82" t="n">
-        <v>70334</v>
+        <v>46868</v>
       </c>
       <c r="H82" t="n">
-        <v>47891</v>
+        <v>77312</v>
       </c>
       <c r="I82" t="n">
-        <v>75223</v>
+        <v>40473</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="b">
         <v>0</v>
       </c>
-      <c r="L82" t="n">
-        <v>42751</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>25.98</v>
-      </c>
+        <v>46868</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="P82" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>63a99ec7</t>
+          <t>ec519824</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apple Pixel 8</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>79.53</v>
+        <v>52.39</v>
       </c>
       <c r="D83" t="n">
-        <v>321</v>
+        <v>207</v>
       </c>
       <c r="E83" t="n">
-        <v>18.8</v>
+        <v>75.12</v>
       </c>
       <c r="F83" t="n">
-        <v>62075</v>
+        <v>55913</v>
       </c>
       <c r="G83" t="n">
-        <v>39544</v>
+        <v>36281</v>
       </c>
       <c r="H83" t="n">
-        <v>42590</v>
+        <v>51259</v>
       </c>
       <c r="I83" t="n">
-        <v>8485</v>
+        <v>43358</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="b">
         <v>0</v>
       </c>
-      <c r="L83" t="n">
-        <v>39544</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0.82</v>
-      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>28.8</v>
-      </c>
+        <v>36281</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P83" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>a2b253f8</t>
+          <t>5fe95e02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>37.22</v>
+        <v>84</v>
       </c>
       <c r="D84" t="n">
-        <v>221</v>
+        <v>390</v>
       </c>
       <c r="E84" t="n">
-        <v>75.94</v>
+        <v>46.91</v>
       </c>
       <c r="F84" t="n">
-        <v>49557</v>
+        <v>31947</v>
       </c>
       <c r="G84" t="n">
-        <v>45987</v>
+        <v>66592</v>
       </c>
       <c r="H84" t="n">
-        <v>58510</v>
+        <v>34363</v>
       </c>
       <c r="I84" t="n">
-        <v>41252</v>
+        <v>55913</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="b">
         <v>0</v>
       </c>
-      <c r="L84" t="n">
-        <v>45987</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>82.94</v>
-      </c>
+        <v>31947</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P84" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ec0b621b</t>
+          <t>151b40ec</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>39.53</v>
+        <v>53.98</v>
       </c>
       <c r="D85" t="n">
-        <v>499</v>
+        <v>320</v>
       </c>
       <c r="E85" t="n">
-        <v>85.31999999999999</v>
+        <v>35.97</v>
       </c>
       <c r="F85" t="n">
-        <v>33092</v>
+        <v>63090</v>
       </c>
       <c r="G85" t="n">
-        <v>45138</v>
+        <v>59060</v>
       </c>
       <c r="H85" t="n">
-        <v>51632</v>
+        <v>79660</v>
       </c>
       <c r="I85" t="n">
-        <v>30358</v>
+        <v>25607</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="b">
         <v>0</v>
       </c>
-      <c r="L85" t="n">
-        <v>33092</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>96.31999999999999</v>
-      </c>
+        <v>59060</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P85" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9e75bab3</t>
+          <t>73fe53c4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4376,504 +4643,537 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>50.07</v>
+        <v>57.98</v>
       </c>
       <c r="D86" t="n">
-        <v>420</v>
+        <v>198</v>
       </c>
       <c r="E86" t="n">
-        <v>12.61</v>
+        <v>50.09</v>
       </c>
       <c r="F86" t="n">
-        <v>59902</v>
+        <v>49660</v>
       </c>
       <c r="G86" t="n">
-        <v>73029</v>
+        <v>64453</v>
       </c>
       <c r="H86" t="n">
-        <v>76871</v>
+        <v>73942</v>
       </c>
       <c r="I86" t="n">
-        <v>8701</v>
+        <v>55641</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="b">
         <v>0</v>
       </c>
-      <c r="L86" t="n">
-        <v>59902</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>23.61</v>
-      </c>
+        <v>49660</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P86" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9096dc09</t>
+          <t>af834edb</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>62.32</v>
+        <v>34.76</v>
       </c>
       <c r="D87" t="n">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="E87" t="n">
-        <v>41.62</v>
+        <v>21.04</v>
       </c>
       <c r="F87" t="n">
-        <v>49037</v>
+        <v>32553</v>
       </c>
       <c r="G87" t="n">
-        <v>49614</v>
+        <v>61724</v>
       </c>
       <c r="H87" t="n">
-        <v>52175</v>
+        <v>65691</v>
       </c>
       <c r="I87" t="n">
-        <v>49781</v>
+        <v>11740</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="b">
         <v>0</v>
       </c>
-      <c r="L87" t="n">
-        <v>49037</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>46.62</v>
-      </c>
+        <v>32553</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P87" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>291e7f9d</t>
+          <t>6c050a1b</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>33.5</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>374</v>
+        <v>30</v>
       </c>
       <c r="E88" t="n">
-        <v>73.43000000000001</v>
+        <v>55.94</v>
       </c>
       <c r="F88" t="n">
-        <v>68706</v>
+        <v>72408</v>
       </c>
       <c r="G88" t="n">
-        <v>63167</v>
+        <v>41133</v>
       </c>
       <c r="H88" t="n">
-        <v>53578</v>
+        <v>75678</v>
       </c>
       <c r="I88" t="n">
-        <v>47215</v>
+        <v>17189</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="b">
         <v>0</v>
       </c>
-      <c r="L88" t="n">
-        <v>53578</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
-        <v>81.43000000000001</v>
-      </c>
+        <v>41133</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P88" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>af216b1d</t>
+          <t>361613ba</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Realme S23</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>43.98</v>
+        <v>89.94</v>
       </c>
       <c r="D89" t="n">
-        <v>474</v>
+        <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>22.04</v>
+        <v>28.25</v>
       </c>
       <c r="F89" t="n">
-        <v>45168</v>
+        <v>49153</v>
       </c>
       <c r="G89" t="n">
-        <v>40641</v>
+        <v>68681</v>
       </c>
       <c r="H89" t="n">
-        <v>43683</v>
+        <v>43114</v>
       </c>
       <c r="I89" t="n">
-        <v>11283</v>
+        <v>33384</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="b">
         <v>0</v>
       </c>
-      <c r="L89" t="n">
-        <v>40641</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>36.04</v>
-      </c>
+        <v>43114</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P89" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>e5a81f3b</t>
+          <t>1d386235</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>62.41</v>
+        <v>71.89</v>
       </c>
       <c r="D90" t="n">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="E90" t="n">
-        <v>38.25</v>
+        <v>57.54</v>
       </c>
       <c r="F90" t="n">
-        <v>57420</v>
+        <v>34393</v>
       </c>
       <c r="G90" t="n">
-        <v>57030</v>
+        <v>64357</v>
       </c>
       <c r="H90" t="n">
-        <v>62602</v>
+        <v>45033</v>
       </c>
       <c r="I90" t="n">
-        <v>32072</v>
+        <v>25850</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="b">
         <v>0</v>
       </c>
-      <c r="L90" t="n">
-        <v>57030</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0.76</v>
-      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>42.25</v>
-      </c>
+        <v>34393</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P90" t="n">
+        <v>69.53999999999999</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4356b8aa</t>
+          <t>1314c433</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>86.43000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="D91" t="n">
-        <v>57</v>
+        <v>495</v>
       </c>
       <c r="E91" t="n">
-        <v>22.71</v>
+        <v>36.98</v>
       </c>
       <c r="F91" t="n">
-        <v>56591</v>
+        <v>65627</v>
       </c>
       <c r="G91" t="n">
-        <v>71231</v>
+        <v>53654</v>
       </c>
       <c r="H91" t="n">
-        <v>66499</v>
+        <v>56262</v>
       </c>
       <c r="I91" t="n">
-        <v>29783</v>
+        <v>69547</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="b">
         <v>0</v>
       </c>
-      <c r="L91" t="n">
-        <v>56591</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0.71</v>
-      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>36.71</v>
-      </c>
+        <v>53654</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P91" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>e1e400ed</t>
+          <t>a03e015f</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>76.43000000000001</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>62.62</v>
+        <v>29.99</v>
       </c>
       <c r="F92" t="n">
-        <v>41187</v>
+        <v>31660</v>
       </c>
       <c r="G92" t="n">
-        <v>55083</v>
+        <v>49335</v>
       </c>
       <c r="H92" t="n">
-        <v>43396</v>
+        <v>41933</v>
       </c>
       <c r="I92" t="n">
-        <v>29764</v>
+        <v>72600</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="b">
         <v>0</v>
       </c>
-      <c r="L92" t="n">
-        <v>41187</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0.87</v>
-      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>68.62</v>
-      </c>
+        <v>31660</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P92" t="n">
+        <v>41.98999999999999</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>21b5da15</t>
+          <t>03154642</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Xiaomi 14</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>73.86</v>
+        <v>38.84</v>
       </c>
       <c r="D93" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="E93" t="n">
-        <v>40.51</v>
+        <v>28.65</v>
       </c>
       <c r="F93" t="n">
-        <v>32121</v>
+        <v>33270</v>
       </c>
       <c r="G93" t="n">
-        <v>52948</v>
+        <v>44818</v>
       </c>
       <c r="H93" t="n">
-        <v>78282</v>
+        <v>77168</v>
       </c>
       <c r="I93" t="n">
-        <v>18908</v>
+        <v>54181</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="b">
         <v>0</v>
       </c>
-      <c r="L93" t="n">
-        <v>32121</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0.72</v>
-      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>42.51</v>
-      </c>
+        <v>33270</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P93" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8c56ee87</t>
+          <t>fae14961</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>43.77</v>
+        <v>32.81</v>
       </c>
       <c r="D94" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E94" t="n">
-        <v>25.32</v>
+        <v>76.41</v>
       </c>
       <c r="F94" t="n">
-        <v>43172</v>
+        <v>43384</v>
       </c>
       <c r="G94" t="n">
-        <v>69586</v>
+        <v>33823</v>
       </c>
       <c r="H94" t="n">
-        <v>51726</v>
+        <v>72064</v>
       </c>
       <c r="I94" t="n">
-        <v>67510</v>
+        <v>32389</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="b">
         <v>0</v>
       </c>
-      <c r="L94" t="n">
-        <v>43172</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>38.32</v>
-      </c>
+        <v>33823</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P94" t="n">
+        <v>86.41</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>43f9b473</t>
+          <t>75db501b</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>99.3</v>
+        <v>39.16</v>
       </c>
       <c r="D95" t="n">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="E95" t="n">
-        <v>97.8</v>
+        <v>55.81</v>
       </c>
       <c r="F95" t="n">
-        <v>67056</v>
+        <v>66051</v>
       </c>
       <c r="G95" t="n">
-        <v>41444</v>
+        <v>74410</v>
       </c>
       <c r="H95" t="n">
-        <v>35410</v>
+        <v>76699</v>
       </c>
       <c r="I95" t="n">
-        <v>21698</v>
+        <v>20037</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="b">
         <v>0</v>
       </c>
-      <c r="L95" t="n">
-        <v>35410</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>107.8</v>
-      </c>
+        <v>66051</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P95" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6a7e169b</t>
+          <t>9a7b9f87</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>53.44</v>
+        <v>31.62</v>
       </c>
       <c r="D96" t="n">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="E96" t="n">
-        <v>51.53</v>
+        <v>61.79</v>
       </c>
       <c r="F96" t="n">
-        <v>43618</v>
+        <v>64602</v>
       </c>
       <c r="G96" t="n">
-        <v>70437</v>
+        <v>49168</v>
       </c>
       <c r="H96" t="n">
-        <v>52752</v>
+        <v>71438</v>
       </c>
       <c r="I96" t="n">
-        <v>54117</v>
+        <v>72202</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="b">
         <v>0</v>
       </c>
-      <c r="L96" t="n">
-        <v>43618</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>58.53</v>
-      </c>
+        <v>49168</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P96" t="n">
+        <v>70.78999999999999</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dc0d950f</t>
+          <t>50b3e0d1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4882,223 +5182,238 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>62.52</v>
+        <v>66.66</v>
       </c>
       <c r="D97" t="n">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="E97" t="n">
-        <v>26.57</v>
+        <v>98.55</v>
       </c>
       <c r="F97" t="n">
-        <v>75380</v>
+        <v>59471</v>
       </c>
       <c r="G97" t="n">
-        <v>31555</v>
+        <v>67587</v>
       </c>
       <c r="H97" t="n">
-        <v>77833</v>
+        <v>30591</v>
       </c>
       <c r="I97" t="n">
-        <v>75728</v>
+        <v>12194</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="b">
         <v>0</v>
       </c>
-      <c r="L97" t="n">
-        <v>31555</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0.78</v>
-      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>32.57</v>
-      </c>
+        <v>30591</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P97" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>71343594</t>
+          <t>9498e5dc</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>95.73999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="D98" t="n">
-        <v>323</v>
+        <v>226</v>
       </c>
       <c r="E98" t="n">
-        <v>50.47</v>
+        <v>12.3</v>
       </c>
       <c r="F98" t="n">
-        <v>49905</v>
+        <v>64387</v>
       </c>
       <c r="G98" t="n">
-        <v>77125</v>
+        <v>66791</v>
       </c>
       <c r="H98" t="n">
-        <v>63790</v>
+        <v>31714</v>
       </c>
       <c r="I98" t="n">
-        <v>77202</v>
+        <v>8329</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="b">
         <v>0</v>
       </c>
-      <c r="L98" t="n">
-        <v>49905</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>52.47</v>
-      </c>
+        <v>31714</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P98" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>a08cee91</t>
+          <t>54db95c2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>73.19</v>
+        <v>44.45</v>
       </c>
       <c r="D99" t="n">
-        <v>489</v>
+        <v>323</v>
       </c>
       <c r="E99" t="n">
-        <v>68.51000000000001</v>
+        <v>28.95</v>
       </c>
       <c r="F99" t="n">
-        <v>59253</v>
+        <v>79791</v>
       </c>
       <c r="G99" t="n">
-        <v>38639</v>
+        <v>42957</v>
       </c>
       <c r="H99" t="n">
-        <v>65809</v>
+        <v>37562</v>
       </c>
       <c r="I99" t="n">
-        <v>35070</v>
+        <v>33093</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="b">
         <v>0</v>
       </c>
-      <c r="L99" t="n">
-        <v>38639</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>75.51000000000001</v>
-      </c>
+        <v>37562</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P99" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>e3217e16</t>
+          <t>2637360f</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>47.94</v>
+        <v>94.36</v>
       </c>
       <c r="D100" t="n">
-        <v>157</v>
+        <v>322</v>
       </c>
       <c r="E100" t="n">
-        <v>54.75</v>
+        <v>52.9</v>
       </c>
       <c r="F100" t="n">
-        <v>46124</v>
+        <v>55770</v>
       </c>
       <c r="G100" t="n">
-        <v>65270</v>
+        <v>69274</v>
       </c>
       <c r="H100" t="n">
-        <v>74411</v>
+        <v>34087</v>
       </c>
       <c r="I100" t="n">
-        <v>54605</v>
+        <v>30395</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="b">
         <v>0</v>
       </c>
-      <c r="L100" t="n">
-        <v>46124</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>58.75</v>
-      </c>
+        <v>34087</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="P100" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>876ecbf8</t>
+          <t>6b541560</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>62.34</v>
+        <v>35.98</v>
       </c>
       <c r="D101" t="n">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="E101" t="n">
-        <v>24.93</v>
+        <v>35.73</v>
       </c>
       <c r="F101" t="n">
-        <v>72954</v>
+        <v>52534</v>
       </c>
       <c r="G101" t="n">
-        <v>68402</v>
+        <v>66723</v>
       </c>
       <c r="H101" t="n">
-        <v>78354</v>
+        <v>76677</v>
       </c>
       <c r="I101" t="n">
-        <v>40579</v>
+        <v>45213</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="b">
         <v>0</v>
       </c>
-      <c r="L101" t="n">
-        <v>68402</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0.71</v>
-      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>37.93</v>
-      </c>
+        <v>52534</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P101" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/mock_product_data.xlsx
+++ b/data/mock_product_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,6 +511,11 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Price Gap</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Price</t>
         </is>
       </c>
@@ -518,34 +523,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0f867433</t>
+          <t>2a4d6d38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.53</v>
+        <v>78.02</v>
       </c>
       <c r="D2" t="n">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="E2" t="n">
-        <v>61.82</v>
+        <v>99.38</v>
       </c>
       <c r="F2" t="n">
-        <v>58680</v>
+        <v>49636</v>
       </c>
       <c r="G2" t="n">
-        <v>49892</v>
+        <v>53672</v>
       </c>
       <c r="H2" t="n">
-        <v>32217</v>
+        <v>67513</v>
       </c>
       <c r="I2" t="n">
-        <v>64332</v>
+        <v>51754</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
@@ -554,47 +559,50 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>32217</v>
+        <v>49636</v>
       </c>
       <c r="O2" t="n">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="P2" t="n">
-        <v>63.82</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>105.38</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2118</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>c4b79787</t>
+          <t>87164b04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.85</v>
+        <v>61.63</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
-        <v>12.35</v>
+        <v>31.06</v>
       </c>
       <c r="F3" t="n">
-        <v>48691</v>
+        <v>46194</v>
       </c>
       <c r="G3" t="n">
-        <v>32793</v>
+        <v>71762</v>
       </c>
       <c r="H3" t="n">
-        <v>74231</v>
+        <v>62344</v>
       </c>
       <c r="I3" t="n">
-        <v>63893</v>
+        <v>56354</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="b">
@@ -603,47 +611,50 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>32793</v>
+        <v>46194</v>
       </c>
       <c r="O3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P3" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>39.06</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10160</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30cd5455</t>
+          <t>d54e27e0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.09999999999999</v>
+        <v>44.23</v>
       </c>
       <c r="D4" t="n">
-        <v>214</v>
+        <v>464</v>
       </c>
       <c r="E4" t="n">
-        <v>58.43</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>59355</v>
+        <v>31223</v>
       </c>
       <c r="G4" t="n">
-        <v>31841</v>
+        <v>55195</v>
       </c>
       <c r="H4" t="n">
-        <v>79523</v>
+        <v>53248</v>
       </c>
       <c r="I4" t="n">
-        <v>27807</v>
+        <v>53363</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
@@ -652,47 +663,50 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>31841</v>
+        <v>31223</v>
       </c>
       <c r="O4" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="P4" t="n">
-        <v>72.43000000000001</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>73.31999999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22140</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ebafd7d0</t>
+          <t>b8906b65</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>93.68000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="D5" t="n">
-        <v>121</v>
+        <v>491</v>
       </c>
       <c r="E5" t="n">
-        <v>17.32</v>
+        <v>15.21</v>
       </c>
       <c r="F5" t="n">
-        <v>50792</v>
+        <v>64775</v>
       </c>
       <c r="G5" t="n">
-        <v>65587</v>
+        <v>36400</v>
       </c>
       <c r="H5" t="n">
-        <v>54637</v>
+        <v>32584</v>
       </c>
       <c r="I5" t="n">
-        <v>33812</v>
+        <v>50417</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="b">
@@ -701,47 +715,50 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>50792</v>
+        <v>32584</v>
       </c>
       <c r="O5" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="P5" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>25.21</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17833</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8416be31</t>
+          <t>d4fbc019</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.75</v>
+        <v>35.01</v>
       </c>
       <c r="D6" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E6" t="n">
-        <v>56.58</v>
+        <v>66.59</v>
       </c>
       <c r="F6" t="n">
-        <v>57318</v>
+        <v>34593</v>
       </c>
       <c r="G6" t="n">
-        <v>55539</v>
+        <v>32007</v>
       </c>
       <c r="H6" t="n">
-        <v>77568</v>
+        <v>74012</v>
       </c>
       <c r="I6" t="n">
-        <v>18490</v>
+        <v>21578</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="b">
@@ -750,47 +767,50 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>55539</v>
+        <v>32007</v>
       </c>
       <c r="O6" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="P6" t="n">
-        <v>69.58</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>72.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10429</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>53bfaa32</t>
+          <t>d18f7e8c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>87.11</v>
+        <v>89.92</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
-        <v>82.89</v>
+        <v>62.47</v>
       </c>
       <c r="F7" t="n">
-        <v>37795</v>
+        <v>63583</v>
       </c>
       <c r="G7" t="n">
-        <v>64875</v>
+        <v>68024</v>
       </c>
       <c r="H7" t="n">
-        <v>48994</v>
+        <v>74008</v>
       </c>
       <c r="I7" t="n">
-        <v>8443</v>
+        <v>29543</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="b">
@@ -799,47 +819,50 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>37795</v>
+        <v>63583</v>
       </c>
       <c r="O7" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="P7" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>75.47</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>34040</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>79b0243f</t>
+          <t>0e43364a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>98.58</v>
+        <v>34.53</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="E8" t="n">
-        <v>79.29000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="F8" t="n">
-        <v>39185</v>
+        <v>30942</v>
       </c>
       <c r="G8" t="n">
-        <v>44889</v>
+        <v>41073</v>
       </c>
       <c r="H8" t="n">
-        <v>61293</v>
+        <v>30700</v>
       </c>
       <c r="I8" t="n">
-        <v>62688</v>
+        <v>23242</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="b">
@@ -848,47 +871,50 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>39185</v>
+        <v>30700</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="P8" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>62.48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7458</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a3c9e17a</t>
+          <t>3e72c072</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.29000000000001</v>
+        <v>33.32</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>70.43000000000001</v>
+        <v>94.47</v>
       </c>
       <c r="F9" t="n">
-        <v>37844</v>
+        <v>55015</v>
       </c>
       <c r="G9" t="n">
-        <v>45868</v>
+        <v>40630</v>
       </c>
       <c r="H9" t="n">
-        <v>61346</v>
+        <v>77193</v>
       </c>
       <c r="I9" t="n">
-        <v>36131</v>
+        <v>71384</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="b">
@@ -897,47 +923,50 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>37844</v>
+        <v>40630</v>
       </c>
       <c r="O9" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="P9" t="n">
-        <v>83.43000000000001</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>104.47</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30754</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0d148b9c</t>
+          <t>194b50ce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.14</v>
+        <v>40.82</v>
       </c>
       <c r="D10" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="E10" t="n">
-        <v>94.56999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>54125</v>
+        <v>45438</v>
       </c>
       <c r="G10" t="n">
-        <v>46014</v>
+        <v>52885</v>
       </c>
       <c r="H10" t="n">
-        <v>38799</v>
+        <v>52109</v>
       </c>
       <c r="I10" t="n">
-        <v>46852</v>
+        <v>69164</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="b">
@@ -946,47 +975,50 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>38799</v>
+        <v>45438</v>
       </c>
       <c r="O10" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="P10" t="n">
-        <v>100.57</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23726</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>92427247</t>
+          <t>e9b325bf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.43000000000001</v>
+        <v>93.12</v>
       </c>
       <c r="D11" t="n">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>84.73999999999999</v>
+        <v>26.86</v>
       </c>
       <c r="F11" t="n">
-        <v>60231</v>
+        <v>67388</v>
       </c>
       <c r="G11" t="n">
-        <v>42677</v>
+        <v>63629</v>
       </c>
       <c r="H11" t="n">
-        <v>65003</v>
+        <v>44962</v>
       </c>
       <c r="I11" t="n">
-        <v>72126</v>
+        <v>15848</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="b">
@@ -995,47 +1027,50 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>42677</v>
+        <v>44962</v>
       </c>
       <c r="O11" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="P11" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>28.86</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>29114</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>47244eea</t>
+          <t>354ac8ca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96.78</v>
+        <v>44.73</v>
       </c>
       <c r="D12" t="n">
-        <v>209</v>
+        <v>363</v>
       </c>
       <c r="E12" t="n">
-        <v>24.33</v>
+        <v>74.58</v>
       </c>
       <c r="F12" t="n">
-        <v>60563</v>
+        <v>52610</v>
       </c>
       <c r="G12" t="n">
-        <v>70675</v>
+        <v>41351</v>
       </c>
       <c r="H12" t="n">
-        <v>72075</v>
+        <v>39578</v>
       </c>
       <c r="I12" t="n">
-        <v>64513</v>
+        <v>16913</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="b">
@@ -1044,47 +1079,50 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>60563</v>
+        <v>39578</v>
       </c>
       <c r="O12" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="P12" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>86.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22665</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4920180a</t>
+          <t>bbc220e4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>61.18</v>
+        <v>60.4</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="E13" t="n">
-        <v>98.53</v>
+        <v>65.91</v>
       </c>
       <c r="F13" t="n">
-        <v>56015</v>
+        <v>35997</v>
       </c>
       <c r="G13" t="n">
-        <v>38972</v>
+        <v>73550</v>
       </c>
       <c r="H13" t="n">
-        <v>74735</v>
+        <v>41729</v>
       </c>
       <c r="I13" t="n">
-        <v>13974</v>
+        <v>56486</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="b">
@@ -1093,47 +1131,50 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>38972</v>
+        <v>35997</v>
       </c>
       <c r="O13" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="P13" t="n">
-        <v>112.53</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>77.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20489</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9630b49d</t>
+          <t>b89c60f1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85.95999999999999</v>
+        <v>55.59</v>
       </c>
       <c r="D14" t="n">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>50.87</v>
+        <v>84.52</v>
       </c>
       <c r="F14" t="n">
-        <v>61663</v>
+        <v>34413</v>
       </c>
       <c r="G14" t="n">
-        <v>59993</v>
+        <v>71635</v>
       </c>
       <c r="H14" t="n">
-        <v>65644</v>
+        <v>67952</v>
       </c>
       <c r="I14" t="n">
-        <v>16502</v>
+        <v>44666</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="b">
@@ -1142,47 +1183,50 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>59993</v>
+        <v>34413</v>
       </c>
       <c r="O14" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="P14" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>89.52</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10253</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>608eaf6b</t>
+          <t>4e5e9962</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.72</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="E15" t="n">
-        <v>74.88</v>
+        <v>45.57</v>
       </c>
       <c r="F15" t="n">
-        <v>32778</v>
+        <v>47467</v>
       </c>
       <c r="G15" t="n">
-        <v>43973</v>
+        <v>78744</v>
       </c>
       <c r="H15" t="n">
-        <v>54296</v>
+        <v>35592</v>
       </c>
       <c r="I15" t="n">
-        <v>36856</v>
+        <v>47954</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="b">
@@ -1191,47 +1235,50 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>32778</v>
+        <v>35592</v>
       </c>
       <c r="O15" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="P15" t="n">
-        <v>82.88</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>53.57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12362</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6a144c58</t>
+          <t>59505669</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>92.31</v>
+        <v>32.07</v>
       </c>
       <c r="D16" t="n">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>73.56</v>
+        <v>29.69</v>
       </c>
       <c r="F16" t="n">
-        <v>34252</v>
+        <v>60186</v>
       </c>
       <c r="G16" t="n">
-        <v>40976</v>
+        <v>49872</v>
       </c>
       <c r="H16" t="n">
-        <v>42283</v>
+        <v>51539</v>
       </c>
       <c r="I16" t="n">
-        <v>56682</v>
+        <v>78762</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="b">
@@ -1240,47 +1287,50 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>34252</v>
+        <v>49872</v>
       </c>
       <c r="O16" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="P16" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>43.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>28890</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2089e966</t>
+          <t>27241491</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32.29</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E17" t="n">
-        <v>40.94</v>
+        <v>59.82</v>
       </c>
       <c r="F17" t="n">
-        <v>74740</v>
+        <v>76486</v>
       </c>
       <c r="G17" t="n">
-        <v>43651</v>
+        <v>63710</v>
       </c>
       <c r="H17" t="n">
-        <v>65068</v>
+        <v>50140</v>
       </c>
       <c r="I17" t="n">
-        <v>51739</v>
+        <v>14339</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="b">
@@ -1289,47 +1339,50 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>43651</v>
+        <v>50140</v>
       </c>
       <c r="O17" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="P17" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>70.81999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35801</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>122889b4</t>
+          <t>d8f81ff0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>65.77</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>200</v>
+        <v>433</v>
       </c>
       <c r="E18" t="n">
-        <v>64.11</v>
+        <v>20.58</v>
       </c>
       <c r="F18" t="n">
-        <v>65948</v>
+        <v>41234</v>
       </c>
       <c r="G18" t="n">
-        <v>77965</v>
+        <v>51270</v>
       </c>
       <c r="H18" t="n">
-        <v>71390</v>
+        <v>75670</v>
       </c>
       <c r="I18" t="n">
-        <v>76080</v>
+        <v>36384</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="b">
@@ -1338,47 +1391,50 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>65948</v>
+        <v>41234</v>
       </c>
       <c r="O18" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="P18" t="n">
-        <v>77.11</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>30.58</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4850</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ee43da8b</t>
+          <t>0eef2532</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>99.19</v>
+        <v>52.11</v>
       </c>
       <c r="D19" t="n">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="E19" t="n">
-        <v>47.08</v>
+        <v>66.45</v>
       </c>
       <c r="F19" t="n">
-        <v>73197</v>
+        <v>65519</v>
       </c>
       <c r="G19" t="n">
-        <v>61108</v>
+        <v>63148</v>
       </c>
       <c r="H19" t="n">
-        <v>37646</v>
+        <v>66817</v>
       </c>
       <c r="I19" t="n">
-        <v>56038</v>
+        <v>19603</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="b">
@@ -1387,47 +1443,50 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>37646</v>
+        <v>63148</v>
       </c>
       <c r="O19" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="P19" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>68.45</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>43545</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>83bc6045</t>
+          <t>23755b15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36.14</v>
+        <v>38.02</v>
       </c>
       <c r="D20" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E20" t="n">
-        <v>84.45</v>
+        <v>62.04</v>
       </c>
       <c r="F20" t="n">
-        <v>54567</v>
+        <v>58427</v>
       </c>
       <c r="G20" t="n">
-        <v>47186</v>
+        <v>32269</v>
       </c>
       <c r="H20" t="n">
-        <v>41027</v>
+        <v>33693</v>
       </c>
       <c r="I20" t="n">
-        <v>54114</v>
+        <v>12195</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="b">
@@ -1436,47 +1495,50 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>41027</v>
+        <v>32269</v>
       </c>
       <c r="O20" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="P20" t="n">
-        <v>97.45</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>70.03999999999999</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20074</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>580f5766</t>
+          <t>11788d5e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63.57</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>267</v>
+        <v>180</v>
       </c>
       <c r="E21" t="n">
-        <v>18.35</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>34044</v>
+        <v>58591</v>
       </c>
       <c r="G21" t="n">
-        <v>53848</v>
+        <v>55269</v>
       </c>
       <c r="H21" t="n">
-        <v>47712</v>
+        <v>52217</v>
       </c>
       <c r="I21" t="n">
-        <v>15539</v>
+        <v>29046</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="b">
@@ -1485,47 +1547,50 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>34044</v>
+        <v>52217</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="P21" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>99.01000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23171</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05cef934</t>
+          <t>2eb32247</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>71.23</v>
+        <v>54.94</v>
       </c>
       <c r="D22" t="n">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E22" t="n">
-        <v>89.51000000000001</v>
+        <v>99.34</v>
       </c>
       <c r="F22" t="n">
-        <v>49194</v>
+        <v>62515</v>
       </c>
       <c r="G22" t="n">
-        <v>48537</v>
+        <v>52241</v>
       </c>
       <c r="H22" t="n">
-        <v>62127</v>
+        <v>67471</v>
       </c>
       <c r="I22" t="n">
-        <v>38032</v>
+        <v>35386</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="b">
@@ -1534,47 +1599,50 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>48537</v>
+        <v>52241</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="P22" t="n">
-        <v>99.51000000000001</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>108.34</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>16855</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>272df581</t>
+          <t>e87194b0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.49</v>
+        <v>49.18</v>
       </c>
       <c r="D23" t="n">
-        <v>214</v>
+        <v>305</v>
       </c>
       <c r="E23" t="n">
-        <v>72.47</v>
+        <v>94.63</v>
       </c>
       <c r="F23" t="n">
-        <v>42149</v>
+        <v>46164</v>
       </c>
       <c r="G23" t="n">
-        <v>55201</v>
+        <v>77719</v>
       </c>
       <c r="H23" t="n">
-        <v>70770</v>
+        <v>63979</v>
       </c>
       <c r="I23" t="n">
-        <v>39717</v>
+        <v>22299</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="b">
@@ -1583,47 +1651,50 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>42149</v>
+        <v>46164</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="P23" t="n">
-        <v>85.47</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>99.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>23865</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>67f406d2</t>
+          <t>2d35206a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Xiaomi 14</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.17</v>
+        <v>96.14</v>
       </c>
       <c r="D24" t="n">
-        <v>471</v>
+        <v>184</v>
       </c>
       <c r="E24" t="n">
-        <v>97.53</v>
+        <v>24.72</v>
       </c>
       <c r="F24" t="n">
-        <v>52023</v>
+        <v>75683</v>
       </c>
       <c r="G24" t="n">
-        <v>64691</v>
+        <v>46485</v>
       </c>
       <c r="H24" t="n">
-        <v>32945</v>
+        <v>76054</v>
       </c>
       <c r="I24" t="n">
-        <v>68231</v>
+        <v>48685</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="b">
@@ -1632,47 +1703,50 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>32945</v>
+        <v>46485</v>
       </c>
       <c r="O24" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="P24" t="n">
-        <v>109.53</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>34.72</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2200</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a7891030</t>
+          <t>b0a79e0d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43.43</v>
+        <v>44.9</v>
       </c>
       <c r="D25" t="n">
-        <v>189</v>
+        <v>371</v>
       </c>
       <c r="E25" t="n">
-        <v>17.03</v>
+        <v>20.11</v>
       </c>
       <c r="F25" t="n">
-        <v>58298</v>
+        <v>30741</v>
       </c>
       <c r="G25" t="n">
-        <v>36492</v>
+        <v>63591</v>
       </c>
       <c r="H25" t="n">
-        <v>33183</v>
+        <v>39703</v>
       </c>
       <c r="I25" t="n">
-        <v>55738</v>
+        <v>34140</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="b">
@@ -1681,47 +1755,50 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>33183</v>
+        <v>30741</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>34.11</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3399</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43416341</t>
+          <t>64ac0db3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84.83</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>369</v>
+        <v>251</v>
       </c>
       <c r="E26" t="n">
-        <v>34.65</v>
+        <v>52.21</v>
       </c>
       <c r="F26" t="n">
-        <v>55892</v>
+        <v>67639</v>
       </c>
       <c r="G26" t="n">
-        <v>65153</v>
+        <v>30913</v>
       </c>
       <c r="H26" t="n">
-        <v>44958</v>
+        <v>31455</v>
       </c>
       <c r="I26" t="n">
-        <v>47378</v>
+        <v>69126</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="b">
@@ -1730,47 +1807,50 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>44958</v>
+        <v>30913</v>
       </c>
       <c r="O26" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="P26" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>55.21</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>38213</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b11e5393</t>
+          <t>d41ae22e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>95.28</v>
+        <v>30.15</v>
       </c>
       <c r="D27" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="E27" t="n">
-        <v>80.09</v>
+        <v>77.39</v>
       </c>
       <c r="F27" t="n">
-        <v>66588</v>
+        <v>52662</v>
       </c>
       <c r="G27" t="n">
-        <v>42585</v>
+        <v>69719</v>
       </c>
       <c r="H27" t="n">
-        <v>43429</v>
+        <v>57924</v>
       </c>
       <c r="I27" t="n">
-        <v>62721</v>
+        <v>29772</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="b">
@@ -1779,47 +1859,50 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>42585</v>
+        <v>52662</v>
       </c>
       <c r="O27" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="P27" t="n">
-        <v>89.09</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>86.39</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>22890</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4d658b63</t>
+          <t>8f133de7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Samsung Edge 40</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>76.56</v>
+        <v>43.22</v>
       </c>
       <c r="D28" t="n">
-        <v>375</v>
+        <v>283</v>
       </c>
       <c r="E28" t="n">
-        <v>64.65000000000001</v>
+        <v>58.59</v>
       </c>
       <c r="F28" t="n">
-        <v>46940</v>
+        <v>51378</v>
       </c>
       <c r="G28" t="n">
-        <v>77110</v>
+        <v>68673</v>
       </c>
       <c r="H28" t="n">
-        <v>67071</v>
+        <v>37072</v>
       </c>
       <c r="I28" t="n">
-        <v>43943</v>
+        <v>35445</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="b">
@@ -1828,47 +1911,50 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>46940</v>
+        <v>37072</v>
       </c>
       <c r="O28" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="P28" t="n">
-        <v>69.65000000000001</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+        <v>63.59</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1627</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42167913</t>
+          <t>4469fede</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>53.27</v>
+        <v>70.42</v>
       </c>
       <c r="D29" t="n">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="E29" t="n">
-        <v>46.77</v>
+        <v>81.58</v>
       </c>
       <c r="F29" t="n">
-        <v>62030</v>
+        <v>43681</v>
       </c>
       <c r="G29" t="n">
-        <v>34574</v>
+        <v>47151</v>
       </c>
       <c r="H29" t="n">
-        <v>77251</v>
+        <v>34567</v>
       </c>
       <c r="I29" t="n">
-        <v>48053</v>
+        <v>54499</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="b">
@@ -1877,47 +1963,50 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>34574</v>
+        <v>34567</v>
       </c>
       <c r="O29" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="P29" t="n">
-        <v>51.77</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>93.58</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>19932</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dc46b7ee</t>
+          <t>0d41975d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40.15</v>
+        <v>95.44</v>
       </c>
       <c r="D30" t="n">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="E30" t="n">
-        <v>21.57</v>
+        <v>51.88</v>
       </c>
       <c r="F30" t="n">
-        <v>42749</v>
+        <v>49739</v>
       </c>
       <c r="G30" t="n">
-        <v>75266</v>
+        <v>67521</v>
       </c>
       <c r="H30" t="n">
-        <v>36158</v>
+        <v>30783</v>
       </c>
       <c r="I30" t="n">
-        <v>69855</v>
+        <v>69831</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="b">
@@ -1926,47 +2015,50 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>36158</v>
+        <v>30783</v>
       </c>
       <c r="O30" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="P30" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>58.88</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>39048</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>e0d55c93</t>
+          <t>188ecac6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35.02</v>
+        <v>70.61</v>
       </c>
       <c r="D31" t="n">
-        <v>275</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>32.44</v>
+        <v>27.37</v>
       </c>
       <c r="F31" t="n">
-        <v>45026</v>
+        <v>50589</v>
       </c>
       <c r="G31" t="n">
-        <v>42474</v>
+        <v>70856</v>
       </c>
       <c r="H31" t="n">
-        <v>30791</v>
+        <v>37723</v>
       </c>
       <c r="I31" t="n">
-        <v>79220</v>
+        <v>46084</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="b">
@@ -1975,47 +2067,50 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>30791</v>
+        <v>37723</v>
       </c>
       <c r="O31" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="P31" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+        <v>37.37</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8361</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21fd59c6</t>
+          <t>ece4051a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>89.95999999999999</v>
+        <v>48.62</v>
       </c>
       <c r="D32" t="n">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="E32" t="n">
-        <v>93.31999999999999</v>
+        <v>12.09</v>
       </c>
       <c r="F32" t="n">
-        <v>53361</v>
+        <v>75230</v>
       </c>
       <c r="G32" t="n">
-        <v>71784</v>
+        <v>31157</v>
       </c>
       <c r="H32" t="n">
-        <v>39023</v>
+        <v>36039</v>
       </c>
       <c r="I32" t="n">
-        <v>65651</v>
+        <v>60969</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="b">
@@ -2024,47 +2119,50 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>39023</v>
+        <v>31157</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="P32" t="n">
-        <v>100.32</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>23.09</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>29812</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6790bf84</t>
+          <t>6b56438a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>35.93</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="E33" t="n">
-        <v>57.15</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>77698</v>
+        <v>31406</v>
       </c>
       <c r="G33" t="n">
-        <v>76376</v>
+        <v>55433</v>
       </c>
       <c r="H33" t="n">
-        <v>75369</v>
+        <v>38279</v>
       </c>
       <c r="I33" t="n">
-        <v>12579</v>
+        <v>65998</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="b">
@@ -2073,47 +2171,50 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>75369</v>
+        <v>31406</v>
       </c>
       <c r="O33" t="n">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="P33" t="n">
-        <v>68.15000000000001</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>105.07</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>34592</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bf27371d</t>
+          <t>b68db4d5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realme S23</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>43.77</v>
+        <v>64.37</v>
       </c>
       <c r="D34" t="n">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="E34" t="n">
-        <v>20.06</v>
+        <v>55.38</v>
       </c>
       <c r="F34" t="n">
-        <v>31267</v>
+        <v>35346</v>
       </c>
       <c r="G34" t="n">
-        <v>35488</v>
+        <v>63190</v>
       </c>
       <c r="H34" t="n">
-        <v>55296</v>
+        <v>52861</v>
       </c>
       <c r="I34" t="n">
-        <v>79977</v>
+        <v>30491</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="b">
@@ -2122,47 +2223,50 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>31267</v>
+        <v>35346</v>
       </c>
       <c r="O34" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="P34" t="n">
-        <v>27.06</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+        <v>69.38</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4855</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8ce8cdbb</t>
+          <t>1e3bf9ea</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64.2</v>
+        <v>31.39</v>
       </c>
       <c r="D35" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="E35" t="n">
-        <v>63.48</v>
+        <v>45.4</v>
       </c>
       <c r="F35" t="n">
-        <v>77266</v>
+        <v>55983</v>
       </c>
       <c r="G35" t="n">
-        <v>37438</v>
+        <v>36558</v>
       </c>
       <c r="H35" t="n">
-        <v>65638</v>
+        <v>72605</v>
       </c>
       <c r="I35" t="n">
-        <v>68841</v>
+        <v>47335</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="b">
@@ -2171,47 +2275,50 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>37438</v>
+        <v>36558</v>
       </c>
       <c r="O35" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="P35" t="n">
-        <v>71.47999999999999</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>53.4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>10777</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>956465a8</t>
+          <t>331b5a89</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>63.67</v>
+        <v>65.78</v>
       </c>
       <c r="D36" t="n">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="E36" t="n">
-        <v>90.14</v>
+        <v>38.57</v>
       </c>
       <c r="F36" t="n">
-        <v>47935</v>
+        <v>40088</v>
       </c>
       <c r="G36" t="n">
-        <v>70543</v>
+        <v>38530</v>
       </c>
       <c r="H36" t="n">
-        <v>79998</v>
+        <v>47280</v>
       </c>
       <c r="I36" t="n">
-        <v>39349</v>
+        <v>40224</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="b">
@@ -2220,47 +2327,50 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>47935</v>
+        <v>38530</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="P36" t="n">
-        <v>97.14</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>50.57</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1694</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4768154e</t>
+          <t>e8d939d9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>99.03</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>15.58</v>
+        <v>64.95</v>
       </c>
       <c r="F37" t="n">
-        <v>51203</v>
+        <v>39368</v>
       </c>
       <c r="G37" t="n">
-        <v>32836</v>
+        <v>67039</v>
       </c>
       <c r="H37" t="n">
-        <v>62545</v>
+        <v>36341</v>
       </c>
       <c r="I37" t="n">
-        <v>49317</v>
+        <v>35970</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="b">
@@ -2269,47 +2379,50 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>32836</v>
+        <v>36341</v>
       </c>
       <c r="O37" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="P37" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+        <v>69.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>371</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>d30b4d29</t>
+          <t>664f8336</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>61.1</v>
+        <v>69.14</v>
       </c>
       <c r="D38" t="n">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="E38" t="n">
-        <v>33.2</v>
+        <v>12.56</v>
       </c>
       <c r="F38" t="n">
-        <v>68276</v>
+        <v>54021</v>
       </c>
       <c r="G38" t="n">
-        <v>62631</v>
+        <v>46709</v>
       </c>
       <c r="H38" t="n">
-        <v>72394</v>
+        <v>63040</v>
       </c>
       <c r="I38" t="n">
-        <v>17333</v>
+        <v>74955</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="b">
@@ -2318,47 +2431,50 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>62631</v>
+        <v>46709</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="P38" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>23.56</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>28246</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7c9f8d33</t>
+          <t>b8804fa0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41.11</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>126</v>
+        <v>435</v>
       </c>
       <c r="E39" t="n">
-        <v>93.23999999999999</v>
+        <v>61.36</v>
       </c>
       <c r="F39" t="n">
-        <v>43787</v>
+        <v>62238</v>
       </c>
       <c r="G39" t="n">
-        <v>63306</v>
+        <v>71989</v>
       </c>
       <c r="H39" t="n">
-        <v>65606</v>
+        <v>41779</v>
       </c>
       <c r="I39" t="n">
-        <v>53923</v>
+        <v>44130</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="b">
@@ -2367,47 +2483,50 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>43787</v>
+        <v>41779</v>
       </c>
       <c r="O39" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="P39" t="n">
-        <v>106.24</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+        <v>64.36</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2351</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fc8a2f19</t>
+          <t>83c1229d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>81.95</v>
+        <v>48.21</v>
       </c>
       <c r="D40" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E40" t="n">
-        <v>93.93000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>45649</v>
+        <v>34461</v>
       </c>
       <c r="G40" t="n">
-        <v>38270</v>
+        <v>35799</v>
       </c>
       <c r="H40" t="n">
-        <v>74780</v>
+        <v>52985</v>
       </c>
       <c r="I40" t="n">
-        <v>23606</v>
+        <v>38756</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="b">
@@ -2416,47 +2535,50 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>38270</v>
+        <v>34461</v>
       </c>
       <c r="O40" t="n">
         <v>0.65</v>
       </c>
       <c r="P40" t="n">
-        <v>96.93000000000001</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+        <v>93.56999999999999</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4295</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9e6455ac</t>
+          <t>112de73a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>71.15000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="D41" t="n">
-        <v>155</v>
+        <v>317</v>
       </c>
       <c r="E41" t="n">
-        <v>17.36</v>
+        <v>33.16</v>
       </c>
       <c r="F41" t="n">
-        <v>40166</v>
+        <v>40772</v>
       </c>
       <c r="G41" t="n">
-        <v>39441</v>
+        <v>71841</v>
       </c>
       <c r="H41" t="n">
-        <v>60810</v>
+        <v>33051</v>
       </c>
       <c r="I41" t="n">
-        <v>77666</v>
+        <v>70333</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="b">
@@ -2465,47 +2587,50 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>39441</v>
+        <v>33051</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>38.16</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>37282</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05ca374a</t>
+          <t>c059df07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>63.97</v>
+        <v>62.08</v>
       </c>
       <c r="D42" t="n">
-        <v>250</v>
+        <v>333</v>
       </c>
       <c r="E42" t="n">
-        <v>53.14</v>
+        <v>21.47</v>
       </c>
       <c r="F42" t="n">
-        <v>60278</v>
+        <v>55237</v>
       </c>
       <c r="G42" t="n">
-        <v>78932</v>
+        <v>35553</v>
       </c>
       <c r="H42" t="n">
-        <v>39138</v>
+        <v>67242</v>
       </c>
       <c r="I42" t="n">
-        <v>61792</v>
+        <v>24464</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="b">
@@ -2514,47 +2639,50 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>39138</v>
+        <v>35553</v>
       </c>
       <c r="O42" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="P42" t="n">
-        <v>62.14</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+        <v>32.47</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>11089</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8277805e</t>
+          <t>eb765eea</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>86.17</v>
+        <v>51.05</v>
       </c>
       <c r="D43" t="n">
-        <v>487</v>
+        <v>118</v>
       </c>
       <c r="E43" t="n">
-        <v>65.11</v>
+        <v>99.09</v>
       </c>
       <c r="F43" t="n">
-        <v>67711</v>
+        <v>52412</v>
       </c>
       <c r="G43" t="n">
-        <v>74078</v>
+        <v>50641</v>
       </c>
       <c r="H43" t="n">
-        <v>55999</v>
+        <v>73434</v>
       </c>
       <c r="I43" t="n">
-        <v>11531</v>
+        <v>35641</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="b">
@@ -2563,47 +2691,50 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>55999</v>
+        <v>50641</v>
       </c>
       <c r="O43" t="n">
         <v>0.68</v>
       </c>
       <c r="P43" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>110.09</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3f3489dd</t>
+          <t>5fd46adf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>62.02</v>
+        <v>92.34</v>
       </c>
       <c r="D44" t="n">
-        <v>457</v>
+        <v>161</v>
       </c>
       <c r="E44" t="n">
-        <v>15.14</v>
+        <v>89.59</v>
       </c>
       <c r="F44" t="n">
-        <v>39989</v>
+        <v>50452</v>
       </c>
       <c r="G44" t="n">
-        <v>68624</v>
+        <v>37911</v>
       </c>
       <c r="H44" t="n">
-        <v>79077</v>
+        <v>76390</v>
       </c>
       <c r="I44" t="n">
-        <v>51766</v>
+        <v>21915</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="b">
@@ -2612,47 +2743,50 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>39989</v>
+        <v>37911</v>
       </c>
       <c r="O44" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="P44" t="n">
-        <v>22.14</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>91.59</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>15996</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07af0141</t>
+          <t>f313a21d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>74.97</v>
+        <v>35.01</v>
       </c>
       <c r="D45" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E45" t="n">
-        <v>97.45</v>
+        <v>15.49</v>
       </c>
       <c r="F45" t="n">
-        <v>31229</v>
+        <v>34705</v>
       </c>
       <c r="G45" t="n">
-        <v>62541</v>
+        <v>33111</v>
       </c>
       <c r="H45" t="n">
-        <v>66113</v>
+        <v>50408</v>
       </c>
       <c r="I45" t="n">
-        <v>59723</v>
+        <v>25285</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="b">
@@ -2661,47 +2795,50 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>31229</v>
+        <v>33111</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="P45" t="n">
-        <v>100.45</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+        <v>21.49</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7826</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ace46e79</t>
+          <t>86a2e61e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>80.53</v>
+        <v>96.28</v>
       </c>
       <c r="D46" t="n">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E46" t="n">
-        <v>69.97</v>
+        <v>49.92</v>
       </c>
       <c r="F46" t="n">
-        <v>79631</v>
+        <v>37629</v>
       </c>
       <c r="G46" t="n">
-        <v>72686</v>
+        <v>70842</v>
       </c>
       <c r="H46" t="n">
-        <v>58125</v>
+        <v>30306</v>
       </c>
       <c r="I46" t="n">
-        <v>24953</v>
+        <v>33874</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="b">
@@ -2710,47 +2847,50 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>58125</v>
+        <v>30306</v>
       </c>
       <c r="O46" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="P46" t="n">
-        <v>71.97</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+        <v>51.92</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3568</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fb0bfee4</t>
+          <t>233db855</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>42.43</v>
+        <v>30.03</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="E47" t="n">
-        <v>60.13</v>
+        <v>72.45</v>
       </c>
       <c r="F47" t="n">
-        <v>71124</v>
+        <v>44290</v>
       </c>
       <c r="G47" t="n">
-        <v>47982</v>
+        <v>47206</v>
       </c>
       <c r="H47" t="n">
-        <v>48327</v>
+        <v>34178</v>
       </c>
       <c r="I47" t="n">
-        <v>14635</v>
+        <v>19742</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="b">
@@ -2759,47 +2899,50 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>47982</v>
+        <v>34178</v>
       </c>
       <c r="O47" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="P47" t="n">
-        <v>72.13</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+        <v>78.45</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>14436</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>468cef30</t>
+          <t>050fe045</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54.14</v>
+        <v>56.8</v>
       </c>
       <c r="D48" t="n">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="E48" t="n">
-        <v>31.55</v>
+        <v>49.54</v>
       </c>
       <c r="F48" t="n">
-        <v>51774</v>
+        <v>37227</v>
       </c>
       <c r="G48" t="n">
-        <v>54241</v>
+        <v>60712</v>
       </c>
       <c r="H48" t="n">
-        <v>51769</v>
+        <v>74798</v>
       </c>
       <c r="I48" t="n">
-        <v>21892</v>
+        <v>54225</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="b">
@@ -2808,47 +2951,50 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>51769</v>
+        <v>37227</v>
       </c>
       <c r="O48" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="P48" t="n">
-        <v>41.55</v>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+        <v>55.54</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>16998</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5da75c29</t>
+          <t>c3ffbced</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>63.5</v>
+        <v>83.19</v>
       </c>
       <c r="D49" t="n">
-        <v>451</v>
+        <v>46</v>
       </c>
       <c r="E49" t="n">
-        <v>69.45999999999999</v>
+        <v>42.97</v>
       </c>
       <c r="F49" t="n">
-        <v>75844</v>
+        <v>44103</v>
       </c>
       <c r="G49" t="n">
-        <v>58178</v>
+        <v>34570</v>
       </c>
       <c r="H49" t="n">
-        <v>30523</v>
+        <v>67760</v>
       </c>
       <c r="I49" t="n">
-        <v>27589</v>
+        <v>40052</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="b">
@@ -2857,47 +3003,50 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>30523</v>
+        <v>34570</v>
       </c>
       <c r="O49" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>81.45999999999999</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+        <v>56.97</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5482</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>a33cf3b9</t>
+          <t>a82689d7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>84.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="D50" t="n">
-        <v>456</v>
+        <v>228</v>
       </c>
       <c r="E50" t="n">
-        <v>24.83</v>
+        <v>10.84</v>
       </c>
       <c r="F50" t="n">
-        <v>30088</v>
+        <v>78849</v>
       </c>
       <c r="G50" t="n">
-        <v>56688</v>
+        <v>67629</v>
       </c>
       <c r="H50" t="n">
-        <v>40805</v>
+        <v>56596</v>
       </c>
       <c r="I50" t="n">
-        <v>47546</v>
+        <v>47571</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="b">
@@ -2906,47 +3055,50 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>30088</v>
+        <v>56596</v>
       </c>
       <c r="O50" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="P50" t="n">
-        <v>31.83</v>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+        <v>15.84</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>9025</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5c4fb45c</t>
+          <t>e01af7c7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realme S23</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>53.85</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E51" t="n">
-        <v>16.39</v>
+        <v>89.64</v>
       </c>
       <c r="F51" t="n">
-        <v>63164</v>
+        <v>31367</v>
       </c>
       <c r="G51" t="n">
-        <v>37819</v>
+        <v>56714</v>
       </c>
       <c r="H51" t="n">
-        <v>75647</v>
+        <v>53419</v>
       </c>
       <c r="I51" t="n">
-        <v>58166</v>
+        <v>69710</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="b">
@@ -2955,47 +3107,50 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>37819</v>
+        <v>31367</v>
       </c>
       <c r="O51" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P51" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+        <v>99.64</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>38343</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>84ea0013</t>
+          <t>46ffe27e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53.87</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>98</v>
+        <v>478</v>
       </c>
       <c r="E52" t="n">
-        <v>91.09999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="F52" t="n">
-        <v>53564</v>
+        <v>31755</v>
       </c>
       <c r="G52" t="n">
-        <v>76563</v>
+        <v>35931</v>
       </c>
       <c r="H52" t="n">
-        <v>49437</v>
+        <v>41670</v>
       </c>
       <c r="I52" t="n">
-        <v>23019</v>
+        <v>77743</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="b">
@@ -3004,20 +3159,23 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>49437</v>
+        <v>31755</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="P52" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>99.87</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>45988</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2310e16b</t>
+          <t>708dfc5c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3026,25 +3184,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>68.88</v>
+        <v>60.46</v>
       </c>
       <c r="D53" t="n">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="E53" t="n">
-        <v>86.53</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>31257</v>
+        <v>78215</v>
       </c>
       <c r="G53" t="n">
-        <v>48302</v>
+        <v>46701</v>
       </c>
       <c r="H53" t="n">
-        <v>74472</v>
+        <v>67584</v>
       </c>
       <c r="I53" t="n">
-        <v>28839</v>
+        <v>33675</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="b">
@@ -3053,47 +3211,50 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>31257</v>
+        <v>46701</v>
       </c>
       <c r="O53" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>93.53</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+        <v>104.96</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>13026</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53f893e9</t>
+          <t>b532206d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>77.79000000000001</v>
+        <v>34.89</v>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>21.9</v>
+        <v>91.27</v>
       </c>
       <c r="F54" t="n">
-        <v>72512</v>
+        <v>74294</v>
       </c>
       <c r="G54" t="n">
-        <v>48763</v>
+        <v>79952</v>
       </c>
       <c r="H54" t="n">
-        <v>31431</v>
+        <v>72036</v>
       </c>
       <c r="I54" t="n">
-        <v>33065</v>
+        <v>17955</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="b">
@@ -3102,47 +3263,50 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>31431</v>
+        <v>72036</v>
       </c>
       <c r="O54" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="P54" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+        <v>102.27</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>54081</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>a9a053f9</t>
+          <t>abac1f89</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>72.83</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>101</v>
+        <v>399</v>
       </c>
       <c r="E55" t="n">
-        <v>66.06999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="F55" t="n">
-        <v>66440</v>
+        <v>49898</v>
       </c>
       <c r="G55" t="n">
-        <v>32471</v>
+        <v>41977</v>
       </c>
       <c r="H55" t="n">
-        <v>45991</v>
+        <v>32914</v>
       </c>
       <c r="I55" t="n">
-        <v>54544</v>
+        <v>43126</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="b">
@@ -3151,47 +3315,50 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>32471</v>
+        <v>32914</v>
       </c>
       <c r="O55" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="P55" t="n">
-        <v>78.06999999999999</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+        <v>46.81</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>10212</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>f37819e2</t>
+          <t>f5c04ced</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>44.39</v>
+        <v>90.94</v>
       </c>
       <c r="D56" t="n">
-        <v>111</v>
+        <v>258</v>
       </c>
       <c r="E56" t="n">
-        <v>30.7</v>
+        <v>47.78</v>
       </c>
       <c r="F56" t="n">
-        <v>47525</v>
+        <v>56683</v>
       </c>
       <c r="G56" t="n">
-        <v>57025</v>
+        <v>65820</v>
       </c>
       <c r="H56" t="n">
-        <v>59225</v>
+        <v>33338</v>
       </c>
       <c r="I56" t="n">
-        <v>47759</v>
+        <v>16233</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="b">
@@ -3200,47 +3367,50 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>47525</v>
+        <v>33338</v>
       </c>
       <c r="O56" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="P56" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+        <v>53.78</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>17105</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>e41c4a4d</t>
+          <t>862a340f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Apple Pixel 8</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>44.24</v>
+        <v>70</v>
       </c>
       <c r="D57" t="n">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="E57" t="n">
-        <v>26.6</v>
+        <v>32.23</v>
       </c>
       <c r="F57" t="n">
-        <v>44319</v>
+        <v>37102</v>
       </c>
       <c r="G57" t="n">
-        <v>39193</v>
+        <v>53285</v>
       </c>
       <c r="H57" t="n">
-        <v>55414</v>
+        <v>48286</v>
       </c>
       <c r="I57" t="n">
-        <v>69404</v>
+        <v>51077</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="b">
@@ -3249,47 +3419,50 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>39193</v>
+        <v>37102</v>
       </c>
       <c r="O57" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="P57" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
+        <v>41.23</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>13975</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1b47e196</t>
+          <t>9b83349c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>82.66</v>
+        <v>70.89</v>
       </c>
       <c r="D58" t="n">
-        <v>432</v>
+        <v>297</v>
       </c>
       <c r="E58" t="n">
-        <v>62.75</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>50330</v>
+        <v>62827</v>
       </c>
       <c r="G58" t="n">
-        <v>76448</v>
+        <v>67927</v>
       </c>
       <c r="H58" t="n">
-        <v>67409</v>
+        <v>71249</v>
       </c>
       <c r="I58" t="n">
-        <v>8011</v>
+        <v>55728</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="b">
@@ -3298,47 +3471,50 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>50330</v>
+        <v>62827</v>
       </c>
       <c r="O58" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="P58" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+        <v>84.98999999999999</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>7099</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>764b3bb8</t>
+          <t>e4b6acf6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>48.08</v>
+        <v>87.08</v>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="E59" t="n">
-        <v>23.31</v>
+        <v>12.77</v>
       </c>
       <c r="F59" t="n">
-        <v>46035</v>
+        <v>60146</v>
       </c>
       <c r="G59" t="n">
-        <v>54756</v>
+        <v>64290</v>
       </c>
       <c r="H59" t="n">
-        <v>59854</v>
+        <v>62997</v>
       </c>
       <c r="I59" t="n">
-        <v>44516</v>
+        <v>78976</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="b">
@@ -3347,47 +3523,50 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>46035</v>
+        <v>60146</v>
       </c>
       <c r="O59" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="P59" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+        <v>20.77</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>18830</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>635b2bf0</t>
+          <t>ac030a9f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>78.79000000000001</v>
+        <v>60.31</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>91.09</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>37640</v>
+        <v>47565</v>
       </c>
       <c r="G60" t="n">
-        <v>30455</v>
+        <v>43712</v>
       </c>
       <c r="H60" t="n">
-        <v>41499</v>
+        <v>69244</v>
       </c>
       <c r="I60" t="n">
-        <v>41257</v>
+        <v>19926</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="b">
@@ -3396,47 +3575,50 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>30455</v>
+        <v>43712</v>
       </c>
       <c r="O60" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="P60" t="n">
-        <v>105.09</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+        <v>84.95999999999999</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23786</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>c8cecafd</t>
+          <t>949e6fa8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Samsung S23</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>67.97</v>
+        <v>42.57</v>
       </c>
       <c r="D61" t="n">
-        <v>354</v>
+        <v>125</v>
       </c>
       <c r="E61" t="n">
-        <v>94.79000000000001</v>
+        <v>91.06</v>
       </c>
       <c r="F61" t="n">
-        <v>33766</v>
+        <v>46480</v>
       </c>
       <c r="G61" t="n">
-        <v>70950</v>
+        <v>71067</v>
       </c>
       <c r="H61" t="n">
-        <v>52972</v>
+        <v>39304</v>
       </c>
       <c r="I61" t="n">
-        <v>30516</v>
+        <v>22800</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="b">
@@ -3445,47 +3627,50 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>33766</v>
+        <v>39304</v>
       </c>
       <c r="O61" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="P61" t="n">
-        <v>102.79</v>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+        <v>100.06</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>16504</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>180bd4f9</t>
+          <t>c09c1337</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>46.87</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
-        <v>72.06999999999999</v>
+        <v>31.17</v>
       </c>
       <c r="F62" t="n">
-        <v>56069</v>
+        <v>74807</v>
       </c>
       <c r="G62" t="n">
-        <v>61976</v>
+        <v>45158</v>
       </c>
       <c r="H62" t="n">
-        <v>36616</v>
+        <v>70631</v>
       </c>
       <c r="I62" t="n">
-        <v>27048</v>
+        <v>28203</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="b">
@@ -3494,47 +3679,50 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>36616</v>
+        <v>45158</v>
       </c>
       <c r="O62" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="P62" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+        <v>33.17</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>16955</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1c5db80c</t>
+          <t>62b4a019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>44.63</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>257</v>
+        <v>489</v>
       </c>
       <c r="E63" t="n">
-        <v>84.25</v>
+        <v>80.88</v>
       </c>
       <c r="F63" t="n">
-        <v>45447</v>
+        <v>45068</v>
       </c>
       <c r="G63" t="n">
-        <v>38893</v>
+        <v>60749</v>
       </c>
       <c r="H63" t="n">
-        <v>50192</v>
+        <v>48100</v>
       </c>
       <c r="I63" t="n">
-        <v>67393</v>
+        <v>63892</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="b">
@@ -3543,47 +3731,50 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>38893</v>
+        <v>45068</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="P63" t="n">
-        <v>88.25</v>
-      </c>
-      <c r="Q63" t="inlineStr"/>
+        <v>85.88</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>18824</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>95ec47a5</t>
+          <t>79d63ef5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>40.97</v>
+        <v>30.05</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>478</v>
       </c>
       <c r="E64" t="n">
-        <v>10.83</v>
+        <v>40.21</v>
       </c>
       <c r="F64" t="n">
-        <v>38428</v>
+        <v>68642</v>
       </c>
       <c r="G64" t="n">
-        <v>75216</v>
+        <v>47898</v>
       </c>
       <c r="H64" t="n">
-        <v>66509</v>
+        <v>67602</v>
       </c>
       <c r="I64" t="n">
-        <v>32672</v>
+        <v>46207</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="b">
@@ -3592,47 +3783,50 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>38428</v>
+        <v>47898</v>
       </c>
       <c r="O64" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="P64" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="Q64" t="inlineStr"/>
+        <v>48.21</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1691</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8f7c1dd4</t>
+          <t>d592de68</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>59.99</v>
+        <v>53.75</v>
       </c>
       <c r="D65" t="n">
-        <v>184</v>
+        <v>479</v>
       </c>
       <c r="E65" t="n">
-        <v>41.06</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>77811</v>
+        <v>47185</v>
       </c>
       <c r="G65" t="n">
-        <v>46560</v>
+        <v>74472</v>
       </c>
       <c r="H65" t="n">
-        <v>42843</v>
+        <v>72264</v>
       </c>
       <c r="I65" t="n">
-        <v>40247</v>
+        <v>45189</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="b">
@@ -3641,47 +3835,50 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>42843</v>
+        <v>47185</v>
       </c>
       <c r="O65" t="n">
-        <v>0.89</v>
+        <v>0.66</v>
       </c>
       <c r="P65" t="n">
-        <v>53.06</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1996</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fafd77d8</t>
+          <t>31b0abd2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>42.23</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>181</v>
+        <v>367</v>
       </c>
       <c r="E66" t="n">
-        <v>22.05</v>
+        <v>45.15</v>
       </c>
       <c r="F66" t="n">
-        <v>59678</v>
+        <v>60551</v>
       </c>
       <c r="G66" t="n">
-        <v>65937</v>
+        <v>79282</v>
       </c>
       <c r="H66" t="n">
-        <v>72555</v>
+        <v>39363</v>
       </c>
       <c r="I66" t="n">
-        <v>66099</v>
+        <v>11045</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="b">
@@ -3690,47 +3887,50 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>59678</v>
+        <v>39363</v>
       </c>
       <c r="O66" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P66" t="n">
-        <v>33.05</v>
-      </c>
-      <c r="Q66" t="inlineStr"/>
+        <v>53.15</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>28318</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>95abdde1</t>
+          <t>26e38cb5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66.95</v>
+        <v>54.15</v>
       </c>
       <c r="D67" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E67" t="n">
-        <v>29.29</v>
+        <v>93.66</v>
       </c>
       <c r="F67" t="n">
-        <v>53316</v>
+        <v>53848</v>
       </c>
       <c r="G67" t="n">
-        <v>37422</v>
+        <v>66474</v>
       </c>
       <c r="H67" t="n">
-        <v>53463</v>
+        <v>70001</v>
       </c>
       <c r="I67" t="n">
-        <v>75373</v>
+        <v>53812</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="b">
@@ -3739,47 +3939,50 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>37422</v>
+        <v>53848</v>
       </c>
       <c r="O67" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="P67" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+        <v>107.66</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>36</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>a9e2ec67</t>
+          <t>7737d3fe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>72.36</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>388</v>
+        <v>280</v>
       </c>
       <c r="E68" t="n">
-        <v>38.32</v>
+        <v>85.56</v>
       </c>
       <c r="F68" t="n">
-        <v>45070</v>
+        <v>31302</v>
       </c>
       <c r="G68" t="n">
-        <v>64175</v>
+        <v>36301</v>
       </c>
       <c r="H68" t="n">
-        <v>79624</v>
+        <v>56156</v>
       </c>
       <c r="I68" t="n">
-        <v>37778</v>
+        <v>30107</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="b">
@@ -3788,47 +3991,50 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>45070</v>
+        <v>31302</v>
       </c>
       <c r="O68" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="P68" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+        <v>92.56</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2feb16eb</t>
+          <t>fafcab69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>48.97</v>
+        <v>78.97</v>
       </c>
       <c r="D69" t="n">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="E69" t="n">
-        <v>53.84</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>42485</v>
+        <v>70741</v>
       </c>
       <c r="G69" t="n">
-        <v>52941</v>
+        <v>31554</v>
       </c>
       <c r="H69" t="n">
-        <v>41084</v>
+        <v>68967</v>
       </c>
       <c r="I69" t="n">
-        <v>71466</v>
+        <v>21185</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="b">
@@ -3837,20 +4043,23 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>41084</v>
+        <v>31554</v>
       </c>
       <c r="O69" t="n">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="P69" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+        <v>90.73999999999999</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>10369</v>
+      </c>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69166c25</t>
+          <t>93134ab2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3859,25 +4068,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>88.33</v>
+        <v>87.64</v>
       </c>
       <c r="D70" t="n">
-        <v>120</v>
+        <v>443</v>
       </c>
       <c r="E70" t="n">
-        <v>48.03</v>
+        <v>36.6</v>
       </c>
       <c r="F70" t="n">
-        <v>44763</v>
+        <v>35479</v>
       </c>
       <c r="G70" t="n">
-        <v>49731</v>
+        <v>41730</v>
       </c>
       <c r="H70" t="n">
-        <v>54356</v>
+        <v>65007</v>
       </c>
       <c r="I70" t="n">
-        <v>61821</v>
+        <v>17039</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="b">
@@ -3886,47 +4095,50 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>44763</v>
+        <v>35479</v>
       </c>
       <c r="O70" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="P70" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+        <v>46.6</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2d06aba3</t>
+          <t>43282893</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsung S23</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>96.98</v>
+        <v>84.53</v>
       </c>
       <c r="D71" t="n">
-        <v>233</v>
+        <v>487</v>
       </c>
       <c r="E71" t="n">
-        <v>79.38</v>
+        <v>38.63</v>
       </c>
       <c r="F71" t="n">
-        <v>67455</v>
+        <v>77068</v>
       </c>
       <c r="G71" t="n">
-        <v>70254</v>
+        <v>53237</v>
       </c>
       <c r="H71" t="n">
-        <v>54926</v>
+        <v>31494</v>
       </c>
       <c r="I71" t="n">
-        <v>28896</v>
+        <v>53144</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="b">
@@ -3935,47 +4147,50 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>54926</v>
+        <v>31494</v>
       </c>
       <c r="O71" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="P71" t="n">
-        <v>81.38</v>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+        <v>48.63</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>21650</v>
+      </c>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>684aa23a</t>
+          <t>18096011</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>89.53</v>
+        <v>60.98</v>
       </c>
       <c r="D72" t="n">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="E72" t="n">
-        <v>56.99</v>
+        <v>56.4</v>
       </c>
       <c r="F72" t="n">
-        <v>55795</v>
+        <v>47843</v>
       </c>
       <c r="G72" t="n">
-        <v>65802</v>
+        <v>44349</v>
       </c>
       <c r="H72" t="n">
-        <v>49807</v>
+        <v>55842</v>
       </c>
       <c r="I72" t="n">
-        <v>74911</v>
+        <v>39446</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="b">
@@ -3984,47 +4199,50 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>49807</v>
+        <v>44349</v>
       </c>
       <c r="O72" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="P72" t="n">
-        <v>64.99000000000001</v>
-      </c>
-      <c r="Q72" t="inlineStr"/>
+        <v>58.4</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4903</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>eedf440d</t>
+          <t>5c3f3ac5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsung S23</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>36</v>
+        <v>73.27</v>
       </c>
       <c r="D73" t="n">
-        <v>35</v>
+        <v>280</v>
       </c>
       <c r="E73" t="n">
-        <v>93.59999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="F73" t="n">
-        <v>36290</v>
+        <v>52838</v>
       </c>
       <c r="G73" t="n">
-        <v>47652</v>
+        <v>70992</v>
       </c>
       <c r="H73" t="n">
-        <v>45998</v>
+        <v>65592</v>
       </c>
       <c r="I73" t="n">
-        <v>32741</v>
+        <v>35769</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="b">
@@ -4033,47 +4251,50 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>36290</v>
+        <v>52838</v>
       </c>
       <c r="O73" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="P73" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+        <v>93.67</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>17069</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>79a50940</t>
+          <t>919637e3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>45.77</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="E74" t="n">
-        <v>96.53</v>
+        <v>87.98</v>
       </c>
       <c r="F74" t="n">
-        <v>78204</v>
+        <v>75231</v>
       </c>
       <c r="G74" t="n">
-        <v>66334</v>
+        <v>77871</v>
       </c>
       <c r="H74" t="n">
-        <v>66959</v>
+        <v>49459</v>
       </c>
       <c r="I74" t="n">
-        <v>78881</v>
+        <v>78264</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="b">
@@ -4082,47 +4303,50 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
-        <v>66334</v>
+        <v>49459</v>
       </c>
       <c r="O74" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P74" t="n">
-        <v>106.53</v>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+        <v>101.98</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>28805</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>f8e4536e</t>
+          <t>42cb68b8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>Apple Pixel 8</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>36.58</v>
+        <v>87</v>
       </c>
       <c r="D75" t="n">
-        <v>446</v>
+        <v>193</v>
       </c>
       <c r="E75" t="n">
-        <v>69.98</v>
+        <v>16.92</v>
       </c>
       <c r="F75" t="n">
-        <v>40672</v>
+        <v>68868</v>
       </c>
       <c r="G75" t="n">
-        <v>44125</v>
+        <v>33723</v>
       </c>
       <c r="H75" t="n">
-        <v>77945</v>
+        <v>78644</v>
       </c>
       <c r="I75" t="n">
-        <v>63540</v>
+        <v>67967</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="b">
@@ -4131,47 +4355,50 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>40672</v>
+        <v>33723</v>
       </c>
       <c r="O75" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="P75" t="n">
-        <v>82.98</v>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+        <v>19.92</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>34244</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>461853d0</t>
+          <t>8b8a8b3b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36.5</v>
+        <v>44.49</v>
       </c>
       <c r="D76" t="n">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="E76" t="n">
-        <v>48.11</v>
+        <v>52.88</v>
       </c>
       <c r="F76" t="n">
-        <v>79159</v>
+        <v>37929</v>
       </c>
       <c r="G76" t="n">
-        <v>73205</v>
+        <v>34883</v>
       </c>
       <c r="H76" t="n">
-        <v>48258</v>
+        <v>71411</v>
       </c>
       <c r="I76" t="n">
-        <v>18288</v>
+        <v>15231</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="b">
@@ -4180,47 +4407,50 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>48258</v>
+        <v>34883</v>
       </c>
       <c r="O76" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="P76" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="Q76" t="inlineStr"/>
+        <v>65.88</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>19652</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>c5dc8d0d</t>
+          <t>844e77ad</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>94.84999999999999</v>
+        <v>35.37</v>
       </c>
       <c r="D77" t="n">
-        <v>396</v>
+        <v>486</v>
       </c>
       <c r="E77" t="n">
-        <v>37.03</v>
+        <v>36.66</v>
       </c>
       <c r="F77" t="n">
-        <v>61769</v>
+        <v>46094</v>
       </c>
       <c r="G77" t="n">
-        <v>52283</v>
+        <v>31691</v>
       </c>
       <c r="H77" t="n">
-        <v>57558</v>
+        <v>51414</v>
       </c>
       <c r="I77" t="n">
-        <v>68863</v>
+        <v>55777</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="b">
@@ -4229,47 +4459,50 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>52283</v>
+        <v>31691</v>
       </c>
       <c r="O77" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="P77" t="n">
-        <v>41.03</v>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+        <v>46.66</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>24086</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3d7fe79a</t>
+          <t>1cebb73c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>84.64</v>
+        <v>95.25</v>
       </c>
       <c r="D78" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E78" t="n">
-        <v>11.55</v>
+        <v>41.31</v>
       </c>
       <c r="F78" t="n">
-        <v>64224</v>
+        <v>48207</v>
       </c>
       <c r="G78" t="n">
-        <v>77578</v>
+        <v>31472</v>
       </c>
       <c r="H78" t="n">
-        <v>77481</v>
+        <v>65831</v>
       </c>
       <c r="I78" t="n">
-        <v>63975</v>
+        <v>21222</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="b">
@@ -4278,47 +4511,50 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>64224</v>
+        <v>31472</v>
       </c>
       <c r="O78" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="P78" t="n">
-        <v>17.55</v>
-      </c>
-      <c r="Q78" t="inlineStr"/>
+        <v>46.31</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>10250</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21769834</t>
+          <t>d284689c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Xiaomi 14</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>33.97</v>
+        <v>35.83</v>
       </c>
       <c r="D79" t="n">
-        <v>117</v>
+        <v>376</v>
       </c>
       <c r="E79" t="n">
-        <v>48.38</v>
+        <v>44.52</v>
       </c>
       <c r="F79" t="n">
-        <v>36956</v>
+        <v>58153</v>
       </c>
       <c r="G79" t="n">
-        <v>79395</v>
+        <v>64367</v>
       </c>
       <c r="H79" t="n">
-        <v>48959</v>
+        <v>43154</v>
       </c>
       <c r="I79" t="n">
-        <v>62419</v>
+        <v>13789</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="b">
@@ -4327,47 +4563,50 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>36956</v>
+        <v>43154</v>
       </c>
       <c r="O79" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="P79" t="n">
-        <v>57.38</v>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+        <v>55.52</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>29365</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>c645f96f</t>
+          <t>787a823c</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>67.84999999999999</v>
+        <v>99.86</v>
       </c>
       <c r="D80" t="n">
-        <v>399</v>
+        <v>55</v>
       </c>
       <c r="E80" t="n">
-        <v>89.34</v>
+        <v>25.69</v>
       </c>
       <c r="F80" t="n">
-        <v>43538</v>
+        <v>70927</v>
       </c>
       <c r="G80" t="n">
-        <v>30030</v>
+        <v>38245</v>
       </c>
       <c r="H80" t="n">
-        <v>53102</v>
+        <v>58394</v>
       </c>
       <c r="I80" t="n">
-        <v>37028</v>
+        <v>70957</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="b">
@@ -4376,47 +4615,50 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>30030</v>
+        <v>38245</v>
       </c>
       <c r="O80" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="P80" t="n">
-        <v>100.34</v>
-      </c>
-      <c r="Q80" t="inlineStr"/>
+        <v>36.69</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>32712</v>
+      </c>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5bfcda9b</t>
+          <t>bf5d884a</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>48.47</v>
+        <v>51.27</v>
       </c>
       <c r="D81" t="n">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="E81" t="n">
-        <v>70.26000000000001</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>45007</v>
+        <v>63330</v>
       </c>
       <c r="G81" t="n">
-        <v>75036</v>
+        <v>66742</v>
       </c>
       <c r="H81" t="n">
-        <v>60751</v>
+        <v>38491</v>
       </c>
       <c r="I81" t="n">
-        <v>19313</v>
+        <v>12414</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="b">
@@ -4425,47 +4667,50 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>45007</v>
+        <v>38491</v>
       </c>
       <c r="O81" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="P81" t="n">
-        <v>80.26000000000001</v>
-      </c>
-      <c r="Q81" t="inlineStr"/>
+        <v>95.26000000000001</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>26077</v>
+      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a38eb9c0</t>
+          <t>f5a5a585</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>88.23</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="E82" t="n">
-        <v>56.17</v>
+        <v>97.97</v>
       </c>
       <c r="F82" t="n">
-        <v>59488</v>
+        <v>74687</v>
       </c>
       <c r="G82" t="n">
-        <v>46868</v>
+        <v>78990</v>
       </c>
       <c r="H82" t="n">
-        <v>77312</v>
+        <v>49549</v>
       </c>
       <c r="I82" t="n">
-        <v>40473</v>
+        <v>41235</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="b">
@@ -4474,47 +4719,50 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>46868</v>
+        <v>49549</v>
       </c>
       <c r="O82" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="P82" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="Q82" t="inlineStr"/>
+        <v>99.97</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>8314</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ec519824</t>
+          <t>09512998</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Samsung Edge 40</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>52.39</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="D83" t="n">
-        <v>207</v>
+        <v>427</v>
       </c>
       <c r="E83" t="n">
-        <v>75.12</v>
+        <v>25</v>
       </c>
       <c r="F83" t="n">
-        <v>55913</v>
+        <v>49715</v>
       </c>
       <c r="G83" t="n">
-        <v>36281</v>
+        <v>45663</v>
       </c>
       <c r="H83" t="n">
-        <v>51259</v>
+        <v>70257</v>
       </c>
       <c r="I83" t="n">
-        <v>43358</v>
+        <v>58081</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="b">
@@ -4523,47 +4771,50 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>36281</v>
+        <v>45663</v>
       </c>
       <c r="O83" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="P83" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="Q83" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>12418</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5fe95e02</t>
+          <t>d9db35e0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>84</v>
+        <v>55.98</v>
       </c>
       <c r="D84" t="n">
-        <v>390</v>
+        <v>484</v>
       </c>
       <c r="E84" t="n">
-        <v>46.91</v>
+        <v>99.94</v>
       </c>
       <c r="F84" t="n">
-        <v>31947</v>
+        <v>39142</v>
       </c>
       <c r="G84" t="n">
-        <v>66592</v>
+        <v>33910</v>
       </c>
       <c r="H84" t="n">
-        <v>34363</v>
+        <v>38113</v>
       </c>
       <c r="I84" t="n">
-        <v>55913</v>
+        <v>16636</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="b">
@@ -4572,47 +4823,50 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>31947</v>
+        <v>33910</v>
       </c>
       <c r="O84" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="P84" t="n">
-        <v>57.91</v>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+        <v>111.94</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>17274</v>
+      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>151b40ec</t>
+          <t>829677c0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>53.98</v>
+        <v>36.15</v>
       </c>
       <c r="D85" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="E85" t="n">
-        <v>35.97</v>
+        <v>48.27</v>
       </c>
       <c r="F85" t="n">
-        <v>63090</v>
+        <v>58874</v>
       </c>
       <c r="G85" t="n">
-        <v>59060</v>
+        <v>67726</v>
       </c>
       <c r="H85" t="n">
-        <v>79660</v>
+        <v>57251</v>
       </c>
       <c r="I85" t="n">
-        <v>25607</v>
+        <v>16162</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="b">
@@ -4621,47 +4875,50 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>59060</v>
+        <v>57251</v>
       </c>
       <c r="O85" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="P85" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+        <v>51.27</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>41089</v>
+      </c>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>73fe53c4</t>
+          <t>568e716b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>57.98</v>
+        <v>62.42</v>
       </c>
       <c r="D86" t="n">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E86" t="n">
-        <v>50.09</v>
+        <v>94.64</v>
       </c>
       <c r="F86" t="n">
-        <v>49660</v>
+        <v>47497</v>
       </c>
       <c r="G86" t="n">
-        <v>64453</v>
+        <v>71203</v>
       </c>
       <c r="H86" t="n">
-        <v>73942</v>
+        <v>61608</v>
       </c>
       <c r="I86" t="n">
-        <v>55641</v>
+        <v>32127</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="b">
@@ -4670,47 +4927,50 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>49660</v>
+        <v>47497</v>
       </c>
       <c r="O86" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="P86" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+        <v>96.64</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>15370</v>
+      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>af834edb</t>
+          <t>07671fb7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>34.76</v>
+        <v>92.38</v>
       </c>
       <c r="D87" t="n">
-        <v>469</v>
+        <v>27</v>
       </c>
       <c r="E87" t="n">
-        <v>21.04</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>32553</v>
+        <v>55463</v>
       </c>
       <c r="G87" t="n">
-        <v>61724</v>
+        <v>41636</v>
       </c>
       <c r="H87" t="n">
-        <v>65691</v>
+        <v>78520</v>
       </c>
       <c r="I87" t="n">
-        <v>11740</v>
+        <v>21828</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="b">
@@ -4719,47 +4979,50 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>32553</v>
+        <v>41636</v>
       </c>
       <c r="O87" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="P87" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+        <v>81.43000000000001</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>19808</v>
+      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6c050a1b</t>
+          <t>4a46d5e4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>80.34999999999999</v>
+        <v>78.89</v>
       </c>
       <c r="D88" t="n">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E88" t="n">
-        <v>55.94</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>72408</v>
+        <v>43260</v>
       </c>
       <c r="G88" t="n">
-        <v>41133</v>
+        <v>71697</v>
       </c>
       <c r="H88" t="n">
-        <v>75678</v>
+        <v>70863</v>
       </c>
       <c r="I88" t="n">
-        <v>17189</v>
+        <v>64152</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="b">
@@ -4768,47 +5031,50 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
-        <v>41133</v>
+        <v>43260</v>
       </c>
       <c r="O88" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P88" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+        <v>90.56999999999999</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>20892</v>
+      </c>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>361613ba</t>
+          <t>24f7f09b</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>89.94</v>
+        <v>53.05</v>
       </c>
       <c r="D89" t="n">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="E89" t="n">
-        <v>28.25</v>
+        <v>60.81</v>
       </c>
       <c r="F89" t="n">
-        <v>49153</v>
+        <v>71583</v>
       </c>
       <c r="G89" t="n">
-        <v>68681</v>
+        <v>65518</v>
       </c>
       <c r="H89" t="n">
-        <v>43114</v>
+        <v>63856</v>
       </c>
       <c r="I89" t="n">
-        <v>33384</v>
+        <v>10483</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="b">
@@ -4817,47 +5083,50 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>43114</v>
+        <v>63856</v>
       </c>
       <c r="O89" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="P89" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="Q89" t="inlineStr"/>
+        <v>72.81</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>53373</v>
+      </c>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1d386235</t>
+          <t>dbae7ddc</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>71.89</v>
+        <v>30.1</v>
       </c>
       <c r="D90" t="n">
-        <v>175</v>
+        <v>272</v>
       </c>
       <c r="E90" t="n">
-        <v>57.54</v>
+        <v>35.41</v>
       </c>
       <c r="F90" t="n">
-        <v>34393</v>
+        <v>66157</v>
       </c>
       <c r="G90" t="n">
-        <v>64357</v>
+        <v>50257</v>
       </c>
       <c r="H90" t="n">
-        <v>45033</v>
+        <v>52197</v>
       </c>
       <c r="I90" t="n">
-        <v>25850</v>
+        <v>34561</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="b">
@@ -4866,47 +5135,50 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>34393</v>
+        <v>50257</v>
       </c>
       <c r="O90" t="n">
         <v>0.79</v>
       </c>
       <c r="P90" t="n">
-        <v>69.53999999999999</v>
-      </c>
-      <c r="Q90" t="inlineStr"/>
+        <v>43.41</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>15696</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1314c433</t>
+          <t>73e99d28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>78.23</v>
+        <v>75.19</v>
       </c>
       <c r="D91" t="n">
-        <v>495</v>
+        <v>390</v>
       </c>
       <c r="E91" t="n">
-        <v>36.98</v>
+        <v>62.94</v>
       </c>
       <c r="F91" t="n">
-        <v>65627</v>
+        <v>44501</v>
       </c>
       <c r="G91" t="n">
-        <v>53654</v>
+        <v>60081</v>
       </c>
       <c r="H91" t="n">
-        <v>56262</v>
+        <v>70569</v>
       </c>
       <c r="I91" t="n">
-        <v>69547</v>
+        <v>26836</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="b">
@@ -4915,47 +5187,50 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>53654</v>
+        <v>44501</v>
       </c>
       <c r="O91" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="P91" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
+        <v>65.94</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>17665</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>a03e015f</t>
+          <t>1384f9a5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>70.06999999999999</v>
+        <v>46.94</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="E92" t="n">
-        <v>29.99</v>
+        <v>24.97</v>
       </c>
       <c r="F92" t="n">
-        <v>31660</v>
+        <v>48408</v>
       </c>
       <c r="G92" t="n">
-        <v>49335</v>
+        <v>54017</v>
       </c>
       <c r="H92" t="n">
-        <v>41933</v>
+        <v>54756</v>
       </c>
       <c r="I92" t="n">
-        <v>72600</v>
+        <v>33052</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="b">
@@ -4964,47 +5239,50 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>31660</v>
+        <v>48408</v>
       </c>
       <c r="O92" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="P92" t="n">
-        <v>41.98999999999999</v>
-      </c>
-      <c r="Q92" t="inlineStr"/>
+        <v>38.97</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>15356</v>
+      </c>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>03154642</t>
+          <t>9127fffb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>38.84</v>
+        <v>68.84</v>
       </c>
       <c r="D93" t="n">
-        <v>209</v>
+        <v>7</v>
       </c>
       <c r="E93" t="n">
-        <v>28.65</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>33270</v>
+        <v>56866</v>
       </c>
       <c r="G93" t="n">
-        <v>44818</v>
+        <v>47588</v>
       </c>
       <c r="H93" t="n">
-        <v>77168</v>
+        <v>67141</v>
       </c>
       <c r="I93" t="n">
-        <v>54181</v>
+        <v>17888</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="b">
@@ -5013,47 +5291,50 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>33270</v>
+        <v>47588</v>
       </c>
       <c r="O93" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="P93" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="Q93" t="inlineStr"/>
+        <v>88.51000000000001</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>29700</v>
+      </c>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>fae14961</t>
+          <t>f1e8726c</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>32.81</v>
+        <v>75.3</v>
       </c>
       <c r="D94" t="n">
-        <v>167</v>
+        <v>495</v>
       </c>
       <c r="E94" t="n">
-        <v>76.41</v>
+        <v>65.55</v>
       </c>
       <c r="F94" t="n">
-        <v>43384</v>
+        <v>58467</v>
       </c>
       <c r="G94" t="n">
-        <v>33823</v>
+        <v>58382</v>
       </c>
       <c r="H94" t="n">
-        <v>72064</v>
+        <v>38366</v>
       </c>
       <c r="I94" t="n">
-        <v>32389</v>
+        <v>21831</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="b">
@@ -5062,47 +5343,50 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>33823</v>
+        <v>38366</v>
       </c>
       <c r="O94" t="n">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="P94" t="n">
-        <v>86.41</v>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+        <v>74.55</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>16535</v>
+      </c>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>75db501b</t>
+          <t>0fed258a</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>39.16</v>
+        <v>48.59</v>
       </c>
       <c r="D95" t="n">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="E95" t="n">
-        <v>55.81</v>
+        <v>95.66</v>
       </c>
       <c r="F95" t="n">
-        <v>66051</v>
+        <v>56895</v>
       </c>
       <c r="G95" t="n">
-        <v>74410</v>
+        <v>59688</v>
       </c>
       <c r="H95" t="n">
-        <v>76699</v>
+        <v>69687</v>
       </c>
       <c r="I95" t="n">
-        <v>20037</v>
+        <v>49337</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="b">
@@ -5111,47 +5395,50 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>66051</v>
+        <v>56895</v>
       </c>
       <c r="O95" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P95" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="Q95" t="inlineStr"/>
+        <v>109.66</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>7558</v>
+      </c>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9a7b9f87</t>
+          <t>ca8e7c70</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>31.62</v>
+        <v>46.03</v>
       </c>
       <c r="D96" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E96" t="n">
-        <v>61.79</v>
+        <v>61.57</v>
       </c>
       <c r="F96" t="n">
-        <v>64602</v>
+        <v>72371</v>
       </c>
       <c r="G96" t="n">
-        <v>49168</v>
+        <v>39257</v>
       </c>
       <c r="H96" t="n">
-        <v>71438</v>
+        <v>40703</v>
       </c>
       <c r="I96" t="n">
-        <v>72202</v>
+        <v>17500</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="b">
@@ -5160,20 +5447,23 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>49168</v>
+        <v>39257</v>
       </c>
       <c r="O96" t="n">
         <v>0.95</v>
       </c>
       <c r="P96" t="n">
-        <v>70.78999999999999</v>
-      </c>
-      <c r="Q96" t="inlineStr"/>
+        <v>75.56999999999999</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>21757</v>
+      </c>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>50b3e0d1</t>
+          <t>6b84d7e0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5182,25 +5472,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>66.66</v>
+        <v>91.06</v>
       </c>
       <c r="D97" t="n">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="E97" t="n">
-        <v>98.55</v>
+        <v>40.36</v>
       </c>
       <c r="F97" t="n">
-        <v>59471</v>
+        <v>31483</v>
       </c>
       <c r="G97" t="n">
-        <v>67587</v>
+        <v>63965</v>
       </c>
       <c r="H97" t="n">
-        <v>30591</v>
+        <v>72938</v>
       </c>
       <c r="I97" t="n">
-        <v>12194</v>
+        <v>25575</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="b">
@@ -5209,47 +5499,50 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>30591</v>
+        <v>31483</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="P97" t="n">
-        <v>100.55</v>
-      </c>
-      <c r="Q97" t="inlineStr"/>
+        <v>52.36</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>5908</v>
+      </c>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9498e5dc</t>
+          <t>914e39b5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>33.62</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="E98" t="n">
-        <v>12.3</v>
+        <v>32.82</v>
       </c>
       <c r="F98" t="n">
-        <v>64387</v>
+        <v>37318</v>
       </c>
       <c r="G98" t="n">
-        <v>66791</v>
+        <v>52448</v>
       </c>
       <c r="H98" t="n">
-        <v>31714</v>
+        <v>38325</v>
       </c>
       <c r="I98" t="n">
-        <v>8329</v>
+        <v>33927</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="b">
@@ -5258,47 +5551,50 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>31714</v>
+        <v>37318</v>
       </c>
       <c r="O98" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="P98" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="Q98" t="inlineStr"/>
+        <v>35.82</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>3391</v>
+      </c>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>54db95c2</t>
+          <t>99ed274e</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>44.45</v>
+        <v>63.96</v>
       </c>
       <c r="D99" t="n">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="E99" t="n">
-        <v>28.95</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>79791</v>
+        <v>53159</v>
       </c>
       <c r="G99" t="n">
-        <v>42957</v>
+        <v>62563</v>
       </c>
       <c r="H99" t="n">
-        <v>37562</v>
+        <v>43699</v>
       </c>
       <c r="I99" t="n">
-        <v>33093</v>
+        <v>40162</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="b">
@@ -5307,47 +5603,50 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>37562</v>
+        <v>43699</v>
       </c>
       <c r="O99" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="P99" t="n">
-        <v>30.95</v>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3537</v>
+      </c>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2637360f</t>
+          <t>282eca91</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>94.36</v>
+        <v>90.88</v>
       </c>
       <c r="D100" t="n">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="E100" t="n">
-        <v>52.9</v>
+        <v>85.47</v>
       </c>
       <c r="F100" t="n">
-        <v>55770</v>
+        <v>51980</v>
       </c>
       <c r="G100" t="n">
-        <v>69274</v>
+        <v>69104</v>
       </c>
       <c r="H100" t="n">
-        <v>34087</v>
+        <v>62954</v>
       </c>
       <c r="I100" t="n">
-        <v>30395</v>
+        <v>73207</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="b">
@@ -5356,47 +5655,50 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>34087</v>
+        <v>51980</v>
       </c>
       <c r="O100" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="P100" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="Q100" t="inlineStr"/>
+        <v>89.47</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>21227</v>
+      </c>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6b541560</t>
+          <t>3e51d4dd</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>35.98</v>
+        <v>91.88</v>
       </c>
       <c r="D101" t="n">
-        <v>434</v>
+        <v>266</v>
       </c>
       <c r="E101" t="n">
-        <v>35.73</v>
+        <v>13.85</v>
       </c>
       <c r="F101" t="n">
-        <v>52534</v>
+        <v>36192</v>
       </c>
       <c r="G101" t="n">
-        <v>66723</v>
+        <v>46502</v>
       </c>
       <c r="H101" t="n">
-        <v>76677</v>
+        <v>52056</v>
       </c>
       <c r="I101" t="n">
-        <v>45213</v>
+        <v>37906</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="b">
@@ -5405,15 +5707,18 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>52534</v>
+        <v>36192</v>
       </c>
       <c r="O101" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="P101" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="Q101" t="inlineStr"/>
+        <v>16.85</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1714</v>
+      </c>
+      <c r="R101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/mock_product_data.xlsx
+++ b/data/mock_product_data.xlsx
@@ -523,34 +523,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2a4d6d38</t>
+          <t>b47bf37e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.02</v>
+        <v>53.35</v>
       </c>
       <c r="D2" t="n">
-        <v>357</v>
+        <v>292</v>
       </c>
       <c r="E2" t="n">
-        <v>99.38</v>
+        <v>61.68</v>
       </c>
       <c r="F2" t="n">
-        <v>49636</v>
+        <v>39649</v>
       </c>
       <c r="G2" t="n">
-        <v>53672</v>
+        <v>53119</v>
       </c>
       <c r="H2" t="n">
-        <v>67513</v>
+        <v>65460</v>
       </c>
       <c r="I2" t="n">
-        <v>51754</v>
+        <v>20142</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
@@ -559,50 +559,50 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>49636</v>
+        <v>39649</v>
       </c>
       <c r="O2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="P2" t="n">
-        <v>105.38</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>2118</v>
+        <v>19507</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>87164b04</t>
+          <t>3e7727bc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.63</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>385</v>
       </c>
       <c r="E3" t="n">
-        <v>31.06</v>
+        <v>42.82</v>
       </c>
       <c r="F3" t="n">
-        <v>46194</v>
+        <v>75656</v>
       </c>
       <c r="G3" t="n">
-        <v>71762</v>
+        <v>35867</v>
       </c>
       <c r="H3" t="n">
-        <v>62344</v>
+        <v>34685</v>
       </c>
       <c r="I3" t="n">
-        <v>56354</v>
+        <v>60301</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="b">
@@ -611,50 +611,50 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>46194</v>
+        <v>34685</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="P3" t="n">
-        <v>39.06</v>
+        <v>49.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>10160</v>
+        <v>25616</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>d54e27e0</t>
+          <t>e381ed12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44.23</v>
+        <v>97.27</v>
       </c>
       <c r="D4" t="n">
-        <v>464</v>
+        <v>303</v>
       </c>
       <c r="E4" t="n">
-        <v>66.31999999999999</v>
+        <v>34.33</v>
       </c>
       <c r="F4" t="n">
-        <v>31223</v>
+        <v>63693</v>
       </c>
       <c r="G4" t="n">
-        <v>55195</v>
+        <v>41526</v>
       </c>
       <c r="H4" t="n">
-        <v>53248</v>
+        <v>43421</v>
       </c>
       <c r="I4" t="n">
-        <v>53363</v>
+        <v>30487</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
@@ -663,23 +663,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>31223</v>
+        <v>41526</v>
       </c>
       <c r="O4" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="P4" t="n">
-        <v>73.31999999999999</v>
+        <v>37.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>22140</v>
+        <v>11039</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b8906b65</t>
+          <t>16d0a6db</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -688,25 +688,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.22</v>
+        <v>94.02</v>
       </c>
       <c r="D5" t="n">
-        <v>491</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>15.21</v>
+        <v>55.84</v>
       </c>
       <c r="F5" t="n">
-        <v>64775</v>
+        <v>50889</v>
       </c>
       <c r="G5" t="n">
-        <v>36400</v>
+        <v>56993</v>
       </c>
       <c r="H5" t="n">
-        <v>32584</v>
+        <v>46069</v>
       </c>
       <c r="I5" t="n">
-        <v>50417</v>
+        <v>45809</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="b">
@@ -715,50 +715,50 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>32584</v>
+        <v>46069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="P5" t="n">
-        <v>25.21</v>
+        <v>68.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>17833</v>
+        <v>260</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d4fbc019</t>
+          <t>538f4dca</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.01</v>
+        <v>62.11</v>
       </c>
       <c r="D6" t="n">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="E6" t="n">
-        <v>66.59</v>
+        <v>41.41</v>
       </c>
       <c r="F6" t="n">
-        <v>34593</v>
+        <v>43506</v>
       </c>
       <c r="G6" t="n">
-        <v>32007</v>
+        <v>76926</v>
       </c>
       <c r="H6" t="n">
-        <v>74012</v>
+        <v>68911</v>
       </c>
       <c r="I6" t="n">
-        <v>21578</v>
+        <v>11044</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="b">
@@ -767,50 +767,50 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>32007</v>
+        <v>43506</v>
       </c>
       <c r="O6" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="P6" t="n">
-        <v>72.59</v>
+        <v>51.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>10429</v>
+        <v>32462</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d18f7e8c</t>
+          <t>0c87ac52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>89.92</v>
+        <v>60.63</v>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="E7" t="n">
-        <v>62.47</v>
+        <v>16.8</v>
       </c>
       <c r="F7" t="n">
-        <v>63583</v>
+        <v>70915</v>
       </c>
       <c r="G7" t="n">
-        <v>68024</v>
+        <v>38868</v>
       </c>
       <c r="H7" t="n">
-        <v>74008</v>
+        <v>33795</v>
       </c>
       <c r="I7" t="n">
-        <v>29543</v>
+        <v>46021</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="b">
@@ -819,50 +819,50 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>63583</v>
+        <v>33795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="P7" t="n">
-        <v>75.47</v>
+        <v>30.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>34040</v>
+        <v>12226</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0e43364a</t>
+          <t>a0f5efaf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34.53</v>
+        <v>30.79</v>
       </c>
       <c r="D8" t="n">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="E8" t="n">
-        <v>49.48</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>30942</v>
+        <v>51711</v>
       </c>
       <c r="G8" t="n">
-        <v>41073</v>
+        <v>55755</v>
       </c>
       <c r="H8" t="n">
-        <v>30700</v>
+        <v>45542</v>
       </c>
       <c r="I8" t="n">
-        <v>23242</v>
+        <v>61216</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="b">
@@ -871,50 +871,50 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>30700</v>
+        <v>45542</v>
       </c>
       <c r="O8" t="n">
-        <v>0.67</v>
+        <v>0.99</v>
       </c>
       <c r="P8" t="n">
-        <v>62.48</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>7458</v>
+        <v>15674</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3e72c072</t>
+          <t>ce136f14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33.32</v>
+        <v>37.69</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>377</v>
       </c>
       <c r="E9" t="n">
-        <v>94.47</v>
+        <v>74.86</v>
       </c>
       <c r="F9" t="n">
-        <v>55015</v>
+        <v>54191</v>
       </c>
       <c r="G9" t="n">
-        <v>40630</v>
+        <v>43261</v>
       </c>
       <c r="H9" t="n">
-        <v>77193</v>
+        <v>68611</v>
       </c>
       <c r="I9" t="n">
-        <v>71384</v>
+        <v>54153</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="b">
@@ -923,50 +923,50 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>40630</v>
+        <v>43261</v>
       </c>
       <c r="O9" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="P9" t="n">
-        <v>104.47</v>
+        <v>80.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>30754</v>
+        <v>10892</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>194b50ce</t>
+          <t>61bb9b6b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40.82</v>
+        <v>54.74</v>
       </c>
       <c r="D10" t="n">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="E10" t="n">
-        <v>84.09999999999999</v>
+        <v>27.89</v>
       </c>
       <c r="F10" t="n">
-        <v>45438</v>
+        <v>68026</v>
       </c>
       <c r="G10" t="n">
-        <v>52885</v>
+        <v>55783</v>
       </c>
       <c r="H10" t="n">
-        <v>52109</v>
+        <v>73385</v>
       </c>
       <c r="I10" t="n">
-        <v>69164</v>
+        <v>67681</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="b">
@@ -975,50 +975,50 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>45438</v>
+        <v>55783</v>
       </c>
       <c r="O10" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="P10" t="n">
-        <v>94.09999999999999</v>
+        <v>38.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>23726</v>
+        <v>11898</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e9b325bf</t>
+          <t>5727a6d8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93.12</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="E11" t="n">
-        <v>26.86</v>
+        <v>50.04</v>
       </c>
       <c r="F11" t="n">
-        <v>67388</v>
+        <v>33605</v>
       </c>
       <c r="G11" t="n">
-        <v>63629</v>
+        <v>41403</v>
       </c>
       <c r="H11" t="n">
-        <v>44962</v>
+        <v>70282</v>
       </c>
       <c r="I11" t="n">
-        <v>15848</v>
+        <v>20255</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="b">
@@ -1027,50 +1027,50 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>44962</v>
+        <v>33605</v>
       </c>
       <c r="O11" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="P11" t="n">
-        <v>28.86</v>
+        <v>54.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>29114</v>
+        <v>13350</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>354ac8ca</t>
+          <t>bd710456</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>44.73</v>
+        <v>54.11</v>
       </c>
       <c r="D12" t="n">
-        <v>363</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>74.58</v>
+        <v>13.11</v>
       </c>
       <c r="F12" t="n">
-        <v>52610</v>
+        <v>66342</v>
       </c>
       <c r="G12" t="n">
-        <v>41351</v>
+        <v>45837</v>
       </c>
       <c r="H12" t="n">
-        <v>39578</v>
+        <v>57099</v>
       </c>
       <c r="I12" t="n">
-        <v>16913</v>
+        <v>74249</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="b">
@@ -1079,50 +1079,50 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>39578</v>
+        <v>45837</v>
       </c>
       <c r="O12" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="P12" t="n">
-        <v>86.58</v>
+        <v>18.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>22665</v>
+        <v>28412</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bbc220e4</t>
+          <t>12cea37b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60.4</v>
+        <v>41.34</v>
       </c>
       <c r="D13" t="n">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>65.91</v>
+        <v>56.66</v>
       </c>
       <c r="F13" t="n">
-        <v>35997</v>
+        <v>79990</v>
       </c>
       <c r="G13" t="n">
-        <v>73550</v>
+        <v>64600</v>
       </c>
       <c r="H13" t="n">
-        <v>41729</v>
+        <v>51115</v>
       </c>
       <c r="I13" t="n">
-        <v>56486</v>
+        <v>46530</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="b">
@@ -1131,50 +1131,50 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>35997</v>
+        <v>51115</v>
       </c>
       <c r="O13" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>77.91</v>
+        <v>64.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>20489</v>
+        <v>4585</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b89c60f1</t>
+          <t>16dfb6a9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.59</v>
+        <v>84.78</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>199</v>
       </c>
       <c r="E14" t="n">
-        <v>84.52</v>
+        <v>46.01</v>
       </c>
       <c r="F14" t="n">
-        <v>34413</v>
+        <v>39190</v>
       </c>
       <c r="G14" t="n">
-        <v>71635</v>
+        <v>33678</v>
       </c>
       <c r="H14" t="n">
-        <v>67952</v>
+        <v>55944</v>
       </c>
       <c r="I14" t="n">
-        <v>44666</v>
+        <v>9516</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="b">
@@ -1183,50 +1183,50 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>34413</v>
+        <v>33678</v>
       </c>
       <c r="O14" t="n">
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="P14" t="n">
-        <v>89.52</v>
+        <v>53.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>10253</v>
+        <v>24162</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4e5e9962</t>
+          <t>3cf3038b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.31999999999999</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="E15" t="n">
-        <v>45.57</v>
+        <v>81.7</v>
       </c>
       <c r="F15" t="n">
-        <v>47467</v>
+        <v>76958</v>
       </c>
       <c r="G15" t="n">
-        <v>78744</v>
+        <v>34771</v>
       </c>
       <c r="H15" t="n">
-        <v>35592</v>
+        <v>73178</v>
       </c>
       <c r="I15" t="n">
-        <v>47954</v>
+        <v>60881</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="b">
@@ -1235,50 +1235,50 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>35592</v>
+        <v>34771</v>
       </c>
       <c r="O15" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="P15" t="n">
-        <v>53.57</v>
+        <v>83.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>12362</v>
+        <v>26110</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>59505669</t>
+          <t>c6bd25d7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32.07</v>
+        <v>44.27</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>486</v>
       </c>
       <c r="E16" t="n">
-        <v>29.69</v>
+        <v>60.14</v>
       </c>
       <c r="F16" t="n">
-        <v>60186</v>
+        <v>33620</v>
       </c>
       <c r="G16" t="n">
-        <v>49872</v>
+        <v>65580</v>
       </c>
       <c r="H16" t="n">
-        <v>51539</v>
+        <v>73826</v>
       </c>
       <c r="I16" t="n">
-        <v>78762</v>
+        <v>10371</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="b">
@@ -1287,50 +1287,50 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>49872</v>
+        <v>33620</v>
       </c>
       <c r="O16" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="P16" t="n">
-        <v>43.69</v>
+        <v>68.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>28890</v>
+        <v>23249</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27241491</t>
+          <t>a64f472e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>64.20999999999999</v>
+        <v>52.66</v>
       </c>
       <c r="D17" t="n">
-        <v>164</v>
+        <v>429</v>
       </c>
       <c r="E17" t="n">
-        <v>59.82</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>76486</v>
+        <v>38027</v>
       </c>
       <c r="G17" t="n">
-        <v>63710</v>
+        <v>30092</v>
       </c>
       <c r="H17" t="n">
-        <v>50140</v>
+        <v>73295</v>
       </c>
       <c r="I17" t="n">
-        <v>14339</v>
+        <v>65882</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="b">
@@ -1339,50 +1339,50 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>50140</v>
+        <v>30092</v>
       </c>
       <c r="O17" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>70.81999999999999</v>
+        <v>106.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>35801</v>
+        <v>35790</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>d8f81ff0</t>
+          <t>6580a0f7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>94.65000000000001</v>
+        <v>42.75</v>
       </c>
       <c r="D18" t="n">
-        <v>433</v>
+        <v>367</v>
       </c>
       <c r="E18" t="n">
-        <v>20.58</v>
+        <v>62.09</v>
       </c>
       <c r="F18" t="n">
-        <v>41234</v>
+        <v>77173</v>
       </c>
       <c r="G18" t="n">
-        <v>51270</v>
+        <v>44996</v>
       </c>
       <c r="H18" t="n">
-        <v>75670</v>
+        <v>52535</v>
       </c>
       <c r="I18" t="n">
-        <v>36384</v>
+        <v>76215</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="b">
@@ -1391,50 +1391,50 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>41234</v>
+        <v>44996</v>
       </c>
       <c r="O18" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="P18" t="n">
-        <v>30.58</v>
+        <v>72.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>4850</v>
+        <v>31219</v>
       </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0eef2532</t>
+          <t>f16788f6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Apple Pixel 8</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>52.11</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>66.45</v>
+        <v>35.69</v>
       </c>
       <c r="F19" t="n">
-        <v>65519</v>
+        <v>36931</v>
       </c>
       <c r="G19" t="n">
-        <v>63148</v>
+        <v>46308</v>
       </c>
       <c r="H19" t="n">
-        <v>66817</v>
+        <v>73164</v>
       </c>
       <c r="I19" t="n">
-        <v>19603</v>
+        <v>40956</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="b">
@@ -1443,50 +1443,50 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>63148</v>
+        <v>36931</v>
       </c>
       <c r="O19" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="P19" t="n">
-        <v>68.45</v>
+        <v>43.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>43545</v>
+        <v>4025</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23755b15</t>
+          <t>0c45c8dc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>OnePlus Edge 40</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.02</v>
+        <v>79.55</v>
       </c>
       <c r="D20" t="n">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="E20" t="n">
-        <v>62.04</v>
+        <v>80.13</v>
       </c>
       <c r="F20" t="n">
-        <v>58427</v>
+        <v>79016</v>
       </c>
       <c r="G20" t="n">
-        <v>32269</v>
+        <v>71858</v>
       </c>
       <c r="H20" t="n">
-        <v>33693</v>
+        <v>46448</v>
       </c>
       <c r="I20" t="n">
-        <v>12195</v>
+        <v>29582</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="b">
@@ -1495,50 +1495,50 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>32269</v>
+        <v>46448</v>
       </c>
       <c r="O20" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="P20" t="n">
-        <v>70.03999999999999</v>
+        <v>92.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>20074</v>
+        <v>16866</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11788d5e</t>
+          <t>d0a165bd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.40000000000001</v>
+        <v>42.06</v>
       </c>
       <c r="D21" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="E21" t="n">
-        <v>93.01000000000001</v>
+        <v>69.42</v>
       </c>
       <c r="F21" t="n">
-        <v>58591</v>
+        <v>32493</v>
       </c>
       <c r="G21" t="n">
-        <v>55269</v>
+        <v>42499</v>
       </c>
       <c r="H21" t="n">
-        <v>52217</v>
+        <v>61989</v>
       </c>
       <c r="I21" t="n">
-        <v>29046</v>
+        <v>57832</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="b">
@@ -1547,50 +1547,50 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>52217</v>
+        <v>32493</v>
       </c>
       <c r="O21" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="P21" t="n">
-        <v>99.01000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>23171</v>
+        <v>25339</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2eb32247</t>
+          <t>8aa3fca1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54.94</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="E22" t="n">
-        <v>99.34</v>
+        <v>85.53</v>
       </c>
       <c r="F22" t="n">
-        <v>62515</v>
+        <v>54544</v>
       </c>
       <c r="G22" t="n">
-        <v>52241</v>
+        <v>52745</v>
       </c>
       <c r="H22" t="n">
-        <v>67471</v>
+        <v>52965</v>
       </c>
       <c r="I22" t="n">
-        <v>35386</v>
+        <v>31439</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="b">
@@ -1599,50 +1599,50 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>52241</v>
+        <v>52745</v>
       </c>
       <c r="O22" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="P22" t="n">
-        <v>108.34</v>
+        <v>92.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>16855</v>
+        <v>21306</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e87194b0</t>
+          <t>152d024f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49.18</v>
+        <v>42.63</v>
       </c>
       <c r="D23" t="n">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="E23" t="n">
-        <v>94.63</v>
+        <v>59.39</v>
       </c>
       <c r="F23" t="n">
-        <v>46164</v>
+        <v>57206</v>
       </c>
       <c r="G23" t="n">
-        <v>77719</v>
+        <v>50047</v>
       </c>
       <c r="H23" t="n">
-        <v>63979</v>
+        <v>31289</v>
       </c>
       <c r="I23" t="n">
-        <v>22299</v>
+        <v>24140</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="b">
@@ -1651,50 +1651,50 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>46164</v>
+        <v>31289</v>
       </c>
       <c r="O23" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="P23" t="n">
-        <v>99.63</v>
+        <v>62.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>23865</v>
+        <v>7149</v>
       </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2d35206a</t>
+          <t>57124b4f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>96.14</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="E24" t="n">
-        <v>24.72</v>
+        <v>31.83</v>
       </c>
       <c r="F24" t="n">
-        <v>75683</v>
+        <v>37466</v>
       </c>
       <c r="G24" t="n">
-        <v>46485</v>
+        <v>37200</v>
       </c>
       <c r="H24" t="n">
-        <v>76054</v>
+        <v>60309</v>
       </c>
       <c r="I24" t="n">
-        <v>48685</v>
+        <v>33811</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="b">
@@ -1703,23 +1703,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>46485</v>
+        <v>37200</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="P24" t="n">
-        <v>34.72</v>
+        <v>36.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2200</v>
+        <v>3389</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b0a79e0d</t>
+          <t>8147ee8d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1728,25 +1728,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44.9</v>
+        <v>45.62</v>
       </c>
       <c r="D25" t="n">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E25" t="n">
-        <v>20.11</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>30741</v>
+        <v>32969</v>
       </c>
       <c r="G25" t="n">
-        <v>63591</v>
+        <v>42236</v>
       </c>
       <c r="H25" t="n">
-        <v>39703</v>
+        <v>55801</v>
       </c>
       <c r="I25" t="n">
-        <v>34140</v>
+        <v>28589</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="b">
@@ -1755,50 +1755,50 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>30741</v>
+        <v>32969</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="P25" t="n">
-        <v>34.11</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>3399</v>
+        <v>4380</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>64ac0db3</t>
+          <t>8e8d5e73</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84.40000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="D26" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E26" t="n">
-        <v>52.21</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>67639</v>
+        <v>42747</v>
       </c>
       <c r="G26" t="n">
-        <v>30913</v>
+        <v>34826</v>
       </c>
       <c r="H26" t="n">
-        <v>31455</v>
+        <v>47648</v>
       </c>
       <c r="I26" t="n">
-        <v>69126</v>
+        <v>30959</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="b">
@@ -1807,50 +1807,50 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>30913</v>
+        <v>34826</v>
       </c>
       <c r="O26" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="P26" t="n">
-        <v>55.21</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>38213</v>
+        <v>3867</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d41ae22e</t>
+          <t>c15426e4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30.15</v>
+        <v>35.73</v>
       </c>
       <c r="D27" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E27" t="n">
-        <v>77.39</v>
+        <v>85.81</v>
       </c>
       <c r="F27" t="n">
-        <v>52662</v>
+        <v>52086</v>
       </c>
       <c r="G27" t="n">
-        <v>69719</v>
+        <v>34550</v>
       </c>
       <c r="H27" t="n">
-        <v>57924</v>
+        <v>51832</v>
       </c>
       <c r="I27" t="n">
-        <v>29772</v>
+        <v>69488</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="b">
@@ -1859,50 +1859,50 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>52662</v>
+        <v>34550</v>
       </c>
       <c r="O27" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="P27" t="n">
-        <v>86.39</v>
+        <v>89.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>22890</v>
+        <v>34938</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8f133de7</t>
+          <t>908b26f1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43.22</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>283</v>
+        <v>420</v>
       </c>
       <c r="E28" t="n">
-        <v>58.59</v>
+        <v>53.75</v>
       </c>
       <c r="F28" t="n">
-        <v>51378</v>
+        <v>66215</v>
       </c>
       <c r="G28" t="n">
-        <v>68673</v>
+        <v>56429</v>
       </c>
       <c r="H28" t="n">
-        <v>37072</v>
+        <v>74057</v>
       </c>
       <c r="I28" t="n">
-        <v>35445</v>
+        <v>71511</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="b">
@@ -1911,50 +1911,50 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>37072</v>
+        <v>56429</v>
       </c>
       <c r="O28" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="P28" t="n">
-        <v>63.59</v>
+        <v>61.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>1627</v>
+        <v>15082</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4469fede</t>
+          <t>e54090ed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>70.42</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="E29" t="n">
-        <v>81.58</v>
+        <v>58.45</v>
       </c>
       <c r="F29" t="n">
-        <v>43681</v>
+        <v>39745</v>
       </c>
       <c r="G29" t="n">
-        <v>47151</v>
+        <v>49721</v>
       </c>
       <c r="H29" t="n">
-        <v>34567</v>
+        <v>75013</v>
       </c>
       <c r="I29" t="n">
-        <v>54499</v>
+        <v>72422</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="b">
@@ -1963,23 +1963,23 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>34567</v>
+        <v>39745</v>
       </c>
       <c r="O29" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>93.58</v>
+        <v>61.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>19932</v>
+        <v>32677</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0d41975d</t>
+          <t>39e9bc47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1988,25 +1988,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>95.44</v>
+        <v>83.8</v>
       </c>
       <c r="D30" t="n">
-        <v>274</v>
+        <v>422</v>
       </c>
       <c r="E30" t="n">
-        <v>51.88</v>
+        <v>79.12</v>
       </c>
       <c r="F30" t="n">
-        <v>49739</v>
+        <v>32045</v>
       </c>
       <c r="G30" t="n">
-        <v>67521</v>
+        <v>62201</v>
       </c>
       <c r="H30" t="n">
-        <v>30783</v>
+        <v>75780</v>
       </c>
       <c r="I30" t="n">
-        <v>69831</v>
+        <v>26839</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="b">
@@ -2015,50 +2015,50 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>30783</v>
+        <v>32045</v>
       </c>
       <c r="O30" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="P30" t="n">
-        <v>58.88</v>
+        <v>92.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>39048</v>
+        <v>5206</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>188ecac6</t>
+          <t>e102768a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70.61</v>
+        <v>35.91</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>471</v>
       </c>
       <c r="E31" t="n">
-        <v>27.37</v>
+        <v>99.34</v>
       </c>
       <c r="F31" t="n">
-        <v>50589</v>
+        <v>57987</v>
       </c>
       <c r="G31" t="n">
-        <v>70856</v>
+        <v>52629</v>
       </c>
       <c r="H31" t="n">
-        <v>37723</v>
+        <v>35627</v>
       </c>
       <c r="I31" t="n">
-        <v>46084</v>
+        <v>13447</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="b">
@@ -2067,50 +2067,50 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>37723</v>
+        <v>35627</v>
       </c>
       <c r="O31" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="P31" t="n">
-        <v>37.37</v>
+        <v>112.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>8361</v>
+        <v>22180</v>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ece4051a</t>
+          <t>692008cb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>48.62</v>
+        <v>71.06</v>
       </c>
       <c r="D32" t="n">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>12.09</v>
+        <v>19.9</v>
       </c>
       <c r="F32" t="n">
-        <v>75230</v>
+        <v>37413</v>
       </c>
       <c r="G32" t="n">
-        <v>31157</v>
+        <v>65647</v>
       </c>
       <c r="H32" t="n">
-        <v>36039</v>
+        <v>70755</v>
       </c>
       <c r="I32" t="n">
-        <v>60969</v>
+        <v>27130</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="b">
@@ -2119,50 +2119,50 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>31157</v>
+        <v>37413</v>
       </c>
       <c r="O32" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="P32" t="n">
-        <v>23.09</v>
+        <v>23.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>29812</v>
+        <v>10283</v>
       </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6b56438a</t>
+          <t>dd8f13db</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>93.23999999999999</v>
+        <v>84.77</v>
       </c>
       <c r="D33" t="n">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="E33" t="n">
-        <v>99.06999999999999</v>
+        <v>62.57</v>
       </c>
       <c r="F33" t="n">
-        <v>31406</v>
+        <v>46522</v>
       </c>
       <c r="G33" t="n">
-        <v>55433</v>
+        <v>57043</v>
       </c>
       <c r="H33" t="n">
-        <v>38279</v>
+        <v>67923</v>
       </c>
       <c r="I33" t="n">
-        <v>65998</v>
+        <v>23587</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="b">
@@ -2171,50 +2171,50 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>31406</v>
+        <v>46522</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="P33" t="n">
-        <v>105.07</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>34592</v>
+        <v>22935</v>
       </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b68db4d5</t>
+          <t>d64bcad3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64.37</v>
+        <v>42.91</v>
       </c>
       <c r="D34" t="n">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="E34" t="n">
-        <v>55.38</v>
+        <v>69.59</v>
       </c>
       <c r="F34" t="n">
-        <v>35346</v>
+        <v>62729</v>
       </c>
       <c r="G34" t="n">
-        <v>63190</v>
+        <v>77660</v>
       </c>
       <c r="H34" t="n">
-        <v>52861</v>
+        <v>73715</v>
       </c>
       <c r="I34" t="n">
-        <v>30491</v>
+        <v>78676</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="b">
@@ -2223,50 +2223,50 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>35346</v>
+        <v>62729</v>
       </c>
       <c r="O34" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="P34" t="n">
-        <v>69.38</v>
+        <v>73.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>4855</v>
+        <v>15947</v>
       </c>
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1e3bf9ea</t>
+          <t>dbd04758</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>31.39</v>
+        <v>52.28</v>
       </c>
       <c r="D35" t="n">
-        <v>189</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>45.4</v>
+        <v>46.24</v>
       </c>
       <c r="F35" t="n">
-        <v>55983</v>
+        <v>31078</v>
       </c>
       <c r="G35" t="n">
-        <v>36558</v>
+        <v>77828</v>
       </c>
       <c r="H35" t="n">
-        <v>72605</v>
+        <v>63513</v>
       </c>
       <c r="I35" t="n">
-        <v>47335</v>
+        <v>46222</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="b">
@@ -2275,50 +2275,50 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>36558</v>
+        <v>31078</v>
       </c>
       <c r="O35" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="P35" t="n">
-        <v>53.4</v>
+        <v>55.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>10777</v>
+        <v>15144</v>
       </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>331b5a89</t>
+          <t>1c6ac36e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>65.78</v>
+        <v>99.36</v>
       </c>
       <c r="D36" t="n">
-        <v>390</v>
+        <v>94</v>
       </c>
       <c r="E36" t="n">
-        <v>38.57</v>
+        <v>74.59</v>
       </c>
       <c r="F36" t="n">
-        <v>40088</v>
+        <v>74657</v>
       </c>
       <c r="G36" t="n">
-        <v>38530</v>
+        <v>77091</v>
       </c>
       <c r="H36" t="n">
-        <v>47280</v>
+        <v>35317</v>
       </c>
       <c r="I36" t="n">
-        <v>40224</v>
+        <v>20730</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="b">
@@ -2327,50 +2327,50 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>38530</v>
+        <v>35317</v>
       </c>
       <c r="O36" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="P36" t="n">
-        <v>50.57</v>
+        <v>83.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>1694</v>
+        <v>14587</v>
       </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>e8d939d9</t>
+          <t>b66544f2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Samsung CMF 2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>86.26000000000001</v>
+        <v>51.42</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>360</v>
       </c>
       <c r="E37" t="n">
-        <v>64.95</v>
+        <v>33.47</v>
       </c>
       <c r="F37" t="n">
-        <v>39368</v>
+        <v>30769</v>
       </c>
       <c r="G37" t="n">
-        <v>67039</v>
+        <v>42678</v>
       </c>
       <c r="H37" t="n">
-        <v>36341</v>
+        <v>43660</v>
       </c>
       <c r="I37" t="n">
-        <v>35970</v>
+        <v>41186</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="b">
@@ -2379,50 +2379,50 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>36341</v>
+        <v>30769</v>
       </c>
       <c r="O37" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="P37" t="n">
-        <v>69.95</v>
+        <v>41.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>371</v>
+        <v>10417</v>
       </c>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>664f8336</t>
+          <t>8f0f9c78</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69.14</v>
+        <v>88.58</v>
       </c>
       <c r="D38" t="n">
-        <v>332</v>
+        <v>405</v>
       </c>
       <c r="E38" t="n">
-        <v>12.56</v>
+        <v>24.65</v>
       </c>
       <c r="F38" t="n">
-        <v>54021</v>
+        <v>32711</v>
       </c>
       <c r="G38" t="n">
-        <v>46709</v>
+        <v>60129</v>
       </c>
       <c r="H38" t="n">
-        <v>63040</v>
+        <v>60747</v>
       </c>
       <c r="I38" t="n">
-        <v>74955</v>
+        <v>73352</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="b">
@@ -2431,50 +2431,50 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>46709</v>
+        <v>32711</v>
       </c>
       <c r="O38" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="P38" t="n">
-        <v>23.56</v>
+        <v>32.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>28246</v>
+        <v>40641</v>
       </c>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>b8804fa0</t>
+          <t>77c3a4f4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Realme 14</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>66.54000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="D39" t="n">
-        <v>435</v>
+        <v>191</v>
       </c>
       <c r="E39" t="n">
-        <v>61.36</v>
+        <v>43.42</v>
       </c>
       <c r="F39" t="n">
-        <v>62238</v>
+        <v>76756</v>
       </c>
       <c r="G39" t="n">
-        <v>71989</v>
+        <v>54934</v>
       </c>
       <c r="H39" t="n">
-        <v>41779</v>
+        <v>59725</v>
       </c>
       <c r="I39" t="n">
-        <v>44130</v>
+        <v>31902</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="b">
@@ -2483,50 +2483,50 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>41779</v>
+        <v>54934</v>
       </c>
       <c r="O39" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="P39" t="n">
-        <v>64.36</v>
+        <v>50.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>2351</v>
+        <v>23032</v>
       </c>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>83c1229d</t>
+          <t>688c3b9f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>48.21</v>
+        <v>79.66</v>
       </c>
       <c r="D40" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E40" t="n">
-        <v>85.56999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="F40" t="n">
-        <v>34461</v>
+        <v>55309</v>
       </c>
       <c r="G40" t="n">
-        <v>35799</v>
+        <v>51347</v>
       </c>
       <c r="H40" t="n">
-        <v>52985</v>
+        <v>53385</v>
       </c>
       <c r="I40" t="n">
-        <v>38756</v>
+        <v>64993</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="b">
@@ -2535,50 +2535,50 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>34461</v>
+        <v>51347</v>
       </c>
       <c r="O40" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="P40" t="n">
-        <v>93.56999999999999</v>
+        <v>19.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>4295</v>
+        <v>13646</v>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>112de73a</t>
+          <t>9b7a2c88</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>89.47</v>
+        <v>76.56</v>
       </c>
       <c r="D41" t="n">
-        <v>317</v>
+        <v>116</v>
       </c>
       <c r="E41" t="n">
-        <v>33.16</v>
+        <v>16.6</v>
       </c>
       <c r="F41" t="n">
-        <v>40772</v>
+        <v>71742</v>
       </c>
       <c r="G41" t="n">
-        <v>71841</v>
+        <v>55560</v>
       </c>
       <c r="H41" t="n">
-        <v>33051</v>
+        <v>44108</v>
       </c>
       <c r="I41" t="n">
-        <v>70333</v>
+        <v>9434</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="b">
@@ -2587,50 +2587,50 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>33051</v>
+        <v>44108</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="P41" t="n">
-        <v>38.16</v>
+        <v>26.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>37282</v>
+        <v>34674</v>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>c059df07</t>
+          <t>c776197b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>Realme Nord</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>62.08</v>
+        <v>48.25</v>
       </c>
       <c r="D42" t="n">
-        <v>333</v>
+        <v>265</v>
       </c>
       <c r="E42" t="n">
-        <v>21.47</v>
+        <v>59.26</v>
       </c>
       <c r="F42" t="n">
-        <v>55237</v>
+        <v>43817</v>
       </c>
       <c r="G42" t="n">
-        <v>35553</v>
+        <v>75099</v>
       </c>
       <c r="H42" t="n">
-        <v>67242</v>
+        <v>76834</v>
       </c>
       <c r="I42" t="n">
-        <v>24464</v>
+        <v>58578</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="b">
@@ -2639,50 +2639,50 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>35553</v>
+        <v>43817</v>
       </c>
       <c r="O42" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="P42" t="n">
-        <v>32.47</v>
+        <v>71.25999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>11089</v>
+        <v>14761</v>
       </c>
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>eb765eea</t>
+          <t>e8a2d794</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>51.05</v>
+        <v>34.39</v>
       </c>
       <c r="D43" t="n">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="E43" t="n">
-        <v>99.09</v>
+        <v>70.39</v>
       </c>
       <c r="F43" t="n">
-        <v>52412</v>
+        <v>77586</v>
       </c>
       <c r="G43" t="n">
-        <v>50641</v>
+        <v>71885</v>
       </c>
       <c r="H43" t="n">
-        <v>73434</v>
+        <v>72311</v>
       </c>
       <c r="I43" t="n">
-        <v>35641</v>
+        <v>27478</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="b">
@@ -2691,50 +2691,50 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>50641</v>
+        <v>71885</v>
       </c>
       <c r="O43" t="n">
-        <v>0.68</v>
+        <v>0.87</v>
       </c>
       <c r="P43" t="n">
-        <v>110.09</v>
+        <v>77.39</v>
       </c>
       <c r="Q43" t="n">
-        <v>15000</v>
+        <v>44407</v>
       </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5fd46adf</t>
+          <t>0b31a5ca</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>92.34</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>161</v>
+        <v>399</v>
       </c>
       <c r="E44" t="n">
-        <v>89.59</v>
+        <v>48.47</v>
       </c>
       <c r="F44" t="n">
-        <v>50452</v>
+        <v>55632</v>
       </c>
       <c r="G44" t="n">
-        <v>37911</v>
+        <v>36960</v>
       </c>
       <c r="H44" t="n">
-        <v>76390</v>
+        <v>69029</v>
       </c>
       <c r="I44" t="n">
-        <v>21915</v>
+        <v>28482</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="b">
@@ -2743,50 +2743,50 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>37911</v>
+        <v>36960</v>
       </c>
       <c r="O44" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="P44" t="n">
-        <v>91.59</v>
+        <v>57.47</v>
       </c>
       <c r="Q44" t="n">
-        <v>15996</v>
+        <v>8478</v>
       </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f313a21d</t>
+          <t>79c9efc7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.01</v>
+        <v>77.17</v>
       </c>
       <c r="D45" t="n">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="E45" t="n">
-        <v>15.49</v>
+        <v>60.12</v>
       </c>
       <c r="F45" t="n">
-        <v>34705</v>
+        <v>57802</v>
       </c>
       <c r="G45" t="n">
-        <v>33111</v>
+        <v>62017</v>
       </c>
       <c r="H45" t="n">
-        <v>50408</v>
+        <v>74042</v>
       </c>
       <c r="I45" t="n">
-        <v>25285</v>
+        <v>8561</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="b">
@@ -2795,50 +2795,50 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>33111</v>
+        <v>57802</v>
       </c>
       <c r="O45" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="P45" t="n">
-        <v>21.49</v>
+        <v>63.12</v>
       </c>
       <c r="Q45" t="n">
-        <v>7826</v>
+        <v>49241</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>86a2e61e</t>
+          <t>c5ed9e64</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xiaomi Nord</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>96.28</v>
+        <v>95.05</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>407</v>
       </c>
       <c r="E46" t="n">
-        <v>49.92</v>
+        <v>27.61</v>
       </c>
       <c r="F46" t="n">
-        <v>37629</v>
+        <v>34014</v>
       </c>
       <c r="G46" t="n">
-        <v>70842</v>
+        <v>64765</v>
       </c>
       <c r="H46" t="n">
-        <v>30306</v>
+        <v>53492</v>
       </c>
       <c r="I46" t="n">
-        <v>33874</v>
+        <v>69662</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="b">
@@ -2847,50 +2847,50 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>30306</v>
+        <v>34014</v>
       </c>
       <c r="O46" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="P46" t="n">
-        <v>51.92</v>
+        <v>32.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>3568</v>
+        <v>35648</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>233db855</t>
+          <t>28ec7d9d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>30.03</v>
+        <v>68</v>
       </c>
       <c r="D47" t="n">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="E47" t="n">
-        <v>72.45</v>
+        <v>26.96</v>
       </c>
       <c r="F47" t="n">
-        <v>44290</v>
+        <v>72911</v>
       </c>
       <c r="G47" t="n">
-        <v>47206</v>
+        <v>55323</v>
       </c>
       <c r="H47" t="n">
-        <v>34178</v>
+        <v>35436</v>
       </c>
       <c r="I47" t="n">
-        <v>19742</v>
+        <v>42803</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="b">
@@ -2899,50 +2899,50 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>34178</v>
+        <v>35436</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="P47" t="n">
-        <v>78.45</v>
+        <v>34.96</v>
       </c>
       <c r="Q47" t="n">
-        <v>14436</v>
+        <v>7367</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>050fe045</t>
+          <t>d4765d12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>56.8</v>
+        <v>79.16</v>
       </c>
       <c r="D48" t="n">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="E48" t="n">
-        <v>49.54</v>
+        <v>61.87</v>
       </c>
       <c r="F48" t="n">
-        <v>37227</v>
+        <v>42099</v>
       </c>
       <c r="G48" t="n">
-        <v>60712</v>
+        <v>42802</v>
       </c>
       <c r="H48" t="n">
-        <v>74798</v>
+        <v>67699</v>
       </c>
       <c r="I48" t="n">
-        <v>54225</v>
+        <v>16204</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="b">
@@ -2951,50 +2951,50 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>37227</v>
+        <v>42099</v>
       </c>
       <c r="O48" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>55.54</v>
+        <v>63.87</v>
       </c>
       <c r="Q48" t="n">
-        <v>16998</v>
+        <v>25895</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>c3ffbced</t>
+          <t>2c0ee14f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>83.19</v>
+        <v>30.3</v>
       </c>
       <c r="D49" t="n">
-        <v>46</v>
+        <v>316</v>
       </c>
       <c r="E49" t="n">
-        <v>42.97</v>
+        <v>24.04</v>
       </c>
       <c r="F49" t="n">
-        <v>44103</v>
+        <v>62475</v>
       </c>
       <c r="G49" t="n">
-        <v>34570</v>
+        <v>52430</v>
       </c>
       <c r="H49" t="n">
-        <v>67760</v>
+        <v>53178</v>
       </c>
       <c r="I49" t="n">
-        <v>40052</v>
+        <v>41519</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="b">
@@ -3003,23 +3003,23 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>34570</v>
+        <v>52430</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="P49" t="n">
-        <v>56.97</v>
+        <v>28.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>5482</v>
+        <v>10911</v>
       </c>
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>a82689d7</t>
+          <t>10881498</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3028,25 +3028,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>82.53</v>
+        <v>66.75</v>
       </c>
       <c r="D50" t="n">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="E50" t="n">
-        <v>10.84</v>
+        <v>96.3</v>
       </c>
       <c r="F50" t="n">
-        <v>78849</v>
+        <v>50664</v>
       </c>
       <c r="G50" t="n">
-        <v>67629</v>
+        <v>65871</v>
       </c>
       <c r="H50" t="n">
-        <v>56596</v>
+        <v>73156</v>
       </c>
       <c r="I50" t="n">
-        <v>47571</v>
+        <v>14907</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="b">
@@ -3055,50 +3055,50 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>56596</v>
+        <v>50664</v>
       </c>
       <c r="O50" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="P50" t="n">
-        <v>15.84</v>
+        <v>106.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>9025</v>
+        <v>35757</v>
       </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>e01af7c7</t>
+          <t>1fff00d8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Xiaomi S23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>71.29000000000001</v>
+        <v>53.35</v>
       </c>
       <c r="D51" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>89.64</v>
+        <v>10.89</v>
       </c>
       <c r="F51" t="n">
-        <v>31367</v>
+        <v>55766</v>
       </c>
       <c r="G51" t="n">
-        <v>56714</v>
+        <v>72339</v>
       </c>
       <c r="H51" t="n">
-        <v>53419</v>
+        <v>66662</v>
       </c>
       <c r="I51" t="n">
-        <v>69710</v>
+        <v>36158</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="b">
@@ -3107,50 +3107,50 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>31367</v>
+        <v>55766</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="P51" t="n">
-        <v>99.64</v>
+        <v>21.89</v>
       </c>
       <c r="Q51" t="n">
-        <v>38343</v>
+        <v>19608</v>
       </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>46ffe27e</t>
+          <t>f315abe1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Xiaomi Edge 40</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67.15000000000001</v>
+        <v>77.12</v>
       </c>
       <c r="D52" t="n">
-        <v>478</v>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>92.87</v>
+        <v>68.56</v>
       </c>
       <c r="F52" t="n">
-        <v>31755</v>
+        <v>46411</v>
       </c>
       <c r="G52" t="n">
-        <v>35931</v>
+        <v>36806</v>
       </c>
       <c r="H52" t="n">
-        <v>41670</v>
+        <v>57799</v>
       </c>
       <c r="I52" t="n">
-        <v>77743</v>
+        <v>76057</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="b">
@@ -3159,50 +3159,50 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>31755</v>
+        <v>36806</v>
       </c>
       <c r="O52" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="P52" t="n">
-        <v>99.87</v>
+        <v>73.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>45988</v>
+        <v>39251</v>
       </c>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>708dfc5c</t>
+          <t>0c51b48f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60.46</v>
+        <v>96.67</v>
       </c>
       <c r="D53" t="n">
-        <v>260</v>
+        <v>476</v>
       </c>
       <c r="E53" t="n">
-        <v>95.95999999999999</v>
+        <v>22.05</v>
       </c>
       <c r="F53" t="n">
-        <v>78215</v>
+        <v>60911</v>
       </c>
       <c r="G53" t="n">
-        <v>46701</v>
+        <v>31894</v>
       </c>
       <c r="H53" t="n">
-        <v>67584</v>
+        <v>44040</v>
       </c>
       <c r="I53" t="n">
-        <v>33675</v>
+        <v>34979</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="b">
@@ -3211,50 +3211,50 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>46701</v>
+        <v>31894</v>
       </c>
       <c r="O53" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>104.96</v>
+        <v>31.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>13026</v>
+        <v>3085</v>
       </c>
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b532206d</t>
+          <t>39ffa08a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>34.89</v>
+        <v>92.3</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>424</v>
       </c>
       <c r="E54" t="n">
-        <v>91.27</v>
+        <v>31.01</v>
       </c>
       <c r="F54" t="n">
-        <v>74294</v>
+        <v>37558</v>
       </c>
       <c r="G54" t="n">
-        <v>79952</v>
+        <v>60546</v>
       </c>
       <c r="H54" t="n">
-        <v>72036</v>
+        <v>73430</v>
       </c>
       <c r="I54" t="n">
-        <v>17955</v>
+        <v>75543</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="b">
@@ -3263,50 +3263,50 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>72036</v>
+        <v>37558</v>
       </c>
       <c r="O54" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="P54" t="n">
-        <v>102.27</v>
+        <v>44.01000000000001</v>
       </c>
       <c r="Q54" t="n">
-        <v>54081</v>
+        <v>37985</v>
       </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>abac1f89</t>
+          <t>30b83482</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Xiaomi S23</t>
+          <t>Xiaomi 14</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>79.06999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D55" t="n">
-        <v>399</v>
+        <v>253</v>
       </c>
       <c r="E55" t="n">
-        <v>37.81</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>49898</v>
+        <v>53765</v>
       </c>
       <c r="G55" t="n">
-        <v>41977</v>
+        <v>68461</v>
       </c>
       <c r="H55" t="n">
-        <v>32914</v>
+        <v>50267</v>
       </c>
       <c r="I55" t="n">
-        <v>43126</v>
+        <v>59362</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="b">
@@ -3315,50 +3315,50 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>32914</v>
+        <v>50267</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P55" t="n">
-        <v>46.81</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>10212</v>
+        <v>9095</v>
       </c>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>f5c04ced</t>
+          <t>f2f6701e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Realme Edge 40</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>90.94</v>
+        <v>35.95</v>
       </c>
       <c r="D56" t="n">
-        <v>258</v>
+        <v>62</v>
       </c>
       <c r="E56" t="n">
-        <v>47.78</v>
+        <v>92.44</v>
       </c>
       <c r="F56" t="n">
-        <v>56683</v>
+        <v>43959</v>
       </c>
       <c r="G56" t="n">
-        <v>65820</v>
+        <v>44296</v>
       </c>
       <c r="H56" t="n">
-        <v>33338</v>
+        <v>74689</v>
       </c>
       <c r="I56" t="n">
-        <v>16233</v>
+        <v>17616</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="b">
@@ -3367,50 +3367,50 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>33338</v>
+        <v>43959</v>
       </c>
       <c r="O56" t="n">
-        <v>0.98</v>
+        <v>0.71</v>
       </c>
       <c r="P56" t="n">
-        <v>53.78</v>
+        <v>100.44</v>
       </c>
       <c r="Q56" t="n">
-        <v>17105</v>
+        <v>26343</v>
       </c>
       <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>862a340f</t>
+          <t>21acae54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apple Pixel 8</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>70</v>
+        <v>59.49</v>
       </c>
       <c r="D57" t="n">
-        <v>151</v>
+        <v>395</v>
       </c>
       <c r="E57" t="n">
-        <v>32.23</v>
+        <v>87.06</v>
       </c>
       <c r="F57" t="n">
-        <v>37102</v>
+        <v>67308</v>
       </c>
       <c r="G57" t="n">
-        <v>53285</v>
+        <v>66902</v>
       </c>
       <c r="H57" t="n">
-        <v>48286</v>
+        <v>49555</v>
       </c>
       <c r="I57" t="n">
-        <v>51077</v>
+        <v>53192</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="b">
@@ -3419,23 +3419,23 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>37102</v>
+        <v>49555</v>
       </c>
       <c r="O57" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="P57" t="n">
-        <v>41.23</v>
+        <v>89.06</v>
       </c>
       <c r="Q57" t="n">
-        <v>13975</v>
+        <v>3637</v>
       </c>
       <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9b83349c</t>
+          <t>ded3e69e</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>70.89</v>
+        <v>44.76</v>
       </c>
       <c r="D58" t="n">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="E58" t="n">
-        <v>77.98999999999999</v>
+        <v>38.69</v>
       </c>
       <c r="F58" t="n">
-        <v>62827</v>
+        <v>33830</v>
       </c>
       <c r="G58" t="n">
-        <v>67927</v>
+        <v>51674</v>
       </c>
       <c r="H58" t="n">
-        <v>71249</v>
+        <v>68483</v>
       </c>
       <c r="I58" t="n">
-        <v>55728</v>
+        <v>74799</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="b">
@@ -3471,50 +3471,50 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>62827</v>
+        <v>33830</v>
       </c>
       <c r="O58" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="P58" t="n">
-        <v>84.98999999999999</v>
+        <v>52.69</v>
       </c>
       <c r="Q58" t="n">
-        <v>7099</v>
+        <v>40969</v>
       </c>
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>e4b6acf6</t>
+          <t>ac53b3e2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apple Edge 40</t>
+          <t>Apple S23</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>87.08</v>
+        <v>93.83</v>
       </c>
       <c r="D59" t="n">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>12.77</v>
+        <v>30.95</v>
       </c>
       <c r="F59" t="n">
-        <v>60146</v>
+        <v>44466</v>
       </c>
       <c r="G59" t="n">
-        <v>64290</v>
+        <v>54305</v>
       </c>
       <c r="H59" t="n">
-        <v>62997</v>
+        <v>74260</v>
       </c>
       <c r="I59" t="n">
-        <v>78976</v>
+        <v>71088</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="b">
@@ -3523,50 +3523,50 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>60146</v>
+        <v>44466</v>
       </c>
       <c r="O59" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="P59" t="n">
-        <v>20.77</v>
+        <v>39.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>18830</v>
+        <v>26622</v>
       </c>
       <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ac030a9f</t>
+          <t>676d41a6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>60.31</v>
+        <v>53.62</v>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="E60" t="n">
-        <v>82.95999999999999</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>47565</v>
+        <v>58272</v>
       </c>
       <c r="G60" t="n">
-        <v>43712</v>
+        <v>49795</v>
       </c>
       <c r="H60" t="n">
-        <v>69244</v>
+        <v>44717</v>
       </c>
       <c r="I60" t="n">
-        <v>19926</v>
+        <v>35697</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="b">
@@ -3575,50 +3575,50 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>43712</v>
+        <v>44717</v>
       </c>
       <c r="O60" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="P60" t="n">
-        <v>84.95999999999999</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="Q60" t="n">
-        <v>23786</v>
+        <v>9020</v>
       </c>
       <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>949e6fa8</t>
+          <t>c393bc7b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apple Nord</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>42.57</v>
+        <v>97.77</v>
       </c>
       <c r="D61" t="n">
-        <v>125</v>
+        <v>457</v>
       </c>
       <c r="E61" t="n">
-        <v>91.06</v>
+        <v>54.75</v>
       </c>
       <c r="F61" t="n">
-        <v>46480</v>
+        <v>58576</v>
       </c>
       <c r="G61" t="n">
-        <v>71067</v>
+        <v>50753</v>
       </c>
       <c r="H61" t="n">
-        <v>39304</v>
+        <v>51968</v>
       </c>
       <c r="I61" t="n">
-        <v>22800</v>
+        <v>12492</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="b">
@@ -3627,50 +3627,50 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>39304</v>
+        <v>50753</v>
       </c>
       <c r="O61" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="P61" t="n">
-        <v>100.06</v>
+        <v>57.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>16504</v>
+        <v>38261</v>
       </c>
       <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>c09c1337</t>
+          <t>a5eaeda3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>96.93000000000001</v>
+        <v>81.91</v>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="E62" t="n">
-        <v>31.17</v>
+        <v>31.81</v>
       </c>
       <c r="F62" t="n">
-        <v>74807</v>
+        <v>37654</v>
       </c>
       <c r="G62" t="n">
-        <v>45158</v>
+        <v>42043</v>
       </c>
       <c r="H62" t="n">
-        <v>70631</v>
+        <v>70698</v>
       </c>
       <c r="I62" t="n">
-        <v>28203</v>
+        <v>13548</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="b">
@@ -3679,50 +3679,50 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>45158</v>
+        <v>37654</v>
       </c>
       <c r="O62" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="P62" t="n">
-        <v>33.17</v>
+        <v>37.81</v>
       </c>
       <c r="Q62" t="n">
-        <v>16955</v>
+        <v>24106</v>
       </c>
       <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>62b4a019</t>
+          <t>d04ee496</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Realme S23</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>81.15000000000001</v>
+        <v>38.24</v>
       </c>
       <c r="D63" t="n">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="E63" t="n">
-        <v>80.88</v>
+        <v>81.86</v>
       </c>
       <c r="F63" t="n">
-        <v>45068</v>
+        <v>50079</v>
       </c>
       <c r="G63" t="n">
-        <v>60749</v>
+        <v>62885</v>
       </c>
       <c r="H63" t="n">
-        <v>48100</v>
+        <v>33143</v>
       </c>
       <c r="I63" t="n">
-        <v>63892</v>
+        <v>18865</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="b">
@@ -3731,50 +3731,50 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>45068</v>
+        <v>33143</v>
       </c>
       <c r="O63" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="P63" t="n">
-        <v>85.88</v>
+        <v>90.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>18824</v>
+        <v>14278</v>
       </c>
       <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>79d63ef5</t>
+          <t>8d93d464</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>OnePlus 14</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>30.05</v>
+        <v>76.48</v>
       </c>
       <c r="D64" t="n">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="E64" t="n">
-        <v>40.21</v>
+        <v>49.2</v>
       </c>
       <c r="F64" t="n">
-        <v>68642</v>
+        <v>68533</v>
       </c>
       <c r="G64" t="n">
-        <v>47898</v>
+        <v>55395</v>
       </c>
       <c r="H64" t="n">
-        <v>67602</v>
+        <v>64975</v>
       </c>
       <c r="I64" t="n">
-        <v>46207</v>
+        <v>43254</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="b">
@@ -3783,50 +3783,50 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>47898</v>
+        <v>55395</v>
       </c>
       <c r="O64" t="n">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="P64" t="n">
-        <v>48.21</v>
+        <v>57.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>1691</v>
+        <v>12141</v>
       </c>
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>d592de68</t>
+          <t>a533ef22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>53.75</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>479</v>
+        <v>143</v>
       </c>
       <c r="E65" t="n">
-        <v>70.09999999999999</v>
+        <v>32.87</v>
       </c>
       <c r="F65" t="n">
-        <v>47185</v>
+        <v>61664</v>
       </c>
       <c r="G65" t="n">
-        <v>74472</v>
+        <v>53793</v>
       </c>
       <c r="H65" t="n">
-        <v>72264</v>
+        <v>68992</v>
       </c>
       <c r="I65" t="n">
-        <v>45189</v>
+        <v>17042</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="b">
@@ -3835,50 +3835,50 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>47185</v>
+        <v>53793</v>
       </c>
       <c r="O65" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P65" t="n">
-        <v>83.09999999999999</v>
+        <v>35.87</v>
       </c>
       <c r="Q65" t="n">
-        <v>1996</v>
+        <v>36751</v>
       </c>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>31b0abd2</t>
+          <t>cfe9f81e</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Samsung Nord</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>76.59999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="D66" t="n">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="E66" t="n">
-        <v>45.15</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>60551</v>
+        <v>53383</v>
       </c>
       <c r="G66" t="n">
-        <v>79282</v>
+        <v>34034</v>
       </c>
       <c r="H66" t="n">
-        <v>39363</v>
+        <v>64476</v>
       </c>
       <c r="I66" t="n">
-        <v>11045</v>
+        <v>52744</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="b">
@@ -3887,50 +3887,50 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>39363</v>
+        <v>34034</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="P66" t="n">
-        <v>53.15</v>
+        <v>38</v>
       </c>
       <c r="Q66" t="n">
-        <v>28318</v>
+        <v>18710</v>
       </c>
       <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26e38cb5</t>
+          <t>2c13d9ac</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>OnePlus CMF 2</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>54.15</v>
+        <v>30.33</v>
       </c>
       <c r="D67" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E67" t="n">
-        <v>93.66</v>
+        <v>55.91</v>
       </c>
       <c r="F67" t="n">
-        <v>53848</v>
+        <v>44523</v>
       </c>
       <c r="G67" t="n">
-        <v>66474</v>
+        <v>69734</v>
       </c>
       <c r="H67" t="n">
-        <v>70001</v>
+        <v>61482</v>
       </c>
       <c r="I67" t="n">
-        <v>53812</v>
+        <v>8235</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="b">
@@ -3939,50 +3939,50 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>53848</v>
+        <v>44523</v>
       </c>
       <c r="O67" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="P67" t="n">
-        <v>107.66</v>
+        <v>62.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>36</v>
+        <v>36288</v>
       </c>
       <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7737d3fe</t>
+          <t>53ab4f53</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OnePlus Nord</t>
+          <t>Samsung 14</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>72.43000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="D68" t="n">
-        <v>280</v>
+        <v>334</v>
       </c>
       <c r="E68" t="n">
-        <v>85.56</v>
+        <v>20.32</v>
       </c>
       <c r="F68" t="n">
-        <v>31302</v>
+        <v>33086</v>
       </c>
       <c r="G68" t="n">
-        <v>36301</v>
+        <v>36880</v>
       </c>
       <c r="H68" t="n">
-        <v>56156</v>
+        <v>40012</v>
       </c>
       <c r="I68" t="n">
-        <v>30107</v>
+        <v>31658</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="b">
@@ -3991,50 +3991,50 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>31302</v>
+        <v>33086</v>
       </c>
       <c r="O68" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="P68" t="n">
-        <v>92.56</v>
+        <v>33.32</v>
       </c>
       <c r="Q68" t="n">
-        <v>1195</v>
+        <v>1428</v>
       </c>
       <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fafcab69</t>
+          <t>491f3ead</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>78.97</v>
+        <v>78.67</v>
       </c>
       <c r="D69" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="E69" t="n">
-        <v>80.73999999999999</v>
+        <v>70.62</v>
       </c>
       <c r="F69" t="n">
-        <v>70741</v>
+        <v>51835</v>
       </c>
       <c r="G69" t="n">
-        <v>31554</v>
+        <v>74851</v>
       </c>
       <c r="H69" t="n">
-        <v>68967</v>
+        <v>71345</v>
       </c>
       <c r="I69" t="n">
-        <v>21185</v>
+        <v>46072</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="b">
@@ -4043,50 +4043,50 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>31554</v>
+        <v>51835</v>
       </c>
       <c r="O69" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="P69" t="n">
-        <v>90.73999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>10369</v>
+        <v>5763</v>
       </c>
       <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>93134ab2</t>
+          <t>94961b85</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Xiaomi CMF 2</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>87.64</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>443</v>
+        <v>175</v>
       </c>
       <c r="E70" t="n">
-        <v>36.6</v>
+        <v>96.06</v>
       </c>
       <c r="F70" t="n">
-        <v>35479</v>
+        <v>32401</v>
       </c>
       <c r="G70" t="n">
-        <v>41730</v>
+        <v>70522</v>
       </c>
       <c r="H70" t="n">
-        <v>65007</v>
+        <v>62097</v>
       </c>
       <c r="I70" t="n">
-        <v>17039</v>
+        <v>26107</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="b">
@@ -4095,50 +4095,50 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>35479</v>
+        <v>32401</v>
       </c>
       <c r="O70" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P70" t="n">
-        <v>46.6</v>
+        <v>110.06</v>
       </c>
       <c r="Q70" t="n">
-        <v>18440</v>
+        <v>6294</v>
       </c>
       <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>43282893</t>
+          <t>fd38f23c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsung 14</t>
+          <t>Apple Nord</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>84.53</v>
+        <v>96.22</v>
       </c>
       <c r="D71" t="n">
-        <v>487</v>
+        <v>449</v>
       </c>
       <c r="E71" t="n">
-        <v>38.63</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>77068</v>
+        <v>60759</v>
       </c>
       <c r="G71" t="n">
-        <v>53237</v>
+        <v>61962</v>
       </c>
       <c r="H71" t="n">
-        <v>31494</v>
+        <v>71752</v>
       </c>
       <c r="I71" t="n">
-        <v>53144</v>
+        <v>73994</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="b">
@@ -4147,50 +4147,50 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>31494</v>
+        <v>60759</v>
       </c>
       <c r="O71" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="P71" t="n">
-        <v>48.63</v>
+        <v>102.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>21650</v>
+        <v>13235</v>
       </c>
       <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>18096011</t>
+          <t>60be03cb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>60.98</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>405</v>
+        <v>203</v>
       </c>
       <c r="E72" t="n">
-        <v>56.4</v>
+        <v>43.81</v>
       </c>
       <c r="F72" t="n">
-        <v>47843</v>
+        <v>48762</v>
       </c>
       <c r="G72" t="n">
-        <v>44349</v>
+        <v>49207</v>
       </c>
       <c r="H72" t="n">
-        <v>55842</v>
+        <v>76169</v>
       </c>
       <c r="I72" t="n">
-        <v>39446</v>
+        <v>52655</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="b">
@@ -4199,50 +4199,50 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>44349</v>
+        <v>48762</v>
       </c>
       <c r="O72" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="P72" t="n">
-        <v>58.4</v>
+        <v>45.81</v>
       </c>
       <c r="Q72" t="n">
-        <v>4903</v>
+        <v>3893</v>
       </c>
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5c3f3ac5</t>
+          <t>33a84829</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>73.27</v>
+        <v>34.32</v>
       </c>
       <c r="D73" t="n">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="E73" t="n">
-        <v>91.67</v>
+        <v>46.03</v>
       </c>
       <c r="F73" t="n">
-        <v>52838</v>
+        <v>48941</v>
       </c>
       <c r="G73" t="n">
-        <v>70992</v>
+        <v>70300</v>
       </c>
       <c r="H73" t="n">
-        <v>65592</v>
+        <v>34691</v>
       </c>
       <c r="I73" t="n">
-        <v>35769</v>
+        <v>61343</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="b">
@@ -4251,50 +4251,50 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>52838</v>
+        <v>34691</v>
       </c>
       <c r="O73" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="P73" t="n">
-        <v>93.67</v>
+        <v>52.03</v>
       </c>
       <c r="Q73" t="n">
-        <v>17069</v>
+        <v>26652</v>
       </c>
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>919637e3</t>
+          <t>f2cad907</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OnePlus 14</t>
+          <t>Realme Pixel 8</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>81.43000000000001</v>
+        <v>59.77</v>
       </c>
       <c r="D74" t="n">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="E74" t="n">
-        <v>87.98</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>75231</v>
+        <v>58395</v>
       </c>
       <c r="G74" t="n">
-        <v>77871</v>
+        <v>37635</v>
       </c>
       <c r="H74" t="n">
-        <v>49459</v>
+        <v>30035</v>
       </c>
       <c r="I74" t="n">
-        <v>78264</v>
+        <v>23038</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="b">
@@ -4303,50 +4303,50 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
-        <v>49459</v>
+        <v>30035</v>
       </c>
       <c r="O74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="P74" t="n">
-        <v>101.98</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="Q74" t="n">
-        <v>28805</v>
+        <v>6997</v>
       </c>
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42cb68b8</t>
+          <t>e92de3f5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apple Pixel 8</t>
+          <t>Apple CMF 2</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>87</v>
+        <v>79.59</v>
       </c>
       <c r="D75" t="n">
-        <v>193</v>
+        <v>56</v>
       </c>
       <c r="E75" t="n">
-        <v>16.92</v>
+        <v>91.63</v>
       </c>
       <c r="F75" t="n">
-        <v>68868</v>
+        <v>52118</v>
       </c>
       <c r="G75" t="n">
-        <v>33723</v>
+        <v>54977</v>
       </c>
       <c r="H75" t="n">
-        <v>78644</v>
+        <v>65216</v>
       </c>
       <c r="I75" t="n">
-        <v>67967</v>
+        <v>42721</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="b">
@@ -4355,50 +4355,50 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>33723</v>
+        <v>52118</v>
       </c>
       <c r="O75" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="P75" t="n">
-        <v>19.92</v>
+        <v>93.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>34244</v>
+        <v>9397</v>
       </c>
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8b8a8b3b</t>
+          <t>8ba766fa</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realme Nord</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>44.49</v>
+        <v>72.66</v>
       </c>
       <c r="D76" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E76" t="n">
-        <v>52.88</v>
+        <v>16.9</v>
       </c>
       <c r="F76" t="n">
-        <v>37929</v>
+        <v>62206</v>
       </c>
       <c r="G76" t="n">
-        <v>34883</v>
+        <v>67410</v>
       </c>
       <c r="H76" t="n">
-        <v>71411</v>
+        <v>33651</v>
       </c>
       <c r="I76" t="n">
-        <v>15231</v>
+        <v>15784</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="b">
@@ -4407,50 +4407,50 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>34883</v>
+        <v>33651</v>
       </c>
       <c r="O76" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="P76" t="n">
-        <v>65.88</v>
+        <v>24.9</v>
       </c>
       <c r="Q76" t="n">
-        <v>19652</v>
+        <v>17867</v>
       </c>
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>844e77ad</t>
+          <t>3e9bd38a</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung Pixel 8</t>
+          <t>OnePlus S23</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>35.37</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>486</v>
+        <v>349</v>
       </c>
       <c r="E77" t="n">
-        <v>36.66</v>
+        <v>89.39</v>
       </c>
       <c r="F77" t="n">
-        <v>46094</v>
+        <v>51575</v>
       </c>
       <c r="G77" t="n">
-        <v>31691</v>
+        <v>69962</v>
       </c>
       <c r="H77" t="n">
-        <v>51414</v>
+        <v>55169</v>
       </c>
       <c r="I77" t="n">
-        <v>55777</v>
+        <v>41594</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="b">
@@ -4459,50 +4459,50 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>31691</v>
+        <v>51575</v>
       </c>
       <c r="O77" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="P77" t="n">
-        <v>46.66</v>
+        <v>99.39</v>
       </c>
       <c r="Q77" t="n">
-        <v>24086</v>
+        <v>9981</v>
       </c>
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1cebb73c</t>
+          <t>edbaab6c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>95.25</v>
+        <v>60.06</v>
       </c>
       <c r="D78" t="n">
-        <v>394</v>
+        <v>303</v>
       </c>
       <c r="E78" t="n">
-        <v>41.31</v>
+        <v>63.39</v>
       </c>
       <c r="F78" t="n">
-        <v>48207</v>
+        <v>45950</v>
       </c>
       <c r="G78" t="n">
-        <v>31472</v>
+        <v>32205</v>
       </c>
       <c r="H78" t="n">
-        <v>65831</v>
+        <v>40510</v>
       </c>
       <c r="I78" t="n">
-        <v>21222</v>
+        <v>13208</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="b">
@@ -4511,50 +4511,50 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>31472</v>
+        <v>32205</v>
       </c>
       <c r="O78" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="P78" t="n">
-        <v>46.31</v>
+        <v>66.39</v>
       </c>
       <c r="Q78" t="n">
-        <v>10250</v>
+        <v>18997</v>
       </c>
       <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>d284689c</t>
+          <t>a8a96c64</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Xiaomi 14</t>
+          <t>Samsung Pixel 8</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>35.83</v>
+        <v>80.72</v>
       </c>
       <c r="D79" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E79" t="n">
-        <v>44.52</v>
+        <v>31.79</v>
       </c>
       <c r="F79" t="n">
-        <v>58153</v>
+        <v>64076</v>
       </c>
       <c r="G79" t="n">
-        <v>64367</v>
+        <v>63449</v>
       </c>
       <c r="H79" t="n">
-        <v>43154</v>
+        <v>57423</v>
       </c>
       <c r="I79" t="n">
-        <v>13789</v>
+        <v>29686</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="b">
@@ -4563,50 +4563,50 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>43154</v>
+        <v>57423</v>
       </c>
       <c r="O79" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="P79" t="n">
-        <v>55.52</v>
+        <v>43.79</v>
       </c>
       <c r="Q79" t="n">
-        <v>29365</v>
+        <v>27737</v>
       </c>
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>787a823c</t>
+          <t>1efd635f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realme Pixel 8</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>99.86</v>
+        <v>70.69</v>
       </c>
       <c r="D80" t="n">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="E80" t="n">
-        <v>25.69</v>
+        <v>12.98</v>
       </c>
       <c r="F80" t="n">
-        <v>70927</v>
+        <v>70124</v>
       </c>
       <c r="G80" t="n">
-        <v>38245</v>
+        <v>59662</v>
       </c>
       <c r="H80" t="n">
-        <v>58394</v>
+        <v>65666</v>
       </c>
       <c r="I80" t="n">
-        <v>70957</v>
+        <v>71561</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="b">
@@ -4615,50 +4615,50 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>38245</v>
+        <v>59662</v>
       </c>
       <c r="O80" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="P80" t="n">
-        <v>36.69</v>
+        <v>16.98</v>
       </c>
       <c r="Q80" t="n">
-        <v>32712</v>
+        <v>11899</v>
       </c>
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>bf5d884a</t>
+          <t>d815bd6b</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Xiaomi CMF 2</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.27</v>
+        <v>64.42</v>
       </c>
       <c r="D81" t="n">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E81" t="n">
-        <v>87.26000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="F81" t="n">
-        <v>63330</v>
+        <v>67113</v>
       </c>
       <c r="G81" t="n">
-        <v>66742</v>
+        <v>40323</v>
       </c>
       <c r="H81" t="n">
-        <v>38491</v>
+        <v>36451</v>
       </c>
       <c r="I81" t="n">
-        <v>12414</v>
+        <v>60444</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="b">
@@ -4667,50 +4667,50 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>38491</v>
+        <v>36451</v>
       </c>
       <c r="O81" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="P81" t="n">
-        <v>95.26000000000001</v>
+        <v>91.53</v>
       </c>
       <c r="Q81" t="n">
-        <v>26077</v>
+        <v>23993</v>
       </c>
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f5a5a585</t>
+          <t>16fd0e4a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OnePlus CMF 2</t>
+          <t>Apple Pixel 8</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>87.54000000000001</v>
+        <v>66.16</v>
       </c>
       <c r="D82" t="n">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="E82" t="n">
-        <v>97.97</v>
+        <v>17.82</v>
       </c>
       <c r="F82" t="n">
-        <v>74687</v>
+        <v>51074</v>
       </c>
       <c r="G82" t="n">
-        <v>78990</v>
+        <v>67252</v>
       </c>
       <c r="H82" t="n">
-        <v>49549</v>
+        <v>37012</v>
       </c>
       <c r="I82" t="n">
-        <v>41235</v>
+        <v>9765</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="b">
@@ -4719,50 +4719,50 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>49549</v>
+        <v>37012</v>
       </c>
       <c r="O82" t="n">
         <v>0.92</v>
       </c>
       <c r="P82" t="n">
-        <v>99.97</v>
+        <v>24.82</v>
       </c>
       <c r="Q82" t="n">
-        <v>8314</v>
+        <v>27247</v>
       </c>
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09512998</t>
+          <t>33dbe531</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>75.68000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="D83" t="n">
-        <v>427</v>
+        <v>379</v>
       </c>
       <c r="E83" t="n">
-        <v>25</v>
+        <v>74.88</v>
       </c>
       <c r="F83" t="n">
-        <v>49715</v>
+        <v>34827</v>
       </c>
       <c r="G83" t="n">
-        <v>45663</v>
+        <v>56371</v>
       </c>
       <c r="H83" t="n">
-        <v>70257</v>
+        <v>54810</v>
       </c>
       <c r="I83" t="n">
-        <v>58081</v>
+        <v>69223</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="b">
@@ -4771,50 +4771,50 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>45663</v>
+        <v>34827</v>
       </c>
       <c r="O83" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="P83" t="n">
-        <v>38</v>
+        <v>77.88</v>
       </c>
       <c r="Q83" t="n">
-        <v>12418</v>
+        <v>34396</v>
       </c>
       <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>d9db35e0</t>
+          <t>6697ee2a</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Realme Edge 40</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>55.98</v>
+        <v>62.52</v>
       </c>
       <c r="D84" t="n">
-        <v>484</v>
+        <v>173</v>
       </c>
       <c r="E84" t="n">
-        <v>99.94</v>
+        <v>17.03</v>
       </c>
       <c r="F84" t="n">
-        <v>39142</v>
+        <v>70957</v>
       </c>
       <c r="G84" t="n">
-        <v>33910</v>
+        <v>47508</v>
       </c>
       <c r="H84" t="n">
-        <v>38113</v>
+        <v>79386</v>
       </c>
       <c r="I84" t="n">
-        <v>16636</v>
+        <v>32159</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="b">
@@ -4823,50 +4823,50 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>33910</v>
+        <v>47508</v>
       </c>
       <c r="O84" t="n">
-        <v>0.97</v>
+        <v>0.65</v>
       </c>
       <c r="P84" t="n">
-        <v>111.94</v>
+        <v>29.03</v>
       </c>
       <c r="Q84" t="n">
-        <v>17274</v>
+        <v>15349</v>
       </c>
       <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>829677c0</t>
+          <t>ccd5b755</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>OnePlus Nord</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>36.15</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="D85" t="n">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="E85" t="n">
-        <v>48.27</v>
+        <v>33.9</v>
       </c>
       <c r="F85" t="n">
-        <v>58874</v>
+        <v>32208</v>
       </c>
       <c r="G85" t="n">
-        <v>67726</v>
+        <v>39718</v>
       </c>
       <c r="H85" t="n">
-        <v>57251</v>
+        <v>60955</v>
       </c>
       <c r="I85" t="n">
-        <v>16162</v>
+        <v>76657</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="b">
@@ -4875,50 +4875,50 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>57251</v>
+        <v>32208</v>
       </c>
       <c r="O85" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P85" t="n">
-        <v>51.27</v>
+        <v>38.9</v>
       </c>
       <c r="Q85" t="n">
-        <v>41089</v>
+        <v>44449</v>
       </c>
       <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>568e716b</t>
+          <t>8c146d59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apple S23</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>62.42</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>170</v>
+        <v>329</v>
       </c>
       <c r="E86" t="n">
-        <v>94.64</v>
+        <v>59.25</v>
       </c>
       <c r="F86" t="n">
-        <v>47497</v>
+        <v>52201</v>
       </c>
       <c r="G86" t="n">
-        <v>71203</v>
+        <v>70652</v>
       </c>
       <c r="H86" t="n">
-        <v>61608</v>
+        <v>43614</v>
       </c>
       <c r="I86" t="n">
-        <v>32127</v>
+        <v>56258</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="b">
@@ -4927,50 +4927,50 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>47497</v>
+        <v>43614</v>
       </c>
       <c r="O86" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="P86" t="n">
-        <v>96.64</v>
+        <v>72.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>15370</v>
+        <v>12644</v>
       </c>
       <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07671fb7</t>
+          <t>b1b0d38f</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realme 14</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>92.38</v>
+        <v>87.34</v>
       </c>
       <c r="D87" t="n">
-        <v>27</v>
+        <v>463</v>
       </c>
       <c r="E87" t="n">
-        <v>77.43000000000001</v>
+        <v>12.23</v>
       </c>
       <c r="F87" t="n">
-        <v>55463</v>
+        <v>69028</v>
       </c>
       <c r="G87" t="n">
-        <v>41636</v>
+        <v>51335</v>
       </c>
       <c r="H87" t="n">
-        <v>78520</v>
+        <v>72947</v>
       </c>
       <c r="I87" t="n">
-        <v>21828</v>
+        <v>37650</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="b">
@@ -4979,50 +4979,50 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>41636</v>
+        <v>51335</v>
       </c>
       <c r="O87" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="P87" t="n">
-        <v>81.43000000000001</v>
+        <v>21.23</v>
       </c>
       <c r="Q87" t="n">
-        <v>19808</v>
+        <v>13685</v>
       </c>
       <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4a46d5e4</t>
+          <t>99ef2403</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OnePlus S23</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>78.89</v>
+        <v>37.75</v>
       </c>
       <c r="D88" t="n">
-        <v>365</v>
+        <v>193</v>
       </c>
       <c r="E88" t="n">
-        <v>87.56999999999999</v>
+        <v>70</v>
       </c>
       <c r="F88" t="n">
-        <v>43260</v>
+        <v>67626</v>
       </c>
       <c r="G88" t="n">
-        <v>71697</v>
+        <v>50816</v>
       </c>
       <c r="H88" t="n">
-        <v>70863</v>
+        <v>39754</v>
       </c>
       <c r="I88" t="n">
-        <v>64152</v>
+        <v>18968</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="b">
@@ -5031,50 +5031,50 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
-        <v>43260</v>
+        <v>39754</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="P88" t="n">
-        <v>90.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="Q88" t="n">
-        <v>20892</v>
+        <v>20786</v>
       </c>
       <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>24f7f09b</t>
+          <t>1aedeb97</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Samsung Edge 40</t>
+          <t>Apple Pixel 8</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>53.05</v>
+        <v>79.34</v>
       </c>
       <c r="D89" t="n">
-        <v>286</v>
+        <v>477</v>
       </c>
       <c r="E89" t="n">
-        <v>60.81</v>
+        <v>24.56</v>
       </c>
       <c r="F89" t="n">
-        <v>71583</v>
+        <v>73026</v>
       </c>
       <c r="G89" t="n">
-        <v>65518</v>
+        <v>69944</v>
       </c>
       <c r="H89" t="n">
-        <v>63856</v>
+        <v>46401</v>
       </c>
       <c r="I89" t="n">
-        <v>10483</v>
+        <v>10592</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="b">
@@ -5083,50 +5083,50 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>63856</v>
+        <v>46401</v>
       </c>
       <c r="O89" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="P89" t="n">
-        <v>72.81</v>
+        <v>32.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>53373</v>
+        <v>35809</v>
       </c>
       <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>dbae7ddc</t>
+          <t>71b17327</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apple CMF 2</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>30.1</v>
+        <v>53.46</v>
       </c>
       <c r="D90" t="n">
-        <v>272</v>
+        <v>128</v>
       </c>
       <c r="E90" t="n">
-        <v>35.41</v>
+        <v>88.87</v>
       </c>
       <c r="F90" t="n">
-        <v>66157</v>
+        <v>43720</v>
       </c>
       <c r="G90" t="n">
-        <v>50257</v>
+        <v>32349</v>
       </c>
       <c r="H90" t="n">
-        <v>52197</v>
+        <v>57959</v>
       </c>
       <c r="I90" t="n">
-        <v>34561</v>
+        <v>46570</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="b">
@@ -5135,50 +5135,50 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>50257</v>
+        <v>32349</v>
       </c>
       <c r="O90" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="P90" t="n">
-        <v>43.41</v>
+        <v>100.87</v>
       </c>
       <c r="Q90" t="n">
-        <v>15696</v>
+        <v>14221</v>
       </c>
       <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>73e99d28</t>
+          <t>73590c62</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Realme CMF 2</t>
+          <t>OnePlus Pixel 8</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>75.19</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>390</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
-        <v>62.94</v>
+        <v>63.68</v>
       </c>
       <c r="F91" t="n">
-        <v>44501</v>
+        <v>67584</v>
       </c>
       <c r="G91" t="n">
-        <v>60081</v>
+        <v>55935</v>
       </c>
       <c r="H91" t="n">
-        <v>70569</v>
+        <v>79458</v>
       </c>
       <c r="I91" t="n">
-        <v>26836</v>
+        <v>49499</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="b">
@@ -5187,50 +5187,50 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>44501</v>
+        <v>55935</v>
       </c>
       <c r="O91" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="P91" t="n">
-        <v>65.94</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="Q91" t="n">
-        <v>17665</v>
+        <v>6436</v>
       </c>
       <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1384f9a5</t>
+          <t>d7e990f4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>46.94</v>
+        <v>42.99</v>
       </c>
       <c r="D92" t="n">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="E92" t="n">
-        <v>24.97</v>
+        <v>83.72</v>
       </c>
       <c r="F92" t="n">
-        <v>48408</v>
+        <v>51904</v>
       </c>
       <c r="G92" t="n">
-        <v>54017</v>
+        <v>45096</v>
       </c>
       <c r="H92" t="n">
-        <v>54756</v>
+        <v>42596</v>
       </c>
       <c r="I92" t="n">
-        <v>33052</v>
+        <v>27424</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="b">
@@ -5239,50 +5239,50 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>48408</v>
+        <v>42596</v>
       </c>
       <c r="O92" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="P92" t="n">
-        <v>38.97</v>
+        <v>93.72</v>
       </c>
       <c r="Q92" t="n">
-        <v>15356</v>
+        <v>15172</v>
       </c>
       <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9127fffb</t>
+          <t>d8b48002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OnePlus Pixel 8</t>
+          <t>Xiaomi Nord</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>68.84</v>
+        <v>53.08</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="E93" t="n">
-        <v>76.51000000000001</v>
+        <v>41.57</v>
       </c>
       <c r="F93" t="n">
-        <v>56866</v>
+        <v>46452</v>
       </c>
       <c r="G93" t="n">
-        <v>47588</v>
+        <v>37830</v>
       </c>
       <c r="H93" t="n">
-        <v>67141</v>
+        <v>61050</v>
       </c>
       <c r="I93" t="n">
-        <v>17888</v>
+        <v>41670</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="b">
@@ -5291,50 +5291,50 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>47588</v>
+        <v>37830</v>
       </c>
       <c r="O93" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="P93" t="n">
-        <v>88.51000000000001</v>
+        <v>52.57</v>
       </c>
       <c r="Q93" t="n">
-        <v>29700</v>
+        <v>3840</v>
       </c>
       <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>f1e8726c</t>
+          <t>32189390</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Samsung S23</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>75.3</v>
+        <v>58.82</v>
       </c>
       <c r="D94" t="n">
-        <v>495</v>
+        <v>422</v>
       </c>
       <c r="E94" t="n">
-        <v>65.55</v>
+        <v>17.78</v>
       </c>
       <c r="F94" t="n">
-        <v>58467</v>
+        <v>68373</v>
       </c>
       <c r="G94" t="n">
-        <v>58382</v>
+        <v>31921</v>
       </c>
       <c r="H94" t="n">
-        <v>38366</v>
+        <v>59667</v>
       </c>
       <c r="I94" t="n">
-        <v>21831</v>
+        <v>53974</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="b">
@@ -5343,50 +5343,50 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>38366</v>
+        <v>31921</v>
       </c>
       <c r="O94" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="P94" t="n">
-        <v>74.55</v>
+        <v>30.78</v>
       </c>
       <c r="Q94" t="n">
-        <v>16535</v>
+        <v>22053</v>
       </c>
       <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0fed258a</t>
+          <t>86e8941f</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Xiaomi Edge 40</t>
+          <t>Apple 14</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>48.59</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D95" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E95" t="n">
-        <v>95.66</v>
+        <v>77.2</v>
       </c>
       <c r="F95" t="n">
-        <v>56895</v>
+        <v>30433</v>
       </c>
       <c r="G95" t="n">
-        <v>59688</v>
+        <v>47491</v>
       </c>
       <c r="H95" t="n">
-        <v>69687</v>
+        <v>45304</v>
       </c>
       <c r="I95" t="n">
-        <v>49337</v>
+        <v>69343</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="b">
@@ -5395,50 +5395,50 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>56895</v>
+        <v>30433</v>
       </c>
       <c r="O95" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="P95" t="n">
-        <v>109.66</v>
+        <v>88.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>7558</v>
+        <v>38910</v>
       </c>
       <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ca8e7c70</t>
+          <t>b4cbd920</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Xiaomi Pixel 8</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>46.03</v>
+        <v>51.57</v>
       </c>
       <c r="D96" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="E96" t="n">
-        <v>61.57</v>
+        <v>26.28</v>
       </c>
       <c r="F96" t="n">
-        <v>72371</v>
+        <v>31873</v>
       </c>
       <c r="G96" t="n">
-        <v>39257</v>
+        <v>60283</v>
       </c>
       <c r="H96" t="n">
-        <v>40703</v>
+        <v>76984</v>
       </c>
       <c r="I96" t="n">
-        <v>17500</v>
+        <v>68312</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="b">
@@ -5447,50 +5447,50 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>39257</v>
+        <v>31873</v>
       </c>
       <c r="O96" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P96" t="n">
-        <v>75.56999999999999</v>
+        <v>35.28</v>
       </c>
       <c r="Q96" t="n">
-        <v>21757</v>
+        <v>36439</v>
       </c>
       <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6b84d7e0</t>
+          <t>fdd80d69</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OnePlus Edge 40</t>
+          <t>Samsung Edge 40</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>91.06</v>
+        <v>79.39</v>
       </c>
       <c r="D97" t="n">
-        <v>236</v>
+        <v>86</v>
       </c>
       <c r="E97" t="n">
-        <v>40.36</v>
+        <v>73.91</v>
       </c>
       <c r="F97" t="n">
-        <v>31483</v>
+        <v>73228</v>
       </c>
       <c r="G97" t="n">
-        <v>63965</v>
+        <v>72840</v>
       </c>
       <c r="H97" t="n">
-        <v>72938</v>
+        <v>75549</v>
       </c>
       <c r="I97" t="n">
-        <v>25575</v>
+        <v>71792</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="b">
@@ -5499,50 +5499,50 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>31483</v>
+        <v>72840</v>
       </c>
       <c r="O97" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="P97" t="n">
-        <v>52.36</v>
+        <v>86.91</v>
       </c>
       <c r="Q97" t="n">
-        <v>5908</v>
+        <v>1048</v>
       </c>
       <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>914e39b5</t>
+          <t>e7b914a3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung CMF 2</t>
+          <t>Realme CMF 2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>76.23999999999999</v>
+        <v>52.98</v>
       </c>
       <c r="D98" t="n">
-        <v>122</v>
+        <v>423</v>
       </c>
       <c r="E98" t="n">
-        <v>32.82</v>
+        <v>23.76</v>
       </c>
       <c r="F98" t="n">
-        <v>37318</v>
+        <v>71020</v>
       </c>
       <c r="G98" t="n">
-        <v>52448</v>
+        <v>53092</v>
       </c>
       <c r="H98" t="n">
-        <v>38325</v>
+        <v>36194</v>
       </c>
       <c r="I98" t="n">
-        <v>33927</v>
+        <v>42064</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="b">
@@ -5551,50 +5551,50 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>37318</v>
+        <v>36194</v>
       </c>
       <c r="O98" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="P98" t="n">
-        <v>35.82</v>
+        <v>34.76000000000001</v>
       </c>
       <c r="Q98" t="n">
-        <v>3391</v>
+        <v>5870</v>
       </c>
       <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>99ed274e</t>
+          <t>82e41800</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Apple 14</t>
+          <t>Samsung Nord</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>63.96</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>378</v>
+        <v>442</v>
       </c>
       <c r="E99" t="n">
-        <v>79.59999999999999</v>
+        <v>24.86</v>
       </c>
       <c r="F99" t="n">
-        <v>53159</v>
+        <v>51961</v>
       </c>
       <c r="G99" t="n">
-        <v>62563</v>
+        <v>31425</v>
       </c>
       <c r="H99" t="n">
-        <v>43699</v>
+        <v>39903</v>
       </c>
       <c r="I99" t="n">
-        <v>40162</v>
+        <v>31927</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="b">
@@ -5603,50 +5603,50 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>43699</v>
+        <v>31425</v>
       </c>
       <c r="O99" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="P99" t="n">
-        <v>90.59999999999999</v>
+        <v>34.86</v>
       </c>
       <c r="Q99" t="n">
-        <v>3537</v>
+        <v>502</v>
       </c>
       <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>282eca91</t>
+          <t>0eb9f19f</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Realme S23</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>90.88</v>
+        <v>57.02</v>
       </c>
       <c r="D100" t="n">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="E100" t="n">
-        <v>85.47</v>
+        <v>64.52</v>
       </c>
       <c r="F100" t="n">
-        <v>51980</v>
+        <v>55879</v>
       </c>
       <c r="G100" t="n">
-        <v>69104</v>
+        <v>77609</v>
       </c>
       <c r="H100" t="n">
-        <v>62954</v>
+        <v>65923</v>
       </c>
       <c r="I100" t="n">
-        <v>73207</v>
+        <v>78340</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="b">
@@ -5655,50 +5655,50 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>51980</v>
+        <v>55879</v>
       </c>
       <c r="O100" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P100" t="n">
-        <v>89.47</v>
+        <v>76.52</v>
       </c>
       <c r="Q100" t="n">
-        <v>21227</v>
+        <v>22461</v>
       </c>
       <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3e51d4dd</t>
+          <t>365ae9fd</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Xiaomi Pixel 8</t>
+          <t>Apple Edge 40</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>91.88</v>
+        <v>97.61</v>
       </c>
       <c r="D101" t="n">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="E101" t="n">
-        <v>13.85</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="F101" t="n">
-        <v>36192</v>
+        <v>53293</v>
       </c>
       <c r="G101" t="n">
-        <v>46502</v>
+        <v>34055</v>
       </c>
       <c r="H101" t="n">
-        <v>52056</v>
+        <v>34731</v>
       </c>
       <c r="I101" t="n">
-        <v>37906</v>
+        <v>31227</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="b">
@@ -5707,16 +5707,16 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>36192</v>
+        <v>34055</v>
       </c>
       <c r="O101" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="P101" t="n">
-        <v>16.85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="Q101" t="n">
-        <v>1714</v>
+        <v>2828</v>
       </c>
       <c r="R101" t="inlineStr"/>
     </row>
